--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="156">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,234 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Chilean Primera B</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Chilean Primera Division</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
+    <t>Turkish 1 Lig</t>
+  </si>
+  <si>
+    <t>Swiss Challenge League</t>
+  </si>
+  <si>
+    <t>Icelandic Urvalsdeild</t>
+  </si>
+  <si>
+    <t>Austrian Bundesliga</t>
+  </si>
+  <si>
+    <t>Saudi Professional League</t>
+  </si>
+  <si>
+    <t>Swiss Super League</t>
+  </si>
+  <si>
+    <t>English National League</t>
+  </si>
+  <si>
+    <t>English Sky Bet League 1</t>
+  </si>
+  <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
+    <t>00:45:00</t>
+  </si>
+  <si>
+    <t>01:05:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>Cobreloa Calama</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Univ Catolica (Chile)</t>
+  </si>
+  <si>
+    <t>Tolima</t>
+  </si>
+  <si>
+    <t>Ghazl El Mahallah</t>
+  </si>
+  <si>
+    <t>El Geish</t>
+  </si>
+  <si>
+    <t>Helsingborgs</t>
+  </si>
+  <si>
+    <t>Boluspor</t>
+  </si>
+  <si>
+    <t>Sariyer G.K.</t>
+  </si>
+  <si>
+    <t>Neuchatel Xamax</t>
+  </si>
+  <si>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
+    <t>KR Reykjavik</t>
+  </si>
+  <si>
+    <t>RZ Pellets WAC</t>
+  </si>
+  <si>
+    <t>Al-Hilal</t>
+  </si>
+  <si>
+    <t>FC Zurich</t>
+  </si>
+  <si>
+    <t>FC Halifax Town</t>
+  </si>
+  <si>
+    <t>Peterborough</t>
+  </si>
+  <si>
+    <t>Bradford</t>
+  </si>
+  <si>
+    <t>Wycombe</t>
+  </si>
+  <si>
+    <t>Leicester</t>
+  </si>
+  <si>
+    <t>Doncaster</t>
+  </si>
+  <si>
+    <t>Bromley</t>
+  </si>
+  <si>
+    <t>Rubio Nu</t>
+  </si>
+  <si>
+    <t>San Marcos</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>OHiggins</t>
+  </si>
+  <si>
+    <t>Cucuta Deportivo</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>ZED FC</t>
+  </si>
+  <si>
+    <t>Orebro</t>
+  </si>
+  <si>
+    <t>Keciorengucu</t>
+  </si>
+  <si>
+    <t>Pendikspor</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>Etoile Carouge</t>
+  </si>
+  <si>
+    <t>Vikingur Reykjavik</t>
+  </si>
+  <si>
+    <t>Lask Linz</t>
+  </si>
+  <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>Young Boys</t>
+  </si>
+  <si>
+    <t>Hartlepool</t>
+  </si>
+  <si>
+    <t>Stevenage</t>
+  </si>
+  <si>
+    <t>Cambridge Utd</t>
+  </si>
+  <si>
+    <t>Sheff Wed</t>
+  </si>
+  <si>
+    <t>Plymouth</t>
+  </si>
+  <si>
+    <t>Notts Co</t>
+  </si>
+  <si>
+    <t>Leyton Orient</t>
+  </si>
+  <si>
+    <t>Sportivo San Lorenzo</t>
+  </si>
+  <si>
+    <t>2026-08-30 01:22:04</t>
   </si>
 </sst>
 </file>
@@ -585,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +1056,5814 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2">
+        <v>1.69</v>
+      </c>
+      <c r="G2">
+        <v>2.12</v>
+      </c>
+      <c r="H2">
+        <v>3.9</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>3.45</v>
+      </c>
+      <c r="K2">
+        <v>7.4</v>
+      </c>
+      <c r="L2">
+        <v>1.32</v>
+      </c>
+      <c r="M2">
+        <v>1.05</v>
+      </c>
+      <c r="N2">
+        <v>2.98</v>
+      </c>
+      <c r="O2">
+        <v>1.05</v>
+      </c>
+      <c r="P2">
+        <v>1.88</v>
+      </c>
+      <c r="Q2">
+        <v>1.9</v>
+      </c>
+      <c r="R2">
+        <v>1.26</v>
+      </c>
+      <c r="S2">
+        <v>2.88</v>
+      </c>
+      <c r="T2">
+        <v>1.58</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>1.2</v>
+      </c>
+      <c r="W2">
+        <v>1.9</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2">
+        <v>1.01</v>
+      </c>
+      <c r="AR2">
+        <v>1.01</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>1.01</v>
+      </c>
+      <c r="AU2">
+        <v>1.01</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>1.01</v>
+      </c>
+      <c r="AY2">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2">
+        <v>1.01</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
+        <v>1.01</v>
+      </c>
+      <c r="BD2">
+        <v>1.01</v>
+      </c>
+      <c r="BE2">
+        <v>1.01</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3">
+        <v>1.85</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>5.3</v>
+      </c>
+      <c r="I3">
+        <v>7.2</v>
+      </c>
+      <c r="J3">
+        <v>2.74</v>
+      </c>
+      <c r="K3">
+        <v>3.45</v>
+      </c>
+      <c r="L3">
+        <v>1.54</v>
+      </c>
+      <c r="M3">
+        <v>1.13</v>
+      </c>
+      <c r="N3">
+        <v>2.28</v>
+      </c>
+      <c r="O3">
+        <v>1.63</v>
+      </c>
+      <c r="P3">
+        <v>1.36</v>
+      </c>
+      <c r="Q3">
+        <v>3</v>
+      </c>
+      <c r="R3">
+        <v>1.12</v>
+      </c>
+      <c r="S3">
+        <v>6.4</v>
+      </c>
+      <c r="T3">
+        <v>2.22</v>
+      </c>
+      <c r="U3">
+        <v>1.01</v>
+      </c>
+      <c r="V3">
+        <v>1.17</v>
+      </c>
+      <c r="W3">
+        <v>2</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>6.2</v>
+      </c>
+      <c r="AQ3">
+        <v>9.4</v>
+      </c>
+      <c r="AR3">
+        <v>24</v>
+      </c>
+      <c r="AS3">
+        <v>95</v>
+      </c>
+      <c r="AT3">
+        <v>5</v>
+      </c>
+      <c r="AU3">
+        <v>6.6</v>
+      </c>
+      <c r="AV3">
+        <v>19</v>
+      </c>
+      <c r="AW3">
+        <v>70</v>
+      </c>
+      <c r="AX3">
+        <v>7.6</v>
+      </c>
+      <c r="AY3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ3">
+        <v>26</v>
+      </c>
+      <c r="BA3">
+        <v>100</v>
+      </c>
+      <c r="BB3">
+        <v>16.5</v>
+      </c>
+      <c r="BC3">
+        <v>21</v>
+      </c>
+      <c r="BD3">
+        <v>50</v>
+      </c>
+      <c r="BE3">
+        <v>100</v>
+      </c>
+      <c r="BF3">
+        <v>1.01</v>
+      </c>
+      <c r="BG3">
+        <v>1.01</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4">
+        <v>1.89</v>
+      </c>
+      <c r="G4">
+        <v>2.04</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>5.9</v>
+      </c>
+      <c r="J4">
+        <v>3.05</v>
+      </c>
+      <c r="K4">
+        <v>3.5</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.13</v>
+      </c>
+      <c r="N4">
+        <v>2.4</v>
+      </c>
+      <c r="O4">
+        <v>1.6</v>
+      </c>
+      <c r="P4">
+        <v>1.49</v>
+      </c>
+      <c r="Q4">
+        <v>2.8</v>
+      </c>
+      <c r="R4">
+        <v>1.15</v>
+      </c>
+      <c r="S4">
+        <v>6</v>
+      </c>
+      <c r="T4">
+        <v>2.14</v>
+      </c>
+      <c r="U4">
+        <v>1.51</v>
+      </c>
+      <c r="V4">
+        <v>1.2</v>
+      </c>
+      <c r="W4">
+        <v>1.96</v>
+      </c>
+      <c r="X4">
+        <v>9.4</v>
+      </c>
+      <c r="Y4">
+        <v>13</v>
+      </c>
+      <c r="Z4">
+        <v>50</v>
+      </c>
+      <c r="AA4">
+        <v>220</v>
+      </c>
+      <c r="AB4">
+        <v>6.2</v>
+      </c>
+      <c r="AC4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD4">
+        <v>25</v>
+      </c>
+      <c r="AE4">
+        <v>150</v>
+      </c>
+      <c r="AF4">
+        <v>10.5</v>
+      </c>
+      <c r="AG4">
+        <v>12.5</v>
+      </c>
+      <c r="AH4">
+        <v>46</v>
+      </c>
+      <c r="AI4">
+        <v>180</v>
+      </c>
+      <c r="AJ4">
+        <v>25</v>
+      </c>
+      <c r="AK4">
+        <v>46</v>
+      </c>
+      <c r="AL4">
+        <v>100</v>
+      </c>
+      <c r="AM4">
+        <v>360</v>
+      </c>
+      <c r="AN4">
+        <v>29</v>
+      </c>
+      <c r="AO4">
+        <v>280</v>
+      </c>
+      <c r="AP4">
+        <v>6.8</v>
+      </c>
+      <c r="AQ4">
+        <v>10</v>
+      </c>
+      <c r="AR4">
+        <v>23</v>
+      </c>
+      <c r="AS4">
+        <v>7.6</v>
+      </c>
+      <c r="AT4">
+        <v>5.2</v>
+      </c>
+      <c r="AU4">
+        <v>6.6</v>
+      </c>
+      <c r="AV4">
+        <v>20</v>
+      </c>
+      <c r="AW4">
+        <v>7.4</v>
+      </c>
+      <c r="AX4">
+        <v>8.6</v>
+      </c>
+      <c r="AY4">
+        <v>10</v>
+      </c>
+      <c r="AZ4">
+        <v>18.5</v>
+      </c>
+      <c r="BA4">
+        <v>7.4</v>
+      </c>
+      <c r="BB4">
+        <v>20</v>
+      </c>
+      <c r="BC4">
+        <v>18.5</v>
+      </c>
+      <c r="BD4">
+        <v>7.2</v>
+      </c>
+      <c r="BE4">
+        <v>7.6</v>
+      </c>
+      <c r="BF4">
+        <v>16.5</v>
+      </c>
+      <c r="BG4">
+        <v>7.6</v>
+      </c>
+      <c r="BH4">
+        <v>2.96</v>
+      </c>
+      <c r="BI4">
+        <v>2.12</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F5">
+        <v>1.81</v>
+      </c>
+      <c r="G5">
+        <v>1.97</v>
+      </c>
+      <c r="H5">
+        <v>4.2</v>
+      </c>
+      <c r="I5">
+        <v>4.9</v>
+      </c>
+      <c r="J5">
+        <v>3.75</v>
+      </c>
+      <c r="K5">
+        <v>4.2</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.05</v>
+      </c>
+      <c r="N5">
+        <v>4.1</v>
+      </c>
+      <c r="O5">
+        <v>1.26</v>
+      </c>
+      <c r="P5">
+        <v>2.06</v>
+      </c>
+      <c r="Q5">
+        <v>1.76</v>
+      </c>
+      <c r="R5">
+        <v>1.42</v>
+      </c>
+      <c r="S5">
+        <v>2.92</v>
+      </c>
+      <c r="T5">
+        <v>1.72</v>
+      </c>
+      <c r="U5">
+        <v>2.14</v>
+      </c>
+      <c r="V5">
+        <v>1.25</v>
+      </c>
+      <c r="W5">
+        <v>2.02</v>
+      </c>
+      <c r="X5">
+        <v>22</v>
+      </c>
+      <c r="Y5">
+        <v>22</v>
+      </c>
+      <c r="Z5">
+        <v>44</v>
+      </c>
+      <c r="AA5">
+        <v>120</v>
+      </c>
+      <c r="AB5">
+        <v>12.5</v>
+      </c>
+      <c r="AC5">
+        <v>11</v>
+      </c>
+      <c r="AD5">
+        <v>22</v>
+      </c>
+      <c r="AE5">
+        <v>65</v>
+      </c>
+      <c r="AF5">
+        <v>15</v>
+      </c>
+      <c r="AG5">
+        <v>12.5</v>
+      </c>
+      <c r="AH5">
+        <v>22</v>
+      </c>
+      <c r="AI5">
+        <v>70</v>
+      </c>
+      <c r="AJ5">
+        <v>26</v>
+      </c>
+      <c r="AK5">
+        <v>23</v>
+      </c>
+      <c r="AL5">
+        <v>40</v>
+      </c>
+      <c r="AM5">
+        <v>110</v>
+      </c>
+      <c r="AN5">
+        <v>13.5</v>
+      </c>
+      <c r="AO5">
+        <v>65</v>
+      </c>
+      <c r="AP5">
+        <v>12.5</v>
+      </c>
+      <c r="AQ5">
+        <v>13</v>
+      </c>
+      <c r="AR5">
+        <v>1.01</v>
+      </c>
+      <c r="AS5">
+        <v>1.01</v>
+      </c>
+      <c r="AT5">
+        <v>7.4</v>
+      </c>
+      <c r="AU5">
+        <v>6.8</v>
+      </c>
+      <c r="AV5">
+        <v>13</v>
+      </c>
+      <c r="AW5">
+        <v>1.01</v>
+      </c>
+      <c r="AX5">
+        <v>9</v>
+      </c>
+      <c r="AY5">
+        <v>7.6</v>
+      </c>
+      <c r="AZ5">
+        <v>13</v>
+      </c>
+      <c r="BA5">
+        <v>1.01</v>
+      </c>
+      <c r="BB5">
+        <v>15</v>
+      </c>
+      <c r="BC5">
+        <v>13.5</v>
+      </c>
+      <c r="BD5">
+        <v>1.01</v>
+      </c>
+      <c r="BE5">
+        <v>1.01</v>
+      </c>
+      <c r="BF5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>4.7</v>
+      </c>
+      <c r="BI5">
+        <v>2.94</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6">
+        <v>1.37</v>
+      </c>
+      <c r="G6">
+        <v>1.52</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>110</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>240</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>2.46</v>
+      </c>
+      <c r="O6">
+        <v>1.27</v>
+      </c>
+      <c r="P6">
+        <v>1.99</v>
+      </c>
+      <c r="Q6">
+        <v>1.78</v>
+      </c>
+      <c r="R6">
+        <v>1.37</v>
+      </c>
+      <c r="S6">
+        <v>2.88</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
+        <v>1.07</v>
+      </c>
+      <c r="W6">
+        <v>2.92</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6">
+        <v>1.01</v>
+      </c>
+      <c r="AR6">
+        <v>1.01</v>
+      </c>
+      <c r="AS6">
+        <v>1.01</v>
+      </c>
+      <c r="AT6">
+        <v>1.01</v>
+      </c>
+      <c r="AU6">
+        <v>1.01</v>
+      </c>
+      <c r="AV6">
+        <v>1.01</v>
+      </c>
+      <c r="AW6">
+        <v>1.01</v>
+      </c>
+      <c r="AX6">
+        <v>1.01</v>
+      </c>
+      <c r="AY6">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6">
+        <v>1.01</v>
+      </c>
+      <c r="BA6">
+        <v>1.01</v>
+      </c>
+      <c r="BB6">
+        <v>1.01</v>
+      </c>
+      <c r="BC6">
+        <v>1.01</v>
+      </c>
+      <c r="BD6">
+        <v>1.01</v>
+      </c>
+      <c r="BE6">
+        <v>1.01</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.01</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.01</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.01</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7">
+        <v>2.84</v>
+      </c>
+      <c r="G7">
+        <v>3.2</v>
+      </c>
+      <c r="H7">
+        <v>3.05</v>
+      </c>
+      <c r="I7">
+        <v>3.45</v>
+      </c>
+      <c r="J7">
+        <v>2.68</v>
+      </c>
+      <c r="K7">
+        <v>3.15</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.33</v>
+      </c>
+      <c r="Q7">
+        <v>3.15</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8">
+        <v>2.18</v>
+      </c>
+      <c r="G8">
+        <v>2.72</v>
+      </c>
+      <c r="H8">
+        <v>3.5</v>
+      </c>
+      <c r="I8">
+        <v>5.6</v>
+      </c>
+      <c r="J8">
+        <v>2.78</v>
+      </c>
+      <c r="K8">
+        <v>3.95</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.37</v>
+      </c>
+      <c r="Q8">
+        <v>2.56</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9">
+        <v>1.98</v>
+      </c>
+      <c r="G9">
+        <v>2.48</v>
+      </c>
+      <c r="H9">
+        <v>2.76</v>
+      </c>
+      <c r="I9">
+        <v>4.1</v>
+      </c>
+      <c r="J9">
+        <v>3.5</v>
+      </c>
+      <c r="K9">
+        <v>100</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>2.02</v>
+      </c>
+      <c r="Q9">
+        <v>1.56</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F10">
+        <v>4.8</v>
+      </c>
+      <c r="G10">
+        <v>7.6</v>
+      </c>
+      <c r="H10">
+        <v>1.64</v>
+      </c>
+      <c r="I10">
+        <v>1.8</v>
+      </c>
+      <c r="J10">
+        <v>3.9</v>
+      </c>
+      <c r="K10">
+        <v>5.5</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>2.12</v>
+      </c>
+      <c r="Q10">
+        <v>1.01</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11">
+        <v>2.06</v>
+      </c>
+      <c r="G11">
+        <v>2.78</v>
+      </c>
+      <c r="H11">
+        <v>2.8</v>
+      </c>
+      <c r="I11">
+        <v>4.2</v>
+      </c>
+      <c r="J11">
+        <v>3.25</v>
+      </c>
+      <c r="K11">
+        <v>6.4</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.65</v>
+      </c>
+      <c r="Q11">
+        <v>1.88</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" t="s">
+        <v>141</v>
+      </c>
+      <c r="F12">
+        <v>2.72</v>
+      </c>
+      <c r="G12">
+        <v>3.45</v>
+      </c>
+      <c r="H12">
+        <v>2.24</v>
+      </c>
+      <c r="I12">
+        <v>2.58</v>
+      </c>
+      <c r="J12">
+        <v>3.85</v>
+      </c>
+      <c r="K12">
+        <v>5.4</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>2.96</v>
+      </c>
+      <c r="Q12">
+        <v>1.36</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F13">
+        <v>1.57</v>
+      </c>
+      <c r="G13">
+        <v>1.71</v>
+      </c>
+      <c r="H13">
+        <v>4.7</v>
+      </c>
+      <c r="I13">
+        <v>6.4</v>
+      </c>
+      <c r="J13">
+        <v>4.7</v>
+      </c>
+      <c r="K13">
+        <v>6.6</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>3.55</v>
+      </c>
+      <c r="Q13">
+        <v>1.34</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" t="s">
+        <v>143</v>
+      </c>
+      <c r="F14">
+        <v>1.04</v>
+      </c>
+      <c r="G14">
+        <v>1000</v>
+      </c>
+      <c r="H14">
+        <v>1.04</v>
+      </c>
+      <c r="I14">
+        <v>1000</v>
+      </c>
+      <c r="J14">
+        <v>1.04</v>
+      </c>
+      <c r="K14">
+        <v>180</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>3.85</v>
+      </c>
+      <c r="O14">
+        <v>1.03</v>
+      </c>
+      <c r="P14">
+        <v>3.85</v>
+      </c>
+      <c r="Q14">
+        <v>1.17</v>
+      </c>
+      <c r="R14">
+        <v>2.28</v>
+      </c>
+      <c r="S14">
+        <v>1.42</v>
+      </c>
+      <c r="T14">
+        <v>1.01</v>
+      </c>
+      <c r="U14">
+        <v>1.01</v>
+      </c>
+      <c r="V14">
+        <v>1.01</v>
+      </c>
+      <c r="W14">
+        <v>1.01</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>1000</v>
+      </c>
+      <c r="AC14">
+        <v>1000</v>
+      </c>
+      <c r="AD14">
+        <v>1000</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14">
+        <v>1.01</v>
+      </c>
+      <c r="AR14">
+        <v>1.01</v>
+      </c>
+      <c r="AS14">
+        <v>1.01</v>
+      </c>
+      <c r="AT14">
+        <v>1.01</v>
+      </c>
+      <c r="AU14">
+        <v>1.01</v>
+      </c>
+      <c r="AV14">
+        <v>1.01</v>
+      </c>
+      <c r="AW14">
+        <v>1.01</v>
+      </c>
+      <c r="AX14">
+        <v>1.01</v>
+      </c>
+      <c r="AY14">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14">
+        <v>1.01</v>
+      </c>
+      <c r="BA14">
+        <v>1.01</v>
+      </c>
+      <c r="BB14">
+        <v>1.01</v>
+      </c>
+      <c r="BC14">
+        <v>1.01</v>
+      </c>
+      <c r="BD14">
+        <v>1.01</v>
+      </c>
+      <c r="BE14">
+        <v>1.01</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.01</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.01</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.01</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.01</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.01</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" t="s">
+        <v>144</v>
+      </c>
+      <c r="F15">
+        <v>1.04</v>
+      </c>
+      <c r="G15">
+        <v>1000</v>
+      </c>
+      <c r="H15">
+        <v>1.04</v>
+      </c>
+      <c r="I15">
+        <v>1000</v>
+      </c>
+      <c r="J15">
+        <v>1.04</v>
+      </c>
+      <c r="K15">
+        <v>950</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1.24</v>
+      </c>
+      <c r="Q15">
+        <v>1.01</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" t="s">
+        <v>145</v>
+      </c>
+      <c r="F16">
+        <v>1.77</v>
+      </c>
+      <c r="G16">
+        <v>1.91</v>
+      </c>
+      <c r="H16">
+        <v>4.1</v>
+      </c>
+      <c r="I16">
+        <v>4.7</v>
+      </c>
+      <c r="J16">
+        <v>4.1</v>
+      </c>
+      <c r="K16">
+        <v>4.7</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>2.48</v>
+      </c>
+      <c r="Q16">
+        <v>1.57</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17">
+        <v>4.5</v>
+      </c>
+      <c r="G17">
+        <v>1000</v>
+      </c>
+      <c r="H17">
+        <v>1.59</v>
+      </c>
+      <c r="I17">
+        <v>1.73</v>
+      </c>
+      <c r="J17">
+        <v>2.36</v>
+      </c>
+      <c r="K17">
+        <v>6.8</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>3.25</v>
+      </c>
+      <c r="Q17">
+        <v>1.32</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F18">
+        <v>2.54</v>
+      </c>
+      <c r="G18">
+        <v>2.92</v>
+      </c>
+      <c r="H18">
+        <v>2.6</v>
+      </c>
+      <c r="I18">
+        <v>3</v>
+      </c>
+      <c r="J18">
+        <v>3.35</v>
+      </c>
+      <c r="K18">
+        <v>3.95</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.81</v>
+      </c>
+      <c r="Q18">
+        <v>1.83</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19">
+        <v>2.6</v>
+      </c>
+      <c r="G19">
+        <v>2.94</v>
+      </c>
+      <c r="H19">
+        <v>1.09</v>
+      </c>
+      <c r="I19">
+        <v>3.05</v>
+      </c>
+      <c r="J19">
+        <v>1.53</v>
+      </c>
+      <c r="K19">
+        <v>3.8</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>1.12</v>
+      </c>
+      <c r="Q19">
+        <v>1.98</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" t="s">
+        <v>149</v>
+      </c>
+      <c r="F20">
+        <v>1.82</v>
+      </c>
+      <c r="G20">
+        <v>1.9</v>
+      </c>
+      <c r="H20">
+        <v>4.4</v>
+      </c>
+      <c r="I20">
+        <v>5.3</v>
+      </c>
+      <c r="J20">
+        <v>3.7</v>
+      </c>
+      <c r="K20">
+        <v>4.1</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>2</v>
+      </c>
+      <c r="Q20">
+        <v>1.83</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
+        <v>0</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21">
+        <v>2.54</v>
+      </c>
+      <c r="G21">
+        <v>2.88</v>
+      </c>
+      <c r="H21">
+        <v>2.58</v>
+      </c>
+      <c r="I21">
+        <v>2.96</v>
+      </c>
+      <c r="J21">
+        <v>3.45</v>
+      </c>
+      <c r="K21">
+        <v>4.6</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>2.12</v>
+      </c>
+      <c r="Q21">
+        <v>1.72</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>2.16</v>
+      </c>
+      <c r="H22">
+        <v>3.5</v>
+      </c>
+      <c r="I22">
+        <v>4.1</v>
+      </c>
+      <c r="J22">
+        <v>3.95</v>
+      </c>
+      <c r="K22">
+        <v>4.7</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>2.24</v>
+      </c>
+      <c r="Q22">
+        <v>1.65</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" t="s">
+        <v>152</v>
+      </c>
+      <c r="F23">
+        <v>2.06</v>
+      </c>
+      <c r="G23">
+        <v>2.22</v>
+      </c>
+      <c r="H23">
+        <v>3.3</v>
+      </c>
+      <c r="I23">
+        <v>4</v>
+      </c>
+      <c r="J23">
+        <v>3.7</v>
+      </c>
+      <c r="K23">
+        <v>4</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>1.98</v>
+      </c>
+      <c r="Q23">
+        <v>1.8</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" t="s">
+        <v>153</v>
+      </c>
+      <c r="F24">
+        <v>2.32</v>
+      </c>
+      <c r="G24">
+        <v>3.2</v>
+      </c>
+      <c r="H24">
+        <v>2.46</v>
+      </c>
+      <c r="I24">
+        <v>3.4</v>
+      </c>
+      <c r="J24">
+        <v>3.4</v>
+      </c>
+      <c r="K24">
+        <v>6.2</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>1.76</v>
+      </c>
+      <c r="Q24">
+        <v>1.01</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
+        <v>0</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>0</v>
+      </c>
+      <c r="BY24">
+        <v>0</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" t="s">
+        <v>154</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>1.24</v>
+      </c>
+      <c r="Q25">
+        <v>1.01</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+      <c r="BG25">
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <v>0</v>
+      </c>
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <v>0</v>
+      </c>
+      <c r="BK25">
+        <v>0</v>
+      </c>
+      <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <v>0</v>
+      </c>
+      <c r="BN25">
+        <v>0</v>
+      </c>
+      <c r="BO25">
+        <v>0</v>
+      </c>
+      <c r="BP25">
+        <v>0</v>
+      </c>
+      <c r="BQ25">
+        <v>0</v>
+      </c>
+      <c r="BR25">
+        <v>0</v>
+      </c>
+      <c r="BS25">
+        <v>0</v>
+      </c>
+      <c r="BT25">
+        <v>0</v>
+      </c>
+      <c r="BU25">
+        <v>0</v>
+      </c>
+      <c r="BV25">
+        <v>0</v>
+      </c>
+      <c r="BW25">
+        <v>0</v>
+      </c>
+      <c r="BX25">
+        <v>0</v>
+      </c>
+      <c r="BY25">
+        <v>0</v>
+      </c>
+      <c r="BZ25">
+        <v>0</v>
+      </c>
+      <c r="CA25">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
@@ -481,7 +481,7 @@
     <t>Sportivo San Lorenzo</t>
   </si>
   <si>
-    <t>2026-08-30 01:22:04</t>
+    <t>2026-08-30 03:42:37</t>
   </si>
 </sst>
 </file>
@@ -1075,58 +1075,58 @@
         <v>131</v>
       </c>
       <c r="F2">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="G2">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="H2">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J2">
         <v>3.45</v>
       </c>
       <c r="K2">
-        <v>7.4</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
         <v>1.32</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="Q2">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R2">
         <v>1.26</v>
       </c>
       <c r="S2">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="T2">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V2">
         <v>1.2</v>
       </c>
       <c r="W2">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1326,7 +1326,7 @@
         <v>5.3</v>
       </c>
       <c r="I3">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
         <v>2.74</v>
@@ -1338,145 +1338,145 @@
         <v>1.54</v>
       </c>
       <c r="M3">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="O3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P3">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Q3">
         <v>3</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S3">
         <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="V3">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W3">
         <v>2</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AP3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ3">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>24</v>
+        <v>5.2</v>
       </c>
       <c r="AS3">
-        <v>95</v>
+        <v>5.6</v>
       </c>
       <c r="AT3">
         <v>5</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>19</v>
+        <v>4.8</v>
       </c>
       <c r="AW3">
-        <v>70</v>
+        <v>5.6</v>
       </c>
       <c r="AX3">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="BA3">
-        <v>100</v>
+        <v>5.6</v>
       </c>
       <c r="BB3">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BC3">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BD3">
-        <v>50</v>
+        <v>5.4</v>
       </c>
       <c r="BE3">
-        <v>100</v>
+        <v>5.7</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1565,7 +1565,7 @@
         <v>2.04</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I4">
         <v>5.9</v>
@@ -1679,7 +1679,7 @@
         <v>7.6</v>
       </c>
       <c r="AT4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU4">
         <v>6.6</v>
@@ -1801,7 +1801,7 @@
         <v>134</v>
       </c>
       <c r="F5">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G5">
         <v>1.97</v>
@@ -1810,7 +1810,7 @@
         <v>4.2</v>
       </c>
       <c r="I5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J5">
         <v>3.75</v>
@@ -1831,16 +1831,16 @@
         <v>1.26</v>
       </c>
       <c r="P5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q5">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R5">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S5">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T5">
         <v>1.72</v>
@@ -1849,7 +1849,7 @@
         <v>2.14</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W5">
         <v>2.02</v>
@@ -1933,7 +1933,7 @@
         <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY5">
         <v>7.6</v>
@@ -2288,16 +2288,16 @@
         <v>2.84</v>
       </c>
       <c r="G7">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H7">
         <v>3.05</v>
       </c>
       <c r="I7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J7">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K7">
         <v>3.15</v>
@@ -2769,7 +2769,7 @@
         <v>138</v>
       </c>
       <c r="F9">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G9">
         <v>2.48</v>
@@ -2784,7 +2784,7 @@
         <v>3.5</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>7.4</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -3979,19 +3979,19 @@
         <v>143</v>
       </c>
       <c r="F14">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="G14">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="H14">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="J14">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="K14">
         <v>180</v>
@@ -4738,7 +4738,7 @@
         <v>3.25</v>
       </c>
       <c r="Q17">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5434,16 +5434,16 @@
         <v>1.82</v>
       </c>
       <c r="G20">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H20">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I20">
         <v>5.3</v>
       </c>
       <c r="J20">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K20">
         <v>4.1</v>
@@ -5461,10 +5461,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q20">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5685,10 +5685,10 @@
         <v>2.96</v>
       </c>
       <c r="J21">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K21">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5918,10 +5918,10 @@
         <v>2</v>
       </c>
       <c r="G22">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H22">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I22">
         <v>4.1</v>
@@ -5930,7 +5930,7 @@
         <v>3.95</v>
       </c>
       <c r="K22">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -5948,7 +5948,7 @@
         <v>2.24</v>
       </c>
       <c r="Q22">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6157,22 +6157,22 @@
         <v>152</v>
       </c>
       <c r="F23">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G23">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="H23">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J23">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6187,10 +6187,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q23">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="R23">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
@@ -481,7 +481,7 @@
     <t>Sportivo San Lorenzo</t>
   </si>
   <si>
-    <t>2026-08-30 03:42:37</t>
+    <t>2026-08-30 06:03:59</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1084,7 @@
         <v>4.3</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J2">
         <v>3.45</v>
@@ -1114,16 +1114,16 @@
         <v>1.26</v>
       </c>
       <c r="S2">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="T2">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="U2">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="V2">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W2">
         <v>1.96</v>
@@ -1326,10 +1326,10 @@
         <v>5.3</v>
       </c>
       <c r="I3">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J3">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="K3">
         <v>3.45</v>
@@ -1341,7 +1341,7 @@
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="O3">
         <v>1.64</v>
@@ -1365,7 +1365,7 @@
         <v>1.5</v>
       </c>
       <c r="V3">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W3">
         <v>2</v>
@@ -1395,7 +1395,7 @@
         <v>170</v>
       </c>
       <c r="AF3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG3">
         <v>14</v>
@@ -1431,10 +1431,10 @@
         <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS3">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT3">
         <v>5</v>
@@ -1443,10 +1443,10 @@
         <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AW3">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX3">
         <v>8.199999999999999</v>
@@ -1455,28 +1455,28 @@
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BA3">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB3">
         <v>20</v>
       </c>
       <c r="BC3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD3">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG3">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1559,7 +1559,7 @@
         <v>133</v>
       </c>
       <c r="F4">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G4">
         <v>2.04</v>
@@ -1571,10 +1571,10 @@
         <v>5.9</v>
       </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1583,13 +1583,13 @@
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="O4">
         <v>1.6</v>
       </c>
       <c r="P4">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Q4">
         <v>2.8</v>
@@ -3268,7 +3268,7 @@
         <v>3.25</v>
       </c>
       <c r="K11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3740,7 +3740,7 @@
         <v>1.57</v>
       </c>
       <c r="G13">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H13">
         <v>4.7</v>
@@ -3749,7 +3749,7 @@
         <v>6.4</v>
       </c>
       <c r="J13">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K13">
         <v>6.6</v>
@@ -3767,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q13">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>2.92</v>
       </c>
       <c r="K14">
-        <v>180</v>
+        <v>11.5</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4708,19 +4708,19 @@
         <v>4.5</v>
       </c>
       <c r="G17">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="H17">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I17">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="J17">
-        <v>2.36</v>
+        <v>4.2</v>
       </c>
       <c r="K17">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4735,7 +4735,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q17">
         <v>1.34</v>
@@ -5189,22 +5189,22 @@
         <v>148</v>
       </c>
       <c r="F19">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="G19">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H19">
-        <v>1.09</v>
+        <v>2.72</v>
       </c>
       <c r="I19">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J19">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="K19">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5461,10 +5461,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q20">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5706,7 +5706,7 @@
         <v>2.12</v>
       </c>
       <c r="Q21">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -5918,7 +5918,7 @@
         <v>2</v>
       </c>
       <c r="G22">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H22">
         <v>3.6</v>
@@ -5930,7 +5930,7 @@
         <v>3.95</v>
       </c>
       <c r="K22">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6157,22 +6157,22 @@
         <v>152</v>
       </c>
       <c r="F23">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G23">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="H23">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I23">
+        <v>4</v>
+      </c>
+      <c r="J23">
+        <v>3.6</v>
+      </c>
+      <c r="K23">
         <v>3.95</v>
-      </c>
-      <c r="J23">
-        <v>3.4</v>
-      </c>
-      <c r="K23">
-        <v>3.8</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         <v>1.76</v>
       </c>
       <c r="Q24">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="R24">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
@@ -481,7 +481,7 @@
     <t>Sportivo San Lorenzo</t>
   </si>
   <si>
-    <t>2026-08-30 06:03:59</t>
+    <t>2026-08-30 08:25:00</t>
   </si>
 </sst>
 </file>
@@ -1090,37 +1090,37 @@
         <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
         <v>1.32</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="P2">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="R2">
         <v>1.26</v>
       </c>
       <c r="S2">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="T2">
         <v>1.58</v>
       </c>
       <c r="U2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V2">
         <v>1.23</v>
@@ -1326,10 +1326,10 @@
         <v>5.3</v>
       </c>
       <c r="I3">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="K3">
         <v>3.45</v>
@@ -1365,7 +1365,7 @@
         <v>1.5</v>
       </c>
       <c r="V3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W3">
         <v>2</v>
@@ -1559,13 +1559,13 @@
         <v>133</v>
       </c>
       <c r="F4">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I4">
         <v>5.9</v>
@@ -1574,7 +1574,7 @@
         <v>3.1</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1610,10 +1610,10 @@
         <v>1.2</v>
       </c>
       <c r="W4">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X4">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y4">
         <v>13</v>
@@ -1643,7 +1643,7 @@
         <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AI4">
         <v>180</v>
@@ -1652,10 +1652,10 @@
         <v>25</v>
       </c>
       <c r="AK4">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AL4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AM4">
         <v>360</v>
@@ -1673,10 +1673,10 @@
         <v>10</v>
       </c>
       <c r="AR4">
-        <v>23</v>
+        <v>7.6</v>
       </c>
       <c r="AS4">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT4">
         <v>5.3</v>
@@ -1688,7 +1688,7 @@
         <v>20</v>
       </c>
       <c r="AW4">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX4">
         <v>8.6</v>
@@ -1697,28 +1697,28 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>18.5</v>
+        <v>7</v>
       </c>
       <c r="BA4">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB4">
         <v>20</v>
       </c>
       <c r="BC4">
-        <v>18.5</v>
+        <v>7</v>
       </c>
       <c r="BD4">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE4">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF4">
-        <v>16.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG4">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH4">
         <v>2.96</v>
@@ -1822,13 +1822,13 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
-        <v>4.1</v>
+        <v>2.78</v>
       </c>
       <c r="O5">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
         <v>2.08</v>
@@ -2043,7 +2043,7 @@
         <v>135</v>
       </c>
       <c r="F6">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="G6">
         <v>1.52</v>
@@ -2064,7 +2064,7 @@
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
         <v>2.46</v>
@@ -2769,22 +2769,22 @@
         <v>138</v>
       </c>
       <c r="F9">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="G9">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="H9">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="I9">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="J9">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K9">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -3026,7 +3026,7 @@
         <v>3.9</v>
       </c>
       <c r="K10">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3044,7 +3044,7 @@
         <v>2.12</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3256,7 +3256,7 @@
         <v>2.06</v>
       </c>
       <c r="G11">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H11">
         <v>2.8</v>
@@ -3740,16 +3740,16 @@
         <v>1.57</v>
       </c>
       <c r="G13">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H13">
         <v>4.7</v>
       </c>
       <c r="I13">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="J13">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K13">
         <v>6.6</v>
@@ -4947,7 +4947,7 @@
         <v>147</v>
       </c>
       <c r="F18">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="G18">
         <v>2.92</v>
@@ -4956,7 +4956,7 @@
         <v>2.6</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J18">
         <v>3.35</v>
@@ -4980,7 +4980,7 @@
         <v>1.81</v>
       </c>
       <c r="Q18">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5222,7 +5222,7 @@
         <v>1.12</v>
       </c>
       <c r="Q19">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5461,10 +5461,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q20">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -6399,22 +6399,22 @@
         <v>153</v>
       </c>
       <c r="F24">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="G24">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="H24">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="I24">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J24">
         <v>3.4</v>
       </c>
       <c r="K24">
-        <v>6.2</v>
+        <v>3.85</v>
       </c>
       <c r="L24">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
@@ -481,7 +481,7 @@
     <t>Sportivo San Lorenzo</t>
   </si>
   <si>
-    <t>2026-08-30 08:25:00</t>
+    <t>2026-08-30 10:46:03</t>
   </si>
 </sst>
 </file>
@@ -1102,22 +1102,22 @@
         <v>3</v>
       </c>
       <c r="O2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="P2">
         <v>1.7</v>
       </c>
       <c r="Q2">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R2">
         <v>1.26</v>
       </c>
       <c r="S2">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="T2">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U2">
         <v>1.7</v>
@@ -1323,7 +1323,7 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I3">
         <v>6.6</v>
@@ -1335,13 +1335,13 @@
         <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="M3">
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O3">
         <v>1.64</v>
@@ -1359,10 +1359,10 @@
         <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V3">
         <v>1.19</v>
@@ -1479,64 +1479,64 @@
         <v>5.9</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="BM3">
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BY3">
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="CB3" t="s">
         <v>155</v>
@@ -1559,10 +1559,10 @@
         <v>133</v>
       </c>
       <c r="F4">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H4">
         <v>5.1</v>
@@ -1571,13 +1571,13 @@
         <v>5.9</v>
       </c>
       <c r="J4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M4">
         <v>1.13</v>
@@ -1595,7 +1595,7 @@
         <v>2.8</v>
       </c>
       <c r="R4">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S4">
         <v>6</v>
@@ -1610,7 +1610,7 @@
         <v>1.2</v>
       </c>
       <c r="W4">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X4">
         <v>8.199999999999999</v>
@@ -1721,64 +1721,64 @@
         <v>8.6</v>
       </c>
       <c r="BH4">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="BI4">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="CB4" t="s">
         <v>155</v>
@@ -1822,13 +1822,13 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P5">
         <v>2.08</v>
@@ -2049,7 +2049,7 @@
         <v>1.52</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="I6">
         <v>110</v>
@@ -2079,7 +2079,7 @@
         <v>1.78</v>
       </c>
       <c r="R6">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S6">
         <v>2.88</v>
@@ -2288,13 +2288,13 @@
         <v>2.84</v>
       </c>
       <c r="G7">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H7">
         <v>3.05</v>
       </c>
       <c r="I7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J7">
         <v>2.72</v>
@@ -2799,10 +2799,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Q9">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -3737,7 +3737,7 @@
         <v>142</v>
       </c>
       <c r="F13">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G13">
         <v>1.71</v>
@@ -3752,7 +3752,7 @@
         <v>4.7</v>
       </c>
       <c r="K13">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3770,7 +3770,7 @@
         <v>3.7</v>
       </c>
       <c r="Q13">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3979,40 +3979,40 @@
         <v>143</v>
       </c>
       <c r="F14">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="G14">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="H14">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="I14">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="J14">
-        <v>2.92</v>
+        <v>4.6</v>
       </c>
       <c r="K14">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="M14">
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="O14">
         <v>1.03</v>
       </c>
       <c r="P14">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="Q14">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="R14">
         <v>2.28</v>
@@ -4141,55 +4141,55 @@
         <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK14">
         <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BM14">
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ14">
         <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS14">
         <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW14">
         <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BY14">
         <v>1.01</v>
@@ -4463,16 +4463,16 @@
         <v>145</v>
       </c>
       <c r="F16">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="G16">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H16">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I16">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J16">
         <v>4.1</v>
@@ -4711,16 +4711,16 @@
         <v>6.2</v>
       </c>
       <c r="H17">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I17">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="J17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K17">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4947,7 +4947,7 @@
         <v>147</v>
       </c>
       <c r="F18">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="G18">
         <v>2.92</v>
@@ -4956,7 +4956,7 @@
         <v>2.6</v>
       </c>
       <c r="I18">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J18">
         <v>3.35</v>
@@ -5198,13 +5198,13 @@
         <v>2.72</v>
       </c>
       <c r="I19">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="J19">
         <v>3.3</v>
       </c>
       <c r="K19">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5219,10 +5219,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.12</v>
+        <v>1.86</v>
       </c>
       <c r="Q19">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5443,7 +5443,7 @@
         <v>5.3</v>
       </c>
       <c r="J20">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K20">
         <v>4.1</v>
@@ -5464,7 +5464,7 @@
         <v>2</v>
       </c>
       <c r="Q20">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>2.54</v>
       </c>
       <c r="G21">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="H21">
         <v>2.58</v>
@@ -6172,7 +6172,7 @@
         <v>3.6</v>
       </c>
       <c r="K23">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6429,10 +6429,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="Q24">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="R24">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
@@ -481,7 +481,7 @@
     <t>Sportivo San Lorenzo</t>
   </si>
   <si>
-    <t>2026-08-30 10:46:03</t>
+    <t>2026-08-30 13:03:54</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1081,7 @@
         <v>2.04</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="I2">
         <v>5.3</v>
@@ -1162,7 +1162,7 @@
         <v>1000</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ2">
         <v>1000</v>
@@ -1317,7 +1317,7 @@
         <v>132</v>
       </c>
       <c r="F3">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1335,7 +1335,7 @@
         <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.15</v>
@@ -1395,7 +1395,7 @@
         <v>170</v>
       </c>
       <c r="AF3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG3">
         <v>14</v>
@@ -1431,10 +1431,10 @@
         <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT3">
         <v>5</v>
@@ -1443,10 +1443,10 @@
         <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AW3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX3">
         <v>8.199999999999999</v>
@@ -1455,88 +1455,88 @@
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB3">
         <v>20</v>
       </c>
       <c r="BC3">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BD3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE3">
         <v>6</v>
       </c>
       <c r="BF3">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG3">
+        <v>6</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>18.5</v>
+      </c>
+      <c r="BK3">
+        <v>8.4</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>21</v>
+      </c>
+      <c r="BN3">
+        <v>5.6</v>
+      </c>
+      <c r="BO3">
+        <v>2.96</v>
+      </c>
+      <c r="BP3">
+        <v>23</v>
+      </c>
+      <c r="BQ3">
+        <v>10.5</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>21</v>
+      </c>
+      <c r="BT3">
+        <v>12.5</v>
+      </c>
+      <c r="BU3">
         <v>5.9</v>
       </c>
-      <c r="BH3">
-        <v>2.74</v>
-      </c>
-      <c r="BI3">
-        <v>2.12</v>
-      </c>
-      <c r="BJ3">
-        <v>15.5</v>
-      </c>
-      <c r="BK3">
-        <v>10</v>
-      </c>
-      <c r="BL3">
-        <v>370</v>
-      </c>
-      <c r="BM3">
-        <v>1.01</v>
-      </c>
-      <c r="BN3">
-        <v>4.8</v>
-      </c>
-      <c r="BO3">
-        <v>3.4</v>
-      </c>
-      <c r="BP3">
-        <v>19</v>
-      </c>
-      <c r="BQ3">
-        <v>12.5</v>
-      </c>
-      <c r="BR3">
-        <v>60</v>
-      </c>
-      <c r="BS3">
-        <v>36</v>
-      </c>
-      <c r="BT3">
-        <v>10.5</v>
-      </c>
-      <c r="BU3">
-        <v>7</v>
-      </c>
       <c r="BV3">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BW3">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="BX3">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="CA3">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="CB3" t="s">
         <v>155</v>
@@ -1559,13 +1559,13 @@
         <v>133</v>
       </c>
       <c r="F4">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H4">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I4">
         <v>5.9</v>
@@ -1595,7 +1595,7 @@
         <v>2.8</v>
       </c>
       <c r="R4">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="S4">
         <v>6</v>
@@ -1610,7 +1610,7 @@
         <v>1.2</v>
       </c>
       <c r="W4">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X4">
         <v>8.199999999999999</v>
@@ -1804,7 +1804,7 @@
         <v>1.83</v>
       </c>
       <c r="G5">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H5">
         <v>4.2</v>
@@ -1852,7 +1852,7 @@
         <v>1.26</v>
       </c>
       <c r="W5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X5">
         <v>22</v>
@@ -1963,7 +1963,7 @@
         <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI5">
         <v>2.94</v>
@@ -2043,19 +2043,19 @@
         <v>135</v>
       </c>
       <c r="F6">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="G6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H6">
-        <v>4.6</v>
+        <v>1.09</v>
       </c>
       <c r="I6">
         <v>110</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K6">
         <v>240</v>
@@ -2064,25 +2064,25 @@
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="O6">
         <v>1.27</v>
       </c>
       <c r="P6">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R6">
         <v>1.39</v>
       </c>
       <c r="S6">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2094,7 +2094,7 @@
         <v>1.07</v>
       </c>
       <c r="W6">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2288,13 +2288,13 @@
         <v>2.84</v>
       </c>
       <c r="G7">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H7">
         <v>3.05</v>
       </c>
       <c r="I7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J7">
         <v>2.72</v>
@@ -2303,208 +2303,208 @@
         <v>3.15</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P7">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="Q7">
         <v>3.15</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
         <v>155</v>
@@ -2530,13 +2530,13 @@
         <v>2.18</v>
       </c>
       <c r="G8">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H8">
         <v>3.5</v>
       </c>
       <c r="I8">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J8">
         <v>2.78</v>
@@ -2545,16 +2545,16 @@
         <v>3.95</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
         <v>1.37</v>
@@ -2563,190 +2563,190 @@
         <v>2.56</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
         <v>155</v>
@@ -2769,7 +2769,7 @@
         <v>138</v>
       </c>
       <c r="F9">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G9">
         <v>2.38</v>
@@ -3014,7 +3014,7 @@
         <v>4.8</v>
       </c>
       <c r="G10">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H10">
         <v>1.64</v>
@@ -3023,10 +3023,10 @@
         <v>1.8</v>
       </c>
       <c r="J10">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K10">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3044,7 +3044,7 @@
         <v>2.12</v>
       </c>
       <c r="Q10">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3256,7 +3256,7 @@
         <v>2.06</v>
       </c>
       <c r="G11">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="H11">
         <v>2.8</v>
@@ -3286,7 +3286,7 @@
         <v>1.65</v>
       </c>
       <c r="Q11">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3737,22 +3737,22 @@
         <v>142</v>
       </c>
       <c r="F13">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="G13">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="H13">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J13">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3770,7 +3770,7 @@
         <v>3.7</v>
       </c>
       <c r="Q13">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>2.1</v>
       </c>
       <c r="I14">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="J14">
         <v>4.6</v>
@@ -4003,10 +4003,10 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="O14">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="P14">
         <v>4.8</v>
@@ -4015,130 +4015,130 @@
         <v>1.2</v>
       </c>
       <c r="R14">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH14">
         <v>9.199999999999999</v>
@@ -4159,13 +4159,13 @@
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO14">
         <v>6</v>
       </c>
       <c r="BP14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ14">
         <v>1.01</v>
@@ -4183,7 +4183,7 @@
         <v>5.4</v>
       </c>
       <c r="BV14">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW14">
         <v>1.01</v>
@@ -5198,13 +5198,13 @@
         <v>2.72</v>
       </c>
       <c r="I19">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J19">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K19">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5219,10 +5219,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5443,7 +5443,7 @@
         <v>5.3</v>
       </c>
       <c r="J20">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K20">
         <v>4.1</v>
@@ -5464,7 +5464,7 @@
         <v>2</v>
       </c>
       <c r="Q20">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5673,7 +5673,7 @@
         <v>150</v>
       </c>
       <c r="F21">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G21">
         <v>3.05</v>
@@ -5945,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q22">
         <v>1.68</v>
@@ -6163,7 +6163,7 @@
         <v>2.16</v>
       </c>
       <c r="H23">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I23">
         <v>4</v>
@@ -6172,7 +6172,7 @@
         <v>3.6</v>
       </c>
       <c r="K23">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6187,10 +6187,10 @@
         <v>0</v>
       </c>
       <c r="P23">
+        <v>1.9</v>
+      </c>
+      <c r="Q23">
         <v>1.91</v>
-      </c>
-      <c r="Q23">
-        <v>1.92</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6429,10 +6429,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q24">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="R24">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="139">
   <si>
     <t>League</t>
   </si>
@@ -271,33 +271,27 @@
     <t>Egyptian Premier</t>
   </si>
   <si>
+    <t>Turkish 1 Lig</t>
+  </si>
+  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
-    <t>Turkish 1 Lig</t>
+    <t>Austrian Bundesliga</t>
+  </si>
+  <si>
+    <t>Icelandic Urvalsdeild</t>
   </si>
   <si>
     <t>Swiss Challenge League</t>
   </si>
   <si>
-    <t>Icelandic Urvalsdeild</t>
-  </si>
-  <si>
-    <t>Austrian Bundesliga</t>
-  </si>
-  <si>
     <t>Saudi Professional League</t>
   </si>
   <si>
-    <t>Swiss Super League</t>
-  </si>
-  <si>
     <t>English National League</t>
   </si>
   <si>
-    <t>English Sky Bet League 1</t>
-  </si>
-  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
@@ -328,9 +322,6 @@
     <t>18:00:00</t>
   </si>
   <si>
-    <t>18:30:00</t>
-  </si>
-  <si>
     <t>18:45:00</t>
   </si>
   <si>
@@ -358,54 +349,33 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Sariyer G.K.</t>
+  </si>
+  <si>
+    <t>Boluspor</t>
+  </si>
+  <si>
     <t>Helsingborgs</t>
   </si>
   <si>
-    <t>Boluspor</t>
-  </si>
-  <si>
-    <t>Sariyer G.K.</t>
+    <t>RZ Pellets WAC</t>
+  </si>
+  <si>
+    <t>KR Reykjavik</t>
+  </si>
+  <si>
+    <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
     <t>Neuchatel Xamax</t>
   </si>
   <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
-    <t>KR Reykjavik</t>
-  </si>
-  <si>
-    <t>RZ Pellets WAC</t>
-  </si>
-  <si>
     <t>Al-Hilal</t>
   </si>
   <si>
-    <t>FC Zurich</t>
-  </si>
-  <si>
     <t>FC Halifax Town</t>
   </si>
   <si>
-    <t>Peterborough</t>
-  </si>
-  <si>
-    <t>Bradford</t>
-  </si>
-  <si>
-    <t>Wycombe</t>
-  </si>
-  <si>
-    <t>Leicester</t>
-  </si>
-  <si>
-    <t>Doncaster</t>
-  </si>
-  <si>
-    <t>Bromley</t>
-  </si>
-  <si>
     <t>Rubio Nu</t>
   </si>
   <si>
@@ -430,58 +400,37 @@
     <t>ZED FC</t>
   </si>
   <si>
+    <t>Pendikspor</t>
+  </si>
+  <si>
+    <t>Keciorengucu</t>
+  </si>
+  <si>
     <t>Orebro</t>
   </si>
   <si>
-    <t>Keciorengucu</t>
-  </si>
-  <si>
-    <t>Pendikspor</t>
+    <t>Lask Linz</t>
+  </si>
+  <si>
+    <t>Vikingur Reykjavik</t>
+  </si>
+  <si>
+    <t>Etoile Carouge</t>
   </si>
   <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
-    <t>Etoile Carouge</t>
-  </si>
-  <si>
-    <t>Vikingur Reykjavik</t>
-  </si>
-  <si>
-    <t>Lask Linz</t>
-  </si>
-  <si>
     <t>Al Ahli</t>
   </si>
   <si>
-    <t>Young Boys</t>
-  </si>
-  <si>
     <t>Hartlepool</t>
   </si>
   <si>
-    <t>Stevenage</t>
-  </si>
-  <si>
-    <t>Cambridge Utd</t>
-  </si>
-  <si>
-    <t>Sheff Wed</t>
-  </si>
-  <si>
-    <t>Plymouth</t>
-  </si>
-  <si>
-    <t>Notts Co</t>
-  </si>
-  <si>
-    <t>Leyton Orient</t>
-  </si>
-  <si>
     <t>Sportivo San Lorenzo</t>
   </si>
   <si>
-    <t>2026-08-30 13:03:54</t>
+    <t>2026-08-30 15:19:31</t>
   </si>
 </sst>
 </file>
@@ -813,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1063,175 +1012,175 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F2">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="G2">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="H2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q2">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="R2">
+        <v>1.3</v>
+      </c>
+      <c r="S2">
+        <v>3.65</v>
+      </c>
+      <c r="T2">
+        <v>1.83</v>
+      </c>
+      <c r="U2">
+        <v>1.95</v>
+      </c>
+      <c r="V2">
         <v>1.26</v>
       </c>
-      <c r="S2">
-        <v>2.6</v>
-      </c>
-      <c r="T2">
-        <v>1.01</v>
-      </c>
-      <c r="U2">
-        <v>1.7</v>
-      </c>
-      <c r="V2">
-        <v>1.23</v>
-      </c>
       <c r="W2">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI2">
         <v>100</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AS2">
         <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW2">
         <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA2">
         <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE2">
         <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
         <v>1.01</v>
@@ -1297,7 +1246,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1305,16 +1254,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" t="s">
         <v>95</v>
       </c>
-      <c r="C3" t="s">
-        <v>97</v>
-      </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F3">
         <v>1.86</v>
@@ -1335,7 +1284,7 @@
         <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M3">
         <v>1.15</v>
@@ -1479,67 +1428,67 @@
         <v>6</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BJ3">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BK3">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="BM3">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO3">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="BP3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>70</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
         <v>10.5</v>
       </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>21</v>
-      </c>
-      <c r="BT3">
-        <v>12.5</v>
-      </c>
       <c r="BU3">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BW3">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BY3">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="CA3">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1547,22 +1496,22 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
         <v>95</v>
       </c>
-      <c r="C4" t="s">
-        <v>97</v>
-      </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F4">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H4">
         <v>4.9</v>
@@ -1574,7 +1523,7 @@
         <v>3.05</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
         <v>1.52</v>
@@ -1583,13 +1532,13 @@
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="O4">
         <v>1.6</v>
       </c>
       <c r="P4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q4">
         <v>2.8</v>
@@ -1601,7 +1550,7 @@
         <v>6</v>
       </c>
       <c r="T4">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="U4">
         <v>1.51</v>
@@ -1610,7 +1559,7 @@
         <v>1.2</v>
       </c>
       <c r="W4">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X4">
         <v>8.199999999999999</v>
@@ -1730,7 +1679,7 @@
         <v>15.5</v>
       </c>
       <c r="BK4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL4">
         <v>350</v>
@@ -1739,49 +1688,49 @@
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BP4">
         <v>20</v>
       </c>
       <c r="BQ4">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
         <v>10.5</v>
       </c>
       <c r="BU4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BW4">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
         <v>110</v>
       </c>
       <c r="BY4">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
         <v>60</v>
       </c>
       <c r="CA4">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1789,37 +1738,37 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F5">
         <v>1.83</v>
       </c>
       <c r="G5">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="H5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I5">
         <v>4.8</v>
       </c>
       <c r="J5">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
         <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -1828,7 +1777,7 @@
         <v>4.1</v>
       </c>
       <c r="O5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P5">
         <v>2.08</v>
@@ -1852,7 +1801,7 @@
         <v>1.26</v>
       </c>
       <c r="W5">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="X5">
         <v>22</v>
@@ -1963,67 +1912,67 @@
         <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="BI5">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
         <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM5">
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ5">
         <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS5">
         <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU5">
         <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW5">
         <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY5">
         <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA5">
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2031,31 +1980,31 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F6">
         <v>1.37</v>
       </c>
       <c r="G6">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I6">
         <v>110</v>
       </c>
       <c r="J6">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="K6">
         <v>240</v>
@@ -2064,19 +2013,19 @@
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="O6">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q6">
-        <v>1.79</v>
+        <v>1.3</v>
       </c>
       <c r="R6">
         <v>1.39</v>
@@ -2085,7 +2034,7 @@
         <v>2.9</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U6">
         <v>1.01</v>
@@ -2094,7 +2043,7 @@
         <v>1.07</v>
       </c>
       <c r="W6">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2265,7 +2214,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2273,16 +2222,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F7">
         <v>2.84</v>
@@ -2300,7 +2249,7 @@
         <v>2.72</v>
       </c>
       <c r="K7">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2354,7 +2303,7 @@
         <v>9</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD7">
         <v>19.5</v>
@@ -2507,7 +2456,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2515,34 +2464,34 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="F8">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="G8">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I8">
         <v>5.3</v>
       </c>
       <c r="J8">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K8">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2554,7 +2503,7 @@
         <v>2.06</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P8">
         <v>1.37</v>
@@ -2569,7 +2518,7 @@
         <v>5</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U8">
         <v>1.01</v>
@@ -2578,7 +2527,7 @@
         <v>1.23</v>
       </c>
       <c r="W8">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2749,7 +2698,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2757,264 +2706,264 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9">
+        <v>2.06</v>
+      </c>
+      <c r="G9">
+        <v>2.78</v>
+      </c>
+      <c r="H9">
+        <v>2.8</v>
+      </c>
+      <c r="I9">
+        <v>4.1</v>
+      </c>
+      <c r="J9">
+        <v>3.25</v>
+      </c>
+      <c r="K9">
+        <v>6.2</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>2.72</v>
+      </c>
+      <c r="O9">
+        <v>1.33</v>
+      </c>
+      <c r="P9">
+        <v>1.65</v>
+      </c>
+      <c r="Q9">
+        <v>1.87</v>
+      </c>
+      <c r="R9">
+        <v>1.23</v>
+      </c>
+      <c r="S9">
+        <v>3.2</v>
+      </c>
+      <c r="T9">
+        <v>1.01</v>
+      </c>
+      <c r="U9">
+        <v>1.01</v>
+      </c>
+      <c r="V9">
+        <v>1.32</v>
+      </c>
+      <c r="W9">
+        <v>1.56</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9">
+        <v>1.01</v>
+      </c>
+      <c r="AR9">
+        <v>1.01</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>1.01</v>
+      </c>
+      <c r="AU9">
+        <v>1.01</v>
+      </c>
+      <c r="AV9">
+        <v>1.01</v>
+      </c>
+      <c r="AW9">
+        <v>1.01</v>
+      </c>
+      <c r="AX9">
+        <v>1.01</v>
+      </c>
+      <c r="AY9">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9">
+        <v>1.01</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>1.01</v>
+      </c>
+      <c r="BC9">
+        <v>1.01</v>
+      </c>
+      <c r="BD9">
+        <v>1.01</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>4</v>
+      </c>
+      <c r="BI9">
+        <v>2.6</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.01</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
         <v>138</v>
-      </c>
-      <c r="F9">
-        <v>2.14</v>
-      </c>
-      <c r="G9">
-        <v>2.38</v>
-      </c>
-      <c r="H9">
-        <v>3.1</v>
-      </c>
-      <c r="I9">
-        <v>3.65</v>
-      </c>
-      <c r="J9">
-        <v>3.6</v>
-      </c>
-      <c r="K9">
-        <v>4.3</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>2.2</v>
-      </c>
-      <c r="Q9">
-        <v>1.67</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>0</v>
-      </c>
-      <c r="AH9">
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <v>0</v>
-      </c>
-      <c r="AJ9">
-        <v>0</v>
-      </c>
-      <c r="AK9">
-        <v>0</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>0</v>
-      </c>
-      <c r="AO9">
-        <v>0</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>0</v>
-      </c>
-      <c r="BC9">
-        <v>0</v>
-      </c>
-      <c r="BD9">
-        <v>0</v>
-      </c>
-      <c r="BE9">
-        <v>0</v>
-      </c>
-      <c r="BF9">
-        <v>0</v>
-      </c>
-      <c r="BG9">
-        <v>0</v>
-      </c>
-      <c r="BH9">
-        <v>0</v>
-      </c>
-      <c r="BI9">
-        <v>0</v>
-      </c>
-      <c r="BJ9">
-        <v>0</v>
-      </c>
-      <c r="BK9">
-        <v>0</v>
-      </c>
-      <c r="BL9">
-        <v>0</v>
-      </c>
-      <c r="BM9">
-        <v>0</v>
-      </c>
-      <c r="BN9">
-        <v>0</v>
-      </c>
-      <c r="BO9">
-        <v>0</v>
-      </c>
-      <c r="BP9">
-        <v>0</v>
-      </c>
-      <c r="BQ9">
-        <v>0</v>
-      </c>
-      <c r="BR9">
-        <v>0</v>
-      </c>
-      <c r="BS9">
-        <v>0</v>
-      </c>
-      <c r="BT9">
-        <v>0</v>
-      </c>
-      <c r="BU9">
-        <v>0</v>
-      </c>
-      <c r="BV9">
-        <v>0</v>
-      </c>
-      <c r="BW9">
-        <v>0</v>
-      </c>
-      <c r="BX9">
-        <v>0</v>
-      </c>
-      <c r="BY9">
-        <v>0</v>
-      </c>
-      <c r="BZ9">
-        <v>0</v>
-      </c>
-      <c r="CA9">
-        <v>0</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F10">
         <v>4.8</v>
       </c>
       <c r="G10">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="H10">
         <v>1.64</v>
@@ -3023,217 +2972,217 @@
         <v>1.8</v>
       </c>
       <c r="J10">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K10">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P10">
         <v>2.12</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3241,232 +3190,232 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F11">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G11">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="H11">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="I11">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="J11">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="K11">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P11">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q11">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3475,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3483,474 +3432,474 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F12">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="G12">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="I12">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="K12">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P12">
-        <v>2.96</v>
+        <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F13">
-        <v>1.54</v>
+        <v>2.72</v>
       </c>
       <c r="G13">
-        <v>1.66</v>
+        <v>3.15</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="I13">
-        <v>5.8</v>
+        <v>2.34</v>
       </c>
       <c r="J13">
+        <v>4.6</v>
+      </c>
+      <c r="K13">
+        <v>5.5</v>
+      </c>
+      <c r="L13">
+        <v>1.12</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>12</v>
+      </c>
+      <c r="O13">
+        <v>1.06</v>
+      </c>
+      <c r="P13">
         <v>4.8</v>
       </c>
-      <c r="K13">
-        <v>6.6</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>3.7</v>
-      </c>
       <c r="Q13">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3959,249 +3908,249 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="F14">
-        <v>2.68</v>
+        <v>1.53</v>
       </c>
       <c r="G14">
-        <v>3.3</v>
+        <v>1.66</v>
       </c>
       <c r="H14">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>2.36</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K14">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="L14">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O14">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="P14">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q14">
+        <v>1.29</v>
+      </c>
+      <c r="R14">
+        <v>2.12</v>
+      </c>
+      <c r="S14">
+        <v>1.7</v>
+      </c>
+      <c r="T14">
+        <v>1.35</v>
+      </c>
+      <c r="U14">
+        <v>2.64</v>
+      </c>
+      <c r="V14">
         <v>1.2</v>
       </c>
-      <c r="R14">
-        <v>2.56</v>
-      </c>
-      <c r="S14">
-        <v>1.51</v>
-      </c>
-      <c r="T14">
-        <v>1.22</v>
-      </c>
-      <c r="U14">
+      <c r="W14">
+        <v>2.5</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>1000</v>
+      </c>
+      <c r="AC14">
+        <v>1000</v>
+      </c>
+      <c r="AD14">
+        <v>1000</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14">
+        <v>1.01</v>
+      </c>
+      <c r="AR14">
+        <v>1.01</v>
+      </c>
+      <c r="AS14">
+        <v>1.01</v>
+      </c>
+      <c r="AT14">
+        <v>1.01</v>
+      </c>
+      <c r="AU14">
+        <v>1.01</v>
+      </c>
+      <c r="AV14">
+        <v>1.01</v>
+      </c>
+      <c r="AW14">
+        <v>1.01</v>
+      </c>
+      <c r="AX14">
+        <v>1.01</v>
+      </c>
+      <c r="AY14">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14">
+        <v>1.01</v>
+      </c>
+      <c r="BA14">
+        <v>1.01</v>
+      </c>
+      <c r="BB14">
+        <v>1.01</v>
+      </c>
+      <c r="BC14">
+        <v>1.01</v>
+      </c>
+      <c r="BD14">
+        <v>1.01</v>
+      </c>
+      <c r="BE14">
+        <v>1.01</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BI14">
+        <v>4.1</v>
+      </c>
+      <c r="BJ14">
+        <v>12.5</v>
+      </c>
+      <c r="BK14">
+        <v>5.4</v>
+      </c>
+      <c r="BL14">
+        <v>75</v>
+      </c>
+      <c r="BM14">
+        <v>21</v>
+      </c>
+      <c r="BN14">
+        <v>7.6</v>
+      </c>
+      <c r="BO14">
         <v>3.55</v>
       </c>
-      <c r="V14">
-        <v>1.63</v>
-      </c>
-      <c r="W14">
-        <v>1.41</v>
-      </c>
-      <c r="X14">
-        <v>100</v>
-      </c>
-      <c r="Y14">
+      <c r="BP14">
+        <v>13.5</v>
+      </c>
+      <c r="BQ14">
+        <v>5.9</v>
+      </c>
+      <c r="BR14">
+        <v>22</v>
+      </c>
+      <c r="BS14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT14">
+        <v>14.5</v>
+      </c>
+      <c r="BU14">
+        <v>6.2</v>
+      </c>
+      <c r="BV14">
+        <v>46</v>
+      </c>
+      <c r="BW14">
+        <v>18.5</v>
+      </c>
+      <c r="BX14">
         <v>44</v>
       </c>
-      <c r="Z14">
-        <v>40</v>
-      </c>
-      <c r="AA14">
-        <v>46</v>
-      </c>
-      <c r="AB14">
-        <v>55</v>
-      </c>
-      <c r="AC14">
-        <v>22</v>
-      </c>
-      <c r="AD14">
-        <v>19</v>
-      </c>
-      <c r="AE14">
-        <v>25</v>
-      </c>
-      <c r="AF14">
-        <v>50</v>
-      </c>
-      <c r="AG14">
-        <v>22</v>
-      </c>
-      <c r="AH14">
-        <v>17.5</v>
-      </c>
-      <c r="AI14">
-        <v>24</v>
-      </c>
-      <c r="AJ14">
-        <v>65</v>
-      </c>
-      <c r="AK14">
-        <v>32</v>
-      </c>
-      <c r="AL14">
-        <v>28</v>
-      </c>
-      <c r="AM14">
-        <v>34</v>
-      </c>
-      <c r="AN14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO14">
-        <v>6.8</v>
-      </c>
-      <c r="AP14">
-        <v>55</v>
-      </c>
-      <c r="AQ14">
-        <v>26</v>
-      </c>
-      <c r="AR14">
-        <v>23</v>
-      </c>
-      <c r="AS14">
-        <v>27</v>
-      </c>
-      <c r="AT14">
-        <v>30</v>
-      </c>
-      <c r="AU14">
-        <v>13</v>
-      </c>
-      <c r="AV14">
+      <c r="BY14">
+        <v>16.5</v>
+      </c>
+      <c r="BZ14">
         <v>11.5</v>
       </c>
-      <c r="AW14">
-        <v>14.5</v>
-      </c>
-      <c r="AX14">
-        <v>29</v>
-      </c>
-      <c r="AY14">
-        <v>13</v>
-      </c>
-      <c r="AZ14">
-        <v>10.5</v>
-      </c>
-      <c r="BA14">
-        <v>14</v>
-      </c>
-      <c r="BB14">
-        <v>38</v>
-      </c>
-      <c r="BC14">
-        <v>19</v>
-      </c>
-      <c r="BD14">
-        <v>16</v>
-      </c>
-      <c r="BE14">
-        <v>20</v>
-      </c>
-      <c r="BF14">
-        <v>6</v>
-      </c>
-      <c r="BG14">
-        <v>4.3</v>
-      </c>
-      <c r="BH14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BI14">
-        <v>5.7</v>
-      </c>
-      <c r="BJ14">
-        <v>9.4</v>
-      </c>
-      <c r="BK14">
-        <v>1.01</v>
-      </c>
-      <c r="BL14">
-        <v>44</v>
-      </c>
-      <c r="BM14">
-        <v>1.01</v>
-      </c>
-      <c r="BN14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BO14">
-        <v>6</v>
-      </c>
-      <c r="BP14">
-        <v>22</v>
-      </c>
-      <c r="BQ14">
-        <v>1.01</v>
-      </c>
-      <c r="BR14">
-        <v>21</v>
-      </c>
-      <c r="BS14">
-        <v>1.01</v>
-      </c>
-      <c r="BT14">
-        <v>8.6</v>
-      </c>
-      <c r="BU14">
-        <v>5.4</v>
-      </c>
-      <c r="BV14">
-        <v>16.5</v>
-      </c>
-      <c r="BW14">
-        <v>1.01</v>
-      </c>
-      <c r="BX14">
-        <v>18.5</v>
-      </c>
-      <c r="BY14">
-        <v>1.01</v>
-      </c>
-      <c r="BZ14">
-        <v>0</v>
-      </c>
       <c r="CA14">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="CB14" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4209,241 +4158,241 @@
         <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="F15">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H15">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="I15">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="J15">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P15">
-        <v>1.24</v>
+        <v>2.96</v>
       </c>
       <c r="Q15">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4451,16 +4400,16 @@
         <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F16">
         <v>1.74</v>
@@ -4481,16 +4430,16 @@
         <v>4.7</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P16">
         <v>2.48</v>
@@ -4499,193 +4448,193 @@
         <v>1.57</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4693,34 +4642,34 @@
         <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="F17">
-        <v>4.5</v>
+        <v>2.56</v>
       </c>
       <c r="G17">
-        <v>6.2</v>
+        <v>2.92</v>
       </c>
       <c r="H17">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="I17">
-        <v>1.87</v>
+        <v>3.2</v>
       </c>
       <c r="J17">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="K17">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4735,10 +4684,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>3.4</v>
+        <v>1.96</v>
       </c>
       <c r="Q17">
-        <v>1.34</v>
+        <v>1.82</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4927,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4935,34 +4884,34 @@
         <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="F18">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4977,10 +4926,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="Q18">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5169,1701 +5118,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="19" spans="1:80">
-      <c r="A19" t="s">
-        <v>93</v>
-      </c>
-      <c r="B19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" t="s">
-        <v>124</v>
-      </c>
-      <c r="E19" t="s">
-        <v>148</v>
-      </c>
-      <c r="F19">
-        <v>2.66</v>
-      </c>
-      <c r="G19">
-        <v>2.9</v>
-      </c>
-      <c r="H19">
-        <v>2.72</v>
-      </c>
-      <c r="I19">
-        <v>3</v>
-      </c>
-      <c r="J19">
-        <v>3.25</v>
-      </c>
-      <c r="K19">
-        <v>3.65</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>1.84</v>
-      </c>
-      <c r="Q19">
-        <v>2.02</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19">
-        <v>0</v>
-      </c>
-      <c r="AI19">
-        <v>0</v>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>0</v>
-      </c>
-      <c r="AO19">
-        <v>0</v>
-      </c>
-      <c r="AP19">
-        <v>0</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19">
-        <v>0</v>
-      </c>
-      <c r="AV19">
-        <v>0</v>
-      </c>
-      <c r="AW19">
-        <v>0</v>
-      </c>
-      <c r="AX19">
-        <v>0</v>
-      </c>
-      <c r="AY19">
-        <v>0</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>0</v>
-      </c>
-      <c r="BC19">
-        <v>0</v>
-      </c>
-      <c r="BD19">
-        <v>0</v>
-      </c>
-      <c r="BE19">
-        <v>0</v>
-      </c>
-      <c r="BF19">
-        <v>0</v>
-      </c>
-      <c r="BG19">
-        <v>0</v>
-      </c>
-      <c r="BH19">
-        <v>0</v>
-      </c>
-      <c r="BI19">
-        <v>0</v>
-      </c>
-      <c r="BJ19">
-        <v>0</v>
-      </c>
-      <c r="BK19">
-        <v>0</v>
-      </c>
-      <c r="BL19">
-        <v>0</v>
-      </c>
-      <c r="BM19">
-        <v>0</v>
-      </c>
-      <c r="BN19">
-        <v>0</v>
-      </c>
-      <c r="BO19">
-        <v>0</v>
-      </c>
-      <c r="BP19">
-        <v>0</v>
-      </c>
-      <c r="BQ19">
-        <v>0</v>
-      </c>
-      <c r="BR19">
-        <v>0</v>
-      </c>
-      <c r="BS19">
-        <v>0</v>
-      </c>
-      <c r="BT19">
-        <v>0</v>
-      </c>
-      <c r="BU19">
-        <v>0</v>
-      </c>
-      <c r="BV19">
-        <v>0</v>
-      </c>
-      <c r="BW19">
-        <v>0</v>
-      </c>
-      <c r="BX19">
-        <v>0</v>
-      </c>
-      <c r="BY19">
-        <v>0</v>
-      </c>
-      <c r="BZ19">
-        <v>0</v>
-      </c>
-      <c r="CA19">
-        <v>0</v>
-      </c>
-      <c r="CB19" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="20" spans="1:80">
-      <c r="A20" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" t="s">
-        <v>125</v>
-      </c>
-      <c r="E20" t="s">
-        <v>149</v>
-      </c>
-      <c r="F20">
-        <v>1.82</v>
-      </c>
-      <c r="G20">
-        <v>1.89</v>
-      </c>
-      <c r="H20">
-        <v>4.7</v>
-      </c>
-      <c r="I20">
-        <v>5.3</v>
-      </c>
-      <c r="J20">
-        <v>3.75</v>
-      </c>
-      <c r="K20">
-        <v>4.1</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>2</v>
-      </c>
-      <c r="Q20">
-        <v>1.72</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20">
-        <v>0</v>
-      </c>
-      <c r="AI20">
-        <v>0</v>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>0</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>0</v>
-      </c>
-      <c r="AO20">
-        <v>0</v>
-      </c>
-      <c r="AP20">
-        <v>0</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20">
-        <v>0</v>
-      </c>
-      <c r="AV20">
-        <v>0</v>
-      </c>
-      <c r="AW20">
-        <v>0</v>
-      </c>
-      <c r="AX20">
-        <v>0</v>
-      </c>
-      <c r="AY20">
-        <v>0</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>0</v>
-      </c>
-      <c r="BC20">
-        <v>0</v>
-      </c>
-      <c r="BD20">
-        <v>0</v>
-      </c>
-      <c r="BE20">
-        <v>0</v>
-      </c>
-      <c r="BF20">
-        <v>0</v>
-      </c>
-      <c r="BG20">
-        <v>0</v>
-      </c>
-      <c r="BH20">
-        <v>0</v>
-      </c>
-      <c r="BI20">
-        <v>0</v>
-      </c>
-      <c r="BJ20">
-        <v>0</v>
-      </c>
-      <c r="BK20">
-        <v>0</v>
-      </c>
-      <c r="BL20">
-        <v>0</v>
-      </c>
-      <c r="BM20">
-        <v>0</v>
-      </c>
-      <c r="BN20">
-        <v>0</v>
-      </c>
-      <c r="BO20">
-        <v>0</v>
-      </c>
-      <c r="BP20">
-        <v>0</v>
-      </c>
-      <c r="BQ20">
-        <v>0</v>
-      </c>
-      <c r="BR20">
-        <v>0</v>
-      </c>
-      <c r="BS20">
-        <v>0</v>
-      </c>
-      <c r="BT20">
-        <v>0</v>
-      </c>
-      <c r="BU20">
-        <v>0</v>
-      </c>
-      <c r="BV20">
-        <v>0</v>
-      </c>
-      <c r="BW20">
-        <v>0</v>
-      </c>
-      <c r="BX20">
-        <v>0</v>
-      </c>
-      <c r="BY20">
-        <v>0</v>
-      </c>
-      <c r="BZ20">
-        <v>0</v>
-      </c>
-      <c r="CA20">
-        <v>0</v>
-      </c>
-      <c r="CB20" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="21" spans="1:80">
-      <c r="A21" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" t="s">
-        <v>126</v>
-      </c>
-      <c r="E21" t="s">
-        <v>150</v>
-      </c>
-      <c r="F21">
-        <v>2.58</v>
-      </c>
-      <c r="G21">
-        <v>3.05</v>
-      </c>
-      <c r="H21">
-        <v>2.58</v>
-      </c>
-      <c r="I21">
-        <v>2.96</v>
-      </c>
-      <c r="J21">
-        <v>3.55</v>
-      </c>
-      <c r="K21">
-        <v>4.1</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>2.12</v>
-      </c>
-      <c r="Q21">
-        <v>1.74</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>0</v>
-      </c>
-      <c r="AO21">
-        <v>0</v>
-      </c>
-      <c r="AP21">
-        <v>0</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21">
-        <v>0</v>
-      </c>
-      <c r="AV21">
-        <v>0</v>
-      </c>
-      <c r="AW21">
-        <v>0</v>
-      </c>
-      <c r="AX21">
-        <v>0</v>
-      </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>0</v>
-      </c>
-      <c r="BC21">
-        <v>0</v>
-      </c>
-      <c r="BD21">
-        <v>0</v>
-      </c>
-      <c r="BE21">
-        <v>0</v>
-      </c>
-      <c r="BF21">
-        <v>0</v>
-      </c>
-      <c r="BG21">
-        <v>0</v>
-      </c>
-      <c r="BH21">
-        <v>0</v>
-      </c>
-      <c r="BI21">
-        <v>0</v>
-      </c>
-      <c r="BJ21">
-        <v>0</v>
-      </c>
-      <c r="BK21">
-        <v>0</v>
-      </c>
-      <c r="BL21">
-        <v>0</v>
-      </c>
-      <c r="BM21">
-        <v>0</v>
-      </c>
-      <c r="BN21">
-        <v>0</v>
-      </c>
-      <c r="BO21">
-        <v>0</v>
-      </c>
-      <c r="BP21">
-        <v>0</v>
-      </c>
-      <c r="BQ21">
-        <v>0</v>
-      </c>
-      <c r="BR21">
-        <v>0</v>
-      </c>
-      <c r="BS21">
-        <v>0</v>
-      </c>
-      <c r="BT21">
-        <v>0</v>
-      </c>
-      <c r="BU21">
-        <v>0</v>
-      </c>
-      <c r="BV21">
-        <v>0</v>
-      </c>
-      <c r="BW21">
-        <v>0</v>
-      </c>
-      <c r="BX21">
-        <v>0</v>
-      </c>
-      <c r="BY21">
-        <v>0</v>
-      </c>
-      <c r="BZ21">
-        <v>0</v>
-      </c>
-      <c r="CA21">
-        <v>0</v>
-      </c>
-      <c r="CB21" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="22" spans="1:80">
-      <c r="A22" t="s">
-        <v>93</v>
-      </c>
-      <c r="B22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22" t="s">
-        <v>151</v>
-      </c>
-      <c r="F22">
-        <v>2</v>
-      </c>
-      <c r="G22">
-        <v>2.12</v>
-      </c>
-      <c r="H22">
-        <v>3.6</v>
-      </c>
-      <c r="I22">
-        <v>4.1</v>
-      </c>
-      <c r="J22">
-        <v>3.95</v>
-      </c>
-      <c r="K22">
-        <v>4.3</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>2.2</v>
-      </c>
-      <c r="Q22">
-        <v>1.68</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-      <c r="AG22">
-        <v>0</v>
-      </c>
-      <c r="AH22">
-        <v>0</v>
-      </c>
-      <c r="AI22">
-        <v>0</v>
-      </c>
-      <c r="AJ22">
-        <v>0</v>
-      </c>
-      <c r="AK22">
-        <v>0</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>0</v>
-      </c>
-      <c r="AN22">
-        <v>0</v>
-      </c>
-      <c r="AO22">
-        <v>0</v>
-      </c>
-      <c r="AP22">
-        <v>0</v>
-      </c>
-      <c r="AQ22">
-        <v>0</v>
-      </c>
-      <c r="AR22">
-        <v>0</v>
-      </c>
-      <c r="AS22">
-        <v>0</v>
-      </c>
-      <c r="AT22">
-        <v>0</v>
-      </c>
-      <c r="AU22">
-        <v>0</v>
-      </c>
-      <c r="AV22">
-        <v>0</v>
-      </c>
-      <c r="AW22">
-        <v>0</v>
-      </c>
-      <c r="AX22">
-        <v>0</v>
-      </c>
-      <c r="AY22">
-        <v>0</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>0</v>
-      </c>
-      <c r="BC22">
-        <v>0</v>
-      </c>
-      <c r="BD22">
-        <v>0</v>
-      </c>
-      <c r="BE22">
-        <v>0</v>
-      </c>
-      <c r="BF22">
-        <v>0</v>
-      </c>
-      <c r="BG22">
-        <v>0</v>
-      </c>
-      <c r="BH22">
-        <v>0</v>
-      </c>
-      <c r="BI22">
-        <v>0</v>
-      </c>
-      <c r="BJ22">
-        <v>0</v>
-      </c>
-      <c r="BK22">
-        <v>0</v>
-      </c>
-      <c r="BL22">
-        <v>0</v>
-      </c>
-      <c r="BM22">
-        <v>0</v>
-      </c>
-      <c r="BN22">
-        <v>0</v>
-      </c>
-      <c r="BO22">
-        <v>0</v>
-      </c>
-      <c r="BP22">
-        <v>0</v>
-      </c>
-      <c r="BQ22">
-        <v>0</v>
-      </c>
-      <c r="BR22">
-        <v>0</v>
-      </c>
-      <c r="BS22">
-        <v>0</v>
-      </c>
-      <c r="BT22">
-        <v>0</v>
-      </c>
-      <c r="BU22">
-        <v>0</v>
-      </c>
-      <c r="BV22">
-        <v>0</v>
-      </c>
-      <c r="BW22">
-        <v>0</v>
-      </c>
-      <c r="BX22">
-        <v>0</v>
-      </c>
-      <c r="BY22">
-        <v>0</v>
-      </c>
-      <c r="BZ22">
-        <v>0</v>
-      </c>
-      <c r="CA22">
-        <v>0</v>
-      </c>
-      <c r="CB22" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="23" spans="1:80">
-      <c r="A23" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" t="s">
-        <v>105</v>
-      </c>
-      <c r="D23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" t="s">
-        <v>152</v>
-      </c>
-      <c r="F23">
-        <v>2.06</v>
-      </c>
-      <c r="G23">
-        <v>2.16</v>
-      </c>
-      <c r="H23">
-        <v>3.8</v>
-      </c>
-      <c r="I23">
-        <v>4</v>
-      </c>
-      <c r="J23">
-        <v>3.6</v>
-      </c>
-      <c r="K23">
-        <v>3.85</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>1.9</v>
-      </c>
-      <c r="Q23">
-        <v>1.91</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>0</v>
-      </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AH23">
-        <v>0</v>
-      </c>
-      <c r="AI23">
-        <v>0</v>
-      </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
-      <c r="AK23">
-        <v>0</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>0</v>
-      </c>
-      <c r="AO23">
-        <v>0</v>
-      </c>
-      <c r="AP23">
-        <v>0</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23">
-        <v>0</v>
-      </c>
-      <c r="AV23">
-        <v>0</v>
-      </c>
-      <c r="AW23">
-        <v>0</v>
-      </c>
-      <c r="AX23">
-        <v>0</v>
-      </c>
-      <c r="AY23">
-        <v>0</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>0</v>
-      </c>
-      <c r="BB23">
-        <v>0</v>
-      </c>
-      <c r="BC23">
-        <v>0</v>
-      </c>
-      <c r="BD23">
-        <v>0</v>
-      </c>
-      <c r="BE23">
-        <v>0</v>
-      </c>
-      <c r="BF23">
-        <v>0</v>
-      </c>
-      <c r="BG23">
-        <v>0</v>
-      </c>
-      <c r="BH23">
-        <v>0</v>
-      </c>
-      <c r="BI23">
-        <v>0</v>
-      </c>
-      <c r="BJ23">
-        <v>0</v>
-      </c>
-      <c r="BK23">
-        <v>0</v>
-      </c>
-      <c r="BL23">
-        <v>0</v>
-      </c>
-      <c r="BM23">
-        <v>0</v>
-      </c>
-      <c r="BN23">
-        <v>0</v>
-      </c>
-      <c r="BO23">
-        <v>0</v>
-      </c>
-      <c r="BP23">
-        <v>0</v>
-      </c>
-      <c r="BQ23">
-        <v>0</v>
-      </c>
-      <c r="BR23">
-        <v>0</v>
-      </c>
-      <c r="BS23">
-        <v>0</v>
-      </c>
-      <c r="BT23">
-        <v>0</v>
-      </c>
-      <c r="BU23">
-        <v>0</v>
-      </c>
-      <c r="BV23">
-        <v>0</v>
-      </c>
-      <c r="BW23">
-        <v>0</v>
-      </c>
-      <c r="BX23">
-        <v>0</v>
-      </c>
-      <c r="BY23">
-        <v>0</v>
-      </c>
-      <c r="BZ23">
-        <v>0</v>
-      </c>
-      <c r="CA23">
-        <v>0</v>
-      </c>
-      <c r="CB23" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="24" spans="1:80">
-      <c r="A24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24" t="s">
-        <v>153</v>
-      </c>
-      <c r="F24">
-        <v>2.54</v>
-      </c>
-      <c r="G24">
-        <v>2.92</v>
-      </c>
-      <c r="H24">
-        <v>2.7</v>
-      </c>
-      <c r="I24">
-        <v>3.1</v>
-      </c>
-      <c r="J24">
-        <v>3.4</v>
-      </c>
-      <c r="K24">
-        <v>3.85</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>1.89</v>
-      </c>
-      <c r="Q24">
-        <v>1.77</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24">
-        <v>0</v>
-      </c>
-      <c r="Z24">
-        <v>0</v>
-      </c>
-      <c r="AA24">
-        <v>0</v>
-      </c>
-      <c r="AB24">
-        <v>0</v>
-      </c>
-      <c r="AC24">
-        <v>0</v>
-      </c>
-      <c r="AD24">
-        <v>0</v>
-      </c>
-      <c r="AE24">
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <v>0</v>
-      </c>
-      <c r="AG24">
-        <v>0</v>
-      </c>
-      <c r="AH24">
-        <v>0</v>
-      </c>
-      <c r="AI24">
-        <v>0</v>
-      </c>
-      <c r="AJ24">
-        <v>0</v>
-      </c>
-      <c r="AK24">
-        <v>0</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>0</v>
-      </c>
-      <c r="AN24">
-        <v>0</v>
-      </c>
-      <c r="AO24">
-        <v>0</v>
-      </c>
-      <c r="AP24">
-        <v>0</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24">
-        <v>0</v>
-      </c>
-      <c r="AV24">
-        <v>0</v>
-      </c>
-      <c r="AW24">
-        <v>0</v>
-      </c>
-      <c r="AX24">
-        <v>0</v>
-      </c>
-      <c r="AY24">
-        <v>0</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>0</v>
-      </c>
-      <c r="BC24">
-        <v>0</v>
-      </c>
-      <c r="BD24">
-        <v>0</v>
-      </c>
-      <c r="BE24">
-        <v>0</v>
-      </c>
-      <c r="BF24">
-        <v>0</v>
-      </c>
-      <c r="BG24">
-        <v>0</v>
-      </c>
-      <c r="BH24">
-        <v>0</v>
-      </c>
-      <c r="BI24">
-        <v>0</v>
-      </c>
-      <c r="BJ24">
-        <v>0</v>
-      </c>
-      <c r="BK24">
-        <v>0</v>
-      </c>
-      <c r="BL24">
-        <v>0</v>
-      </c>
-      <c r="BM24">
-        <v>0</v>
-      </c>
-      <c r="BN24">
-        <v>0</v>
-      </c>
-      <c r="BO24">
-        <v>0</v>
-      </c>
-      <c r="BP24">
-        <v>0</v>
-      </c>
-      <c r="BQ24">
-        <v>0</v>
-      </c>
-      <c r="BR24">
-        <v>0</v>
-      </c>
-      <c r="BS24">
-        <v>0</v>
-      </c>
-      <c r="BT24">
-        <v>0</v>
-      </c>
-      <c r="BU24">
-        <v>0</v>
-      </c>
-      <c r="BV24">
-        <v>0</v>
-      </c>
-      <c r="BW24">
-        <v>0</v>
-      </c>
-      <c r="BX24">
-        <v>0</v>
-      </c>
-      <c r="BY24">
-        <v>0</v>
-      </c>
-      <c r="BZ24">
-        <v>0</v>
-      </c>
-      <c r="CA24">
-        <v>0</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="25" spans="1:80">
-      <c r="A25" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" t="s">
-        <v>130</v>
-      </c>
-      <c r="E25" t="s">
-        <v>154</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>1.24</v>
-      </c>
-      <c r="Q25">
-        <v>1.01</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25">
-        <v>0</v>
-      </c>
-      <c r="AI25">
-        <v>0</v>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>0</v>
-      </c>
-      <c r="AO25">
-        <v>0</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>0</v>
-      </c>
-      <c r="BC25">
-        <v>0</v>
-      </c>
-      <c r="BD25">
-        <v>0</v>
-      </c>
-      <c r="BE25">
-        <v>0</v>
-      </c>
-      <c r="BF25">
-        <v>0</v>
-      </c>
-      <c r="BG25">
-        <v>0</v>
-      </c>
-      <c r="BH25">
-        <v>0</v>
-      </c>
-      <c r="BI25">
-        <v>0</v>
-      </c>
-      <c r="BJ25">
-        <v>0</v>
-      </c>
-      <c r="BK25">
-        <v>0</v>
-      </c>
-      <c r="BL25">
-        <v>0</v>
-      </c>
-      <c r="BM25">
-        <v>0</v>
-      </c>
-      <c r="BN25">
-        <v>0</v>
-      </c>
-      <c r="BO25">
-        <v>0</v>
-      </c>
-      <c r="BP25">
-        <v>0</v>
-      </c>
-      <c r="BQ25">
-        <v>0</v>
-      </c>
-      <c r="BR25">
-        <v>0</v>
-      </c>
-      <c r="BS25">
-        <v>0</v>
-      </c>
-      <c r="BT25">
-        <v>0</v>
-      </c>
-      <c r="BU25">
-        <v>0</v>
-      </c>
-      <c r="BV25">
-        <v>0</v>
-      </c>
-      <c r="BW25">
-        <v>0</v>
-      </c>
-      <c r="BX25">
-        <v>0</v>
-      </c>
-      <c r="BY25">
-        <v>0</v>
-      </c>
-      <c r="BZ25">
-        <v>0</v>
-      </c>
-      <c r="CA25">
-        <v>0</v>
-      </c>
-      <c r="CB25" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
@@ -715,7 +715,7 @@
     <t>Juventude</t>
   </si>
   <si>
-    <t>2026-08-31 19:44:46</t>
+    <t>2026-08-31 21:58:10</t>
   </si>
 </sst>
 </file>
@@ -1309,226 +1309,226 @@
         <v>180</v>
       </c>
       <c r="F2">
-        <v>2.14</v>
+        <v>2.66</v>
       </c>
       <c r="G2">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="I2">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>2.34</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>2.42</v>
       </c>
       <c r="L2">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="N2">
-        <v>3.55</v>
+        <v>1.5</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>2.9</v>
       </c>
       <c r="P2">
-        <v>1.85</v>
+        <v>1.12</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R2">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
+        <v>29</v>
       </c>
       <c r="T2">
-        <v>1.81</v>
+        <v>4.1</v>
       </c>
       <c r="U2">
-        <v>2.04</v>
+        <v>1.23</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>3.45</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="Z2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA2">
-        <v>110</v>
+        <v>310</v>
       </c>
       <c r="AB2">
-        <v>9.4</v>
+        <v>4.8</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD2">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>410</v>
       </c>
       <c r="AF2">
         <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="AH2">
-        <v>19.5</v>
+        <v>150</v>
       </c>
       <c r="AI2">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="AK2">
+        <v>170</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>300</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>3.3</v>
+      </c>
+      <c r="AQ2">
+        <v>6.8</v>
+      </c>
+      <c r="AR2">
+        <v>25</v>
+      </c>
+      <c r="AS2">
+        <v>14</v>
+      </c>
+      <c r="AT2">
+        <v>4.4</v>
+      </c>
+      <c r="AU2">
+        <v>8</v>
+      </c>
+      <c r="AV2">
         <v>26</v>
       </c>
-      <c r="AL2">
-        <v>42</v>
-      </c>
-      <c r="AM2">
-        <v>360</v>
-      </c>
-      <c r="AN2">
-        <v>20</v>
-      </c>
-      <c r="AO2">
-        <v>55</v>
-      </c>
-      <c r="AP2">
-        <v>10.5</v>
-      </c>
-      <c r="AQ2">
-        <v>11</v>
-      </c>
-      <c r="AR2">
-        <v>20</v>
-      </c>
-      <c r="AS2">
-        <v>48</v>
-      </c>
-      <c r="AT2">
-        <v>7.8</v>
-      </c>
-      <c r="AU2">
-        <v>7</v>
-      </c>
-      <c r="AV2">
-        <v>13</v>
-      </c>
       <c r="AW2">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="AX2">
         <v>12</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="AZ2">
-        <v>16.5</v>
+        <v>50</v>
       </c>
       <c r="BA2">
+        <v>170</v>
+      </c>
+      <c r="BB2">
         <v>46</v>
       </c>
-      <c r="BB2">
-        <v>24</v>
-      </c>
       <c r="BC2">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="BD2">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="BE2">
-        <v>80</v>
+        <v>430</v>
       </c>
       <c r="BF2">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>233</v>
@@ -1551,226 +1551,226 @@
         <v>181</v>
       </c>
       <c r="F3">
-        <v>1.92</v>
+        <v>2.62</v>
       </c>
       <c r="G3">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="L3">
-        <v>1.71</v>
+        <v>5.5</v>
       </c>
       <c r="M3">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="N3">
-        <v>2.34</v>
+        <v>1.51</v>
       </c>
       <c r="O3">
-        <v>1.71</v>
+        <v>2.88</v>
       </c>
       <c r="P3">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="Q3">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R3">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="S3">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="T3">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="U3">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="V3">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
-        <v>2.04</v>
+        <v>1.58</v>
       </c>
       <c r="X3">
-        <v>7.2</v>
+        <v>3.45</v>
       </c>
       <c r="Y3">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA3">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="AB3">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AE3">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="AF3">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AG3">
+        <v>26</v>
+      </c>
+      <c r="AH3">
+        <v>130</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>570</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>190</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>3.3</v>
+      </c>
+      <c r="AQ3">
+        <v>7.6</v>
+      </c>
+      <c r="AR3">
+        <v>30</v>
+      </c>
+      <c r="AS3">
+        <v>12</v>
+      </c>
+      <c r="AT3">
+        <v>4.2</v>
+      </c>
+      <c r="AU3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW3">
+        <v>12</v>
+      </c>
+      <c r="AX3">
+        <v>12</v>
+      </c>
+      <c r="AY3">
+        <v>21</v>
+      </c>
+      <c r="AZ3">
+        <v>75</v>
+      </c>
+      <c r="BA3">
+        <v>280</v>
+      </c>
+      <c r="BB3">
+        <v>48</v>
+      </c>
+      <c r="BC3">
+        <v>95</v>
+      </c>
+      <c r="BD3">
+        <v>12</v>
+      </c>
+      <c r="BE3">
         <v>12.5</v>
       </c>
-      <c r="AH3">
-        <v>36</v>
-      </c>
-      <c r="AI3">
-        <v>220</v>
-      </c>
-      <c r="AJ3">
-        <v>23</v>
-      </c>
-      <c r="AK3">
-        <v>32</v>
-      </c>
-      <c r="AL3">
-        <v>85</v>
-      </c>
-      <c r="AM3">
-        <v>440</v>
-      </c>
-      <c r="AN3">
-        <v>28</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>6.6</v>
-      </c>
-      <c r="AQ3">
-        <v>11</v>
-      </c>
-      <c r="AR3">
-        <v>38</v>
-      </c>
-      <c r="AS3">
-        <v>15</v>
-      </c>
-      <c r="AT3">
-        <v>5.1</v>
-      </c>
-      <c r="AU3">
-        <v>7.2</v>
-      </c>
-      <c r="AV3">
-        <v>24</v>
-      </c>
-      <c r="AW3">
-        <v>14.5</v>
-      </c>
-      <c r="AX3">
-        <v>8.4</v>
-      </c>
-      <c r="AY3">
-        <v>11</v>
-      </c>
-      <c r="AZ3">
-        <v>30</v>
-      </c>
-      <c r="BA3">
-        <v>14.5</v>
-      </c>
-      <c r="BB3">
-        <v>20</v>
-      </c>
-      <c r="BC3">
-        <v>27</v>
-      </c>
-      <c r="BD3">
-        <v>50</v>
-      </c>
-      <c r="BE3">
-        <v>15</v>
-      </c>
       <c r="BF3">
+        <v>110</v>
+      </c>
+      <c r="BG3">
+        <v>12.5</v>
+      </c>
+      <c r="BH3">
+        <v>1.25</v>
+      </c>
+      <c r="BI3">
+        <v>1.21</v>
+      </c>
+      <c r="BJ3">
+        <v>950</v>
+      </c>
+      <c r="BK3">
+        <v>13.5</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>14</v>
+      </c>
+      <c r="BN3">
+        <v>11.5</v>
+      </c>
+      <c r="BO3">
+        <v>9</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>14</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>14</v>
+      </c>
+      <c r="BT3">
         <v>26</v>
       </c>
-      <c r="BG3">
-        <v>15</v>
-      </c>
-      <c r="BH3">
-        <v>2.46</v>
-      </c>
-      <c r="BI3">
-        <v>2.3</v>
-      </c>
-      <c r="BJ3">
-        <v>16</v>
-      </c>
-      <c r="BK3">
-        <v>11.5</v>
-      </c>
-      <c r="BL3">
-        <v>400</v>
-      </c>
-      <c r="BM3">
-        <v>10.5</v>
-      </c>
-      <c r="BN3">
-        <v>4.2</v>
-      </c>
-      <c r="BO3">
-        <v>3.85</v>
-      </c>
-      <c r="BP3">
-        <v>19.5</v>
-      </c>
-      <c r="BQ3">
-        <v>12.5</v>
-      </c>
-      <c r="BR3">
-        <v>60</v>
-      </c>
-      <c r="BS3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT3">
-        <v>10.5</v>
-      </c>
       <c r="BU3">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BV3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="BX3">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BZ3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="CB3" t="s">
         <v>233</v>
@@ -1793,226 +1793,226 @@
         <v>182</v>
       </c>
       <c r="F4">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="G4">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="H4">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>3.25</v>
+        <v>2.48</v>
       </c>
       <c r="K4">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="L4">
-        <v>1.66</v>
+        <v>5.1</v>
       </c>
       <c r="M4">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="N4">
-        <v>2.48</v>
+        <v>1.56</v>
       </c>
       <c r="O4">
-        <v>1.66</v>
+        <v>2.74</v>
       </c>
       <c r="P4">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="Q4">
-        <v>3.05</v>
+        <v>7.6</v>
       </c>
       <c r="R4">
+        <v>1.03</v>
+      </c>
+      <c r="S4">
+        <v>28</v>
+      </c>
+      <c r="T4">
+        <v>4.4</v>
+      </c>
+      <c r="U4">
+        <v>1.25</v>
+      </c>
+      <c r="V4">
         <v>1.16</v>
       </c>
-      <c r="S4">
-        <v>6.8</v>
-      </c>
-      <c r="T4">
-        <v>2.54</v>
-      </c>
-      <c r="U4">
-        <v>1.61</v>
-      </c>
-      <c r="V4">
+      <c r="W4">
+        <v>1.87</v>
+      </c>
+      <c r="X4">
+        <v>3.7</v>
+      </c>
+      <c r="Y4">
+        <v>11</v>
+      </c>
+      <c r="Z4">
+        <v>80</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>4</v>
+      </c>
+      <c r="AC4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD4">
+        <v>70</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>9.6</v>
+      </c>
+      <c r="AG4">
+        <v>23</v>
+      </c>
+      <c r="AH4">
+        <v>130</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>40</v>
+      </c>
+      <c r="AK4">
+        <v>95</v>
+      </c>
+      <c r="AL4">
+        <v>550</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>110</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>3.6</v>
+      </c>
+      <c r="AQ4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR4">
+        <v>55</v>
+      </c>
+      <c r="AS4">
+        <v>360</v>
+      </c>
+      <c r="AT4">
+        <v>3.75</v>
+      </c>
+      <c r="AU4">
+        <v>9</v>
+      </c>
+      <c r="AV4">
+        <v>36</v>
+      </c>
+      <c r="AW4">
+        <v>20</v>
+      </c>
+      <c r="AX4">
+        <v>9</v>
+      </c>
+      <c r="AY4">
+        <v>19.5</v>
+      </c>
+      <c r="AZ4">
+        <v>85</v>
+      </c>
+      <c r="BA4">
+        <v>85</v>
+      </c>
+      <c r="BB4">
+        <v>30</v>
+      </c>
+      <c r="BC4">
+        <v>70</v>
+      </c>
+      <c r="BD4">
+        <v>300</v>
+      </c>
+      <c r="BE4">
+        <v>16.5</v>
+      </c>
+      <c r="BF4">
+        <v>60</v>
+      </c>
+      <c r="BG4">
+        <v>19</v>
+      </c>
+      <c r="BH4">
+        <v>1.27</v>
+      </c>
+      <c r="BI4">
         <v>1.22</v>
       </c>
-      <c r="W4">
-        <v>2.02</v>
-      </c>
-      <c r="X4">
-        <v>7.4</v>
-      </c>
-      <c r="Y4">
-        <v>12.5</v>
-      </c>
-      <c r="Z4">
-        <v>40</v>
-      </c>
-      <c r="AA4">
-        <v>200</v>
-      </c>
-      <c r="AB4">
-        <v>5.8</v>
-      </c>
-      <c r="AC4">
-        <v>7.8</v>
-      </c>
-      <c r="AD4">
+      <c r="BJ4">
+        <v>260</v>
+      </c>
+      <c r="BK4">
+        <v>42</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>17.5</v>
+      </c>
+      <c r="BN4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO4">
+        <v>7.6</v>
+      </c>
+      <c r="BP4">
+        <v>280</v>
+      </c>
+      <c r="BQ4">
+        <v>55</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>17.5</v>
+      </c>
+      <c r="BT4">
         <v>25</v>
       </c>
-      <c r="AE4">
-        <v>130</v>
-      </c>
-      <c r="AF4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG4">
-        <v>11.5</v>
-      </c>
-      <c r="AH4">
-        <v>32</v>
-      </c>
-      <c r="AI4">
-        <v>190</v>
-      </c>
-      <c r="AJ4">
-        <v>23</v>
-      </c>
-      <c r="AK4">
-        <v>29</v>
-      </c>
-      <c r="AL4">
-        <v>75</v>
-      </c>
-      <c r="AM4">
-        <v>400</v>
-      </c>
-      <c r="AN4">
-        <v>28</v>
-      </c>
-      <c r="AO4">
-        <v>310</v>
-      </c>
-      <c r="AP4">
-        <v>7</v>
-      </c>
-      <c r="AQ4">
-        <v>11.5</v>
-      </c>
-      <c r="AR4">
-        <v>34</v>
-      </c>
-      <c r="AS4">
-        <v>44</v>
-      </c>
-      <c r="AT4">
-        <v>5.5</v>
-      </c>
-      <c r="AU4">
-        <v>7.2</v>
-      </c>
-      <c r="AV4">
-        <v>22</v>
-      </c>
-      <c r="AW4">
-        <v>100</v>
-      </c>
-      <c r="AX4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY4">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4">
-        <v>29</v>
-      </c>
-      <c r="BA4">
-        <v>46</v>
-      </c>
-      <c r="BB4">
-        <v>22</v>
-      </c>
-      <c r="BC4">
-        <v>27</v>
-      </c>
-      <c r="BD4">
-        <v>65</v>
-      </c>
-      <c r="BE4">
-        <v>85</v>
-      </c>
-      <c r="BF4">
-        <v>24</v>
-      </c>
-      <c r="BG4">
-        <v>95</v>
-      </c>
-      <c r="BH4">
-        <v>2.52</v>
-      </c>
-      <c r="BI4">
-        <v>2.38</v>
-      </c>
-      <c r="BJ4">
-        <v>13.5</v>
-      </c>
-      <c r="BK4">
+      <c r="BU4">
         <v>11</v>
       </c>
-      <c r="BL4">
-        <v>350</v>
-      </c>
-      <c r="BM4">
-        <v>10</v>
-      </c>
-      <c r="BN4">
-        <v>4.4</v>
-      </c>
-      <c r="BO4">
-        <v>3.9</v>
-      </c>
-      <c r="BP4">
-        <v>20</v>
-      </c>
-      <c r="BQ4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR4">
-        <v>60</v>
-      </c>
-      <c r="BS4">
-        <v>8.6</v>
-      </c>
-      <c r="BT4">
-        <v>10.5</v>
-      </c>
-      <c r="BU4">
-        <v>7.8</v>
-      </c>
       <c r="BV4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BX4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.4</v>
+        <v>17.5</v>
       </c>
       <c r="BZ4">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="CB4" t="s">
         <v>233</v>
@@ -2035,139 +2035,139 @@
         <v>183</v>
       </c>
       <c r="F5">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="G5">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="H5">
+        <v>4.7</v>
+      </c>
+      <c r="I5">
         <v>4.8</v>
       </c>
-      <c r="I5">
-        <v>5.1</v>
-      </c>
       <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
         <v>4.1</v>
       </c>
-      <c r="K5">
+      <c r="L5">
+        <v>1.46</v>
+      </c>
+      <c r="M5">
+        <v>1.06</v>
+      </c>
+      <c r="N5">
         <v>4.3</v>
       </c>
-      <c r="L5">
-        <v>1.35</v>
-      </c>
-      <c r="M5">
-        <v>1.05</v>
-      </c>
-      <c r="N5">
-        <v>4.7</v>
-      </c>
       <c r="O5">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="P5">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q5">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="R5">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S5">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="T5">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="U5">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W5">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="X5">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Z5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA5">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AB5">
         <v>10.5</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AE5">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF5">
         <v>12</v>
       </c>
       <c r="AG5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI5">
         <v>60</v>
       </c>
       <c r="AJ5">
+        <v>21</v>
+      </c>
+      <c r="AK5">
         <v>19</v>
       </c>
-      <c r="AK5">
-        <v>17.5</v>
-      </c>
       <c r="AL5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM5">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AN5">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AO5">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AP5">
+        <v>15</v>
+      </c>
+      <c r="AQ5">
         <v>17</v>
       </c>
-      <c r="AQ5">
-        <v>18</v>
-      </c>
       <c r="AR5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AS5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AT5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AV5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW5">
         <v>50</v>
       </c>
       <c r="AX5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY5">
         <v>8.800000000000001</v>
@@ -2179,82 +2179,82 @@
         <v>50</v>
       </c>
       <c r="BB5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF5">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BH5">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BI5">
         <v>3.15</v>
       </c>
       <c r="BJ5">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
+        <v>8.6</v>
+      </c>
+      <c r="BL5">
+        <v>140</v>
+      </c>
+      <c r="BM5">
+        <v>12</v>
+      </c>
+      <c r="BN5">
+        <v>4.5</v>
+      </c>
+      <c r="BO5">
+        <v>4</v>
+      </c>
+      <c r="BP5">
+        <v>13.5</v>
+      </c>
+      <c r="BQ5">
+        <v>10.5</v>
+      </c>
+      <c r="BR5">
+        <v>36</v>
+      </c>
+      <c r="BS5">
+        <v>19.5</v>
+      </c>
+      <c r="BT5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU5">
         <v>7</v>
       </c>
-      <c r="BL5">
-        <v>130</v>
-      </c>
-      <c r="BM5">
+      <c r="BV5">
+        <v>44</v>
+      </c>
+      <c r="BW5">
+        <v>21</v>
+      </c>
+      <c r="BX5">
+        <v>55</v>
+      </c>
+      <c r="BY5">
+        <v>10</v>
+      </c>
+      <c r="BZ5">
+        <v>25</v>
+      </c>
+      <c r="CA5">
         <v>14.5</v>
-      </c>
-      <c r="BN5">
-        <v>4.6</v>
-      </c>
-      <c r="BO5">
-        <v>4.1</v>
-      </c>
-      <c r="BP5">
-        <v>11.5</v>
-      </c>
-      <c r="BQ5">
-        <v>10</v>
-      </c>
-      <c r="BR5">
-        <v>24</v>
-      </c>
-      <c r="BS5">
-        <v>9.6</v>
-      </c>
-      <c r="BT5">
-        <v>8.4</v>
-      </c>
-      <c r="BU5">
-        <v>7.4</v>
-      </c>
-      <c r="BV5">
-        <v>38</v>
-      </c>
-      <c r="BW5">
-        <v>11</v>
-      </c>
-      <c r="BX5">
-        <v>42</v>
-      </c>
-      <c r="BY5">
-        <v>11.5</v>
-      </c>
-      <c r="BZ5">
-        <v>18</v>
-      </c>
-      <c r="CA5">
-        <v>13.5</v>
       </c>
       <c r="CB5" t="s">
         <v>233</v>
@@ -2283,184 +2283,184 @@
         <v>1.5</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J6">
+        <v>4.4</v>
+      </c>
+      <c r="K6">
         <v>4.5</v>
       </c>
-      <c r="K6">
-        <v>4.6</v>
-      </c>
       <c r="L6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="P6">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q6">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="R6">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S6">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U6">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W6">
         <v>3</v>
       </c>
       <c r="X6">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z6">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AA6">
-        <v>310</v>
+        <v>400</v>
       </c>
       <c r="AB6">
+        <v>7</v>
+      </c>
+      <c r="AC6">
+        <v>10</v>
+      </c>
+      <c r="AD6">
+        <v>34</v>
+      </c>
+      <c r="AE6">
+        <v>180</v>
+      </c>
+      <c r="AF6">
+        <v>7.6</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+      <c r="AH6">
+        <v>30</v>
+      </c>
+      <c r="AI6">
+        <v>160</v>
+      </c>
+      <c r="AJ6">
+        <v>12.5</v>
+      </c>
+      <c r="AK6">
+        <v>18</v>
+      </c>
+      <c r="AL6">
+        <v>46</v>
+      </c>
+      <c r="AM6">
+        <v>220</v>
+      </c>
+      <c r="AN6">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC6">
-        <v>11.5</v>
-      </c>
-      <c r="AD6">
-        <v>40</v>
-      </c>
-      <c r="AE6">
-        <v>150</v>
-      </c>
-      <c r="AF6">
-        <v>8.4</v>
-      </c>
-      <c r="AG6">
-        <v>10.5</v>
-      </c>
-      <c r="AH6">
-        <v>27</v>
-      </c>
-      <c r="AI6">
-        <v>130</v>
-      </c>
-      <c r="AJ6">
-        <v>13</v>
-      </c>
-      <c r="AK6">
-        <v>17.5</v>
-      </c>
-      <c r="AL6">
-        <v>40</v>
-      </c>
-      <c r="AM6">
-        <v>170</v>
-      </c>
-      <c r="AN6">
-        <v>8</v>
-      </c>
       <c r="AO6">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="AP6">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6">
         <v>23</v>
       </c>
       <c r="AR6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AS6">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AT6">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU6">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV6">
+        <v>30</v>
+      </c>
+      <c r="AW6">
+        <v>90</v>
+      </c>
+      <c r="AX6">
+        <v>7</v>
+      </c>
+      <c r="AY6">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6">
         <v>27</v>
       </c>
-      <c r="AW6">
+      <c r="BA6">
         <v>75</v>
       </c>
-      <c r="AX6">
-        <v>7.4</v>
-      </c>
-      <c r="AY6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ6">
-        <v>24</v>
-      </c>
-      <c r="BA6">
-        <v>65</v>
-      </c>
       <c r="BB6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC6">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BD6">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BE6">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="BF6">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BG6">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="BH6">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="BI6">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="BJ6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK6">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BL6">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="BM6">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="BN6">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BO6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP6">
         <v>9.4</v>
@@ -2469,34 +2469,34 @@
         <v>6.8</v>
       </c>
       <c r="BR6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BS6">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BU6">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BV6">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="BW6">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BX6">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="BY6">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BZ6">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="CA6">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="s">
         <v>233</v>
@@ -2519,13 +2519,13 @@
         <v>185</v>
       </c>
       <c r="F7">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G7">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H7">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I7">
         <v>3.15</v>
@@ -2549,7 +2549,7 @@
         <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q7">
         <v>2.08</v>
@@ -2567,10 +2567,10 @@
         <v>2.04</v>
       </c>
       <c r="V7">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W7">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X7">
         <v>13</v>
@@ -2597,7 +2597,7 @@
         <v>38</v>
       </c>
       <c r="AF7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG7">
         <v>14</v>
@@ -2615,58 +2615,58 @@
         <v>34</v>
       </c>
       <c r="AL7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP7">
         <v>9.4</v>
       </c>
       <c r="AQ7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT7">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AU7">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
         <v>10</v>
       </c>
       <c r="AW7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX7">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="AY7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7">
         <v>13.5</v>
       </c>
       <c r="BA7">
+        <v>7</v>
+      </c>
+      <c r="BB7">
         <v>6.8</v>
       </c>
-      <c r="BB7">
-        <v>6.6</v>
-      </c>
       <c r="BC7">
-        <v>26</v>
+        <v>6.4</v>
       </c>
       <c r="BD7">
         <v>6.8</v>
@@ -2678,7 +2678,7 @@
         <v>6.4</v>
       </c>
       <c r="BG7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH7">
         <v>3.55</v>
@@ -2699,19 +2699,19 @@
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BO7">
         <v>4.8</v>
       </c>
       <c r="BP7">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BQ7">
         <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BS7">
         <v>1.01</v>
@@ -2723,10 +2723,10 @@
         <v>5.1</v>
       </c>
       <c r="BV7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX7">
         <v>40</v>
@@ -2761,169 +2761,169 @@
         <v>186</v>
       </c>
       <c r="F8">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G8">
+        <v>3.3</v>
+      </c>
+      <c r="H8">
         <v>3.15</v>
-      </c>
-      <c r="H8">
-        <v>3.2</v>
       </c>
       <c r="I8">
         <v>3.55</v>
       </c>
       <c r="J8">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="K8">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="L8">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.18</v>
       </c>
       <c r="N8">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="O8">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="P8">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
       </c>
       <c r="R8">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S8">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="T8">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="U8">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="V8">
         <v>1.39</v>
       </c>
       <c r="W8">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X8">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="Y8">
-        <v>8.4</v>
+        <v>500</v>
       </c>
       <c r="Z8">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AA8">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB8">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AC8">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AD8">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AE8">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF8">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AG8">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH8">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AI8">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ8">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AK8">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL8">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AM8">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AN8">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AO8">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP8">
-        <v>5.1</v>
+        <v>1.65</v>
       </c>
       <c r="AQ8">
-        <v>6.2</v>
+        <v>1.45</v>
       </c>
       <c r="AR8">
-        <v>17</v>
+        <v>1.56</v>
       </c>
       <c r="AS8">
-        <v>7</v>
+        <v>1.65</v>
       </c>
       <c r="AT8">
-        <v>5.7</v>
+        <v>1.61</v>
       </c>
       <c r="AU8">
-        <v>5.8</v>
+        <v>1.37</v>
       </c>
       <c r="AV8">
-        <v>14</v>
+        <v>1.56</v>
       </c>
       <c r="AW8">
-        <v>6.8</v>
+        <v>1.64</v>
       </c>
       <c r="AX8">
-        <v>12.5</v>
+        <v>1.63</v>
       </c>
       <c r="AY8">
-        <v>11</v>
+        <v>1.55</v>
       </c>
       <c r="AZ8">
-        <v>20</v>
+        <v>1.65</v>
       </c>
       <c r="BA8">
-        <v>7.2</v>
+        <v>1.65</v>
       </c>
       <c r="BB8">
-        <v>6.8</v>
+        <v>1.64</v>
       </c>
       <c r="BC8">
-        <v>6.8</v>
+        <v>1.64</v>
       </c>
       <c r="BD8">
-        <v>7.2</v>
+        <v>1.65</v>
       </c>
       <c r="BE8">
-        <v>7.4</v>
+        <v>1.65</v>
       </c>
       <c r="BF8">
-        <v>7</v>
+        <v>1.65</v>
       </c>
       <c r="BG8">
-        <v>7</v>
+        <v>1.65</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI8">
         <v>1.01</v>
@@ -3018,16 +3018,16 @@
         <v>2.94</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L9">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="M9">
         <v>1.14</v>
       </c>
       <c r="N9">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O9">
         <v>1.5</v>
@@ -3048,7 +3048,7 @@
         <v>2.22</v>
       </c>
       <c r="U9">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V9">
         <v>1.28</v>
@@ -3090,10 +3090,10 @@
         <v>32</v>
       </c>
       <c r="AI9">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ9">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK9">
         <v>85</v>
@@ -3102,13 +3102,13 @@
         <v>170</v>
       </c>
       <c r="AM9">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN9">
         <v>44</v>
       </c>
       <c r="AO9">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AP9">
         <v>6</v>
@@ -3120,7 +3120,7 @@
         <v>24</v>
       </c>
       <c r="AS9">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT9">
         <v>6</v>
@@ -3141,28 +3141,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA9">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB9">
         <v>5.1</v>
       </c>
       <c r="BC9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD9">
         <v>5.5</v>
       </c>
       <c r="BE9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF9">
         <v>5.2</v>
       </c>
       <c r="BG9">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3269,25 +3269,25 @@
         <v>1.12</v>
       </c>
       <c r="N10">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O10">
+        <v>1.55</v>
+      </c>
+      <c r="P10">
         <v>1.54</v>
       </c>
-      <c r="P10">
-        <v>1.5</v>
-      </c>
       <c r="Q10">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R10">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S10">
         <v>5.3</v>
       </c>
       <c r="T10">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U10">
         <v>1.75</v>
@@ -3296,22 +3296,22 @@
         <v>1.43</v>
       </c>
       <c r="W10">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X10">
         <v>10.5</v>
       </c>
       <c r="Y10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA10">
         <v>70</v>
       </c>
       <c r="AB10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10">
         <v>7.4</v>
@@ -3320,7 +3320,7 @@
         <v>15.5</v>
       </c>
       <c r="AE10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF10">
         <v>18.5</v>
@@ -3329,22 +3329,22 @@
         <v>14</v>
       </c>
       <c r="AH10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI10">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ10">
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL10">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM10">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AN10">
         <v>55</v>
@@ -3368,7 +3368,7 @@
         <v>7</v>
       </c>
       <c r="AU10">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="AV10">
         <v>12</v>
@@ -3386,13 +3386,13 @@
         <v>19.5</v>
       </c>
       <c r="BA10">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="BB10">
         <v>6.2</v>
       </c>
       <c r="BC10">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="BD10">
         <v>6.4</v>
@@ -3401,7 +3401,7 @@
         <v>6.8</v>
       </c>
       <c r="BF10">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG10">
         <v>6.2</v>
@@ -3487,115 +3487,115 @@
         <v>189</v>
       </c>
       <c r="F11">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="G11">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="H11">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="I11">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J11">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="K11">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L11">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N11">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="O11">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="P11">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q11">
         <v>2</v>
       </c>
       <c r="R11">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="S11">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V11">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W11">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="X11">
         <v>970</v>
       </c>
       <c r="Y11">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="Z11">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AA11">
         <v>900</v>
       </c>
       <c r="AB11">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AC11">
         <v>970</v>
       </c>
       <c r="AD11">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AE11">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AF11">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AG11">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AH11">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AI11">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="AJ11">
         <v>900</v>
       </c>
       <c r="AK11">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AL11">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP11">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ11">
         <v>1.01</v>
@@ -3649,61 +3649,61 @@
         <v>1.55</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11">
         <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM11">
         <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO11">
         <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ11">
         <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS11">
         <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU11">
         <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW11">
         <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY11">
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA11">
         <v>1.01</v>
@@ -3729,55 +3729,55 @@
         <v>190</v>
       </c>
       <c r="F12">
+        <v>2.26</v>
+      </c>
+      <c r="G12">
+        <v>2.56</v>
+      </c>
+      <c r="H12">
+        <v>3.2</v>
+      </c>
+      <c r="I12">
+        <v>3.7</v>
+      </c>
+      <c r="J12">
+        <v>3.25</v>
+      </c>
+      <c r="K12">
+        <v>3.65</v>
+      </c>
+      <c r="L12">
+        <v>1.36</v>
+      </c>
+      <c r="M12">
+        <v>1.08</v>
+      </c>
+      <c r="N12">
+        <v>3.2</v>
+      </c>
+      <c r="O12">
+        <v>1.34</v>
+      </c>
+      <c r="P12">
+        <v>1.67</v>
+      </c>
+      <c r="Q12">
         <v>2.1</v>
       </c>
-      <c r="G12">
-        <v>2.58</v>
-      </c>
-      <c r="H12">
-        <v>3</v>
-      </c>
-      <c r="I12">
-        <v>4.1</v>
-      </c>
-      <c r="J12">
-        <v>3</v>
-      </c>
-      <c r="K12">
-        <v>6.2</v>
-      </c>
-      <c r="L12">
+      <c r="R12">
+        <v>1.25</v>
+      </c>
+      <c r="S12">
+        <v>1.02</v>
+      </c>
+      <c r="T12">
+        <v>1.75</v>
+      </c>
+      <c r="U12">
+        <v>1.97</v>
+      </c>
+      <c r="V12">
         <v>1.37</v>
-      </c>
-      <c r="M12">
-        <v>1.05</v>
-      </c>
-      <c r="N12">
-        <v>2.56</v>
-      </c>
-      <c r="O12">
-        <v>1.05</v>
-      </c>
-      <c r="P12">
-        <v>1.6</v>
-      </c>
-      <c r="Q12">
-        <v>1.95</v>
-      </c>
-      <c r="R12">
-        <v>1.18</v>
-      </c>
-      <c r="S12">
-        <v>2.74</v>
-      </c>
-      <c r="T12">
-        <v>1.01</v>
-      </c>
-      <c r="U12">
-        <v>1.01</v>
-      </c>
-      <c r="V12">
-        <v>1.32</v>
       </c>
       <c r="W12">
         <v>1.64</v>
@@ -3828,7 +3828,7 @@
         <v>55</v>
       </c>
       <c r="AM12">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN12">
         <v>29</v>
@@ -3971,25 +3971,25 @@
         <v>191</v>
       </c>
       <c r="F13">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G13">
         <v>2.1</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I13">
         <v>5.2</v>
       </c>
       <c r="J13">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K13">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L13">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="M13">
         <v>1.1</v>
@@ -4001,22 +4001,22 @@
         <v>1.44</v>
       </c>
       <c r="P13">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q13">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R13">
         <v>1.23</v>
       </c>
       <c r="S13">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>2.02</v>
       </c>
       <c r="U13">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V13">
         <v>1.23</v>
@@ -4031,7 +4031,7 @@
         <v>14.5</v>
       </c>
       <c r="Z13">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AA13">
         <v>900</v>
@@ -4046,7 +4046,7 @@
         <v>21</v>
       </c>
       <c r="AE13">
-        <v>470</v>
+        <v>190</v>
       </c>
       <c r="AF13">
         <v>12</v>
@@ -4067,7 +4067,7 @@
         <v>29</v>
       </c>
       <c r="AL13">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM13">
         <v>580</v>
@@ -4076,49 +4076,49 @@
         <v>22</v>
       </c>
       <c r="AO13">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="AP13">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AQ13">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="AR13">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AS13">
         <v>7.8</v>
       </c>
       <c r="AT13">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU13">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV13">
         <v>5.9</v>
       </c>
       <c r="AW13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX13">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY13">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="BA13">
         <v>7.6</v>
       </c>
       <c r="BB13">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BC13">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BD13">
         <v>7.2</v>
@@ -4130,64 +4130,64 @@
         <v>6</v>
       </c>
       <c r="BG13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK13">
         <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM13">
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ13">
         <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS13">
         <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU13">
         <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW13">
         <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY13">
         <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA13">
         <v>1.01</v>
@@ -4225,13 +4225,13 @@
         <v>3.55</v>
       </c>
       <c r="J14">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K14">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L14">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M14">
         <v>1.06</v>
@@ -4240,34 +4240,34 @@
         <v>3.6</v>
       </c>
       <c r="O14">
+        <v>1.34</v>
+      </c>
+      <c r="P14">
+        <v>1.89</v>
+      </c>
+      <c r="Q14">
+        <v>2</v>
+      </c>
+      <c r="R14">
         <v>1.35</v>
-      </c>
-      <c r="P14">
-        <v>1.88</v>
-      </c>
-      <c r="Q14">
-        <v>2.02</v>
-      </c>
-      <c r="R14">
-        <v>1.34</v>
       </c>
       <c r="S14">
         <v>3.6</v>
       </c>
       <c r="T14">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U14">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V14">
         <v>1.39</v>
       </c>
       <c r="W14">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y14">
         <v>12.5</v>
@@ -4306,7 +4306,7 @@
         <v>75</v>
       </c>
       <c r="AK14">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL14">
         <v>150</v>
@@ -4330,7 +4330,7 @@
         <v>17</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT14">
         <v>7.2</v>
@@ -4342,7 +4342,7 @@
         <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX14">
         <v>13</v>
@@ -4354,7 +4354,7 @@
         <v>15</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB14">
         <v>14.5</v>
@@ -4363,10 +4363,10 @@
         <v>19.5</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF14">
         <v>16</v>
@@ -4378,10 +4378,10 @@
         <v>3.4</v>
       </c>
       <c r="BI14">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK14">
         <v>7.4</v>
@@ -4399,7 +4399,7 @@
         <v>4.5</v>
       </c>
       <c r="BP14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ14">
         <v>1.01</v>
@@ -4423,7 +4423,7 @@
         <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY14">
         <v>1.01</v>
@@ -4473,13 +4473,13 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="M15">
         <v>1.04</v>
       </c>
       <c r="N15">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O15">
         <v>1.2</v>
@@ -4494,16 +4494,16 @@
         <v>1.58</v>
       </c>
       <c r="S15">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T15">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="U15">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="V15">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="W15">
         <v>1.18</v>
@@ -4527,7 +4527,7 @@
         <v>13</v>
       </c>
       <c r="AD15">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE15">
         <v>18.5</v>
@@ -4536,7 +4536,7 @@
         <v>220</v>
       </c>
       <c r="AG15">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AH15">
         <v>23</v>
@@ -4551,7 +4551,7 @@
         <v>170</v>
       </c>
       <c r="AL15">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AM15">
         <v>500</v>
@@ -4596,13 +4596,13 @@
         <v>16.5</v>
       </c>
       <c r="BA15">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="BB15">
         <v>5</v>
       </c>
       <c r="BC15">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD15">
         <v>4.8</v>
@@ -4700,16 +4700,16 @@
         <v>2.24</v>
       </c>
       <c r="G16">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H16">
         <v>3.75</v>
       </c>
       <c r="I16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K16">
         <v>3.3</v>
@@ -4721,7 +4721,7 @@
         <v>1.12</v>
       </c>
       <c r="N16">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O16">
         <v>1.52</v>
@@ -4730,7 +4730,7 @@
         <v>1.56</v>
       </c>
       <c r="Q16">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="R16">
         <v>1.2</v>
@@ -4745,10 +4745,10 @@
         <v>1.8</v>
       </c>
       <c r="V16">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W16">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -4787,10 +4787,10 @@
         <v>200</v>
       </c>
       <c r="AJ16">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AK16">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="AL16">
         <v>70</v>
@@ -4841,7 +4841,7 @@
         <v>11</v>
       </c>
       <c r="BB16">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BC16">
         <v>27</v>
@@ -4942,7 +4942,7 @@
         <v>2.16</v>
       </c>
       <c r="G17">
-        <v>12</v>
+        <v>4.4</v>
       </c>
       <c r="H17">
         <v>1.86</v>
@@ -4963,13 +4963,13 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O17">
         <v>1.25</v>
       </c>
       <c r="P17">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="Q17">
         <v>1.25</v>
@@ -4978,7 +4978,7 @@
         <v>1.42</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -4990,7 +4990,7 @@
         <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X17">
         <v>500</v>
@@ -5002,13 +5002,13 @@
         <v>500</v>
       </c>
       <c r="AA17">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB17">
         <v>500</v>
       </c>
       <c r="AC17">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AD17">
         <v>970</v>
@@ -5029,7 +5029,7 @@
         <v>500</v>
       </c>
       <c r="AJ17">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK17">
         <v>500</v>
@@ -5098,7 +5098,7 @@
         <v>5.5</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5181,19 +5181,19 @@
         <v>196</v>
       </c>
       <c r="F18">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G18">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H18">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I18">
         <v>3.45</v>
       </c>
       <c r="J18">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K18">
         <v>4.1</v>
@@ -5220,22 +5220,22 @@
         <v>1.52</v>
       </c>
       <c r="S18">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="T18">
         <v>1.62</v>
       </c>
       <c r="U18">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V18">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
         <v>1.76</v>
       </c>
       <c r="X18">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Y18">
         <v>17</v>
@@ -5247,7 +5247,7 @@
         <v>60</v>
       </c>
       <c r="AB18">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC18">
         <v>9.6</v>
@@ -5259,7 +5259,7 @@
         <v>36</v>
       </c>
       <c r="AF18">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AG18">
         <v>12</v>
@@ -5274,7 +5274,7 @@
         <v>30</v>
       </c>
       <c r="AK18">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL18">
         <v>32</v>
@@ -5295,10 +5295,10 @@
         <v>14</v>
       </c>
       <c r="AR18">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AT18">
         <v>10.5</v>
@@ -5310,7 +5310,7 @@
         <v>12</v>
       </c>
       <c r="AW18">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AX18">
         <v>13.5</v>
@@ -5337,7 +5337,7 @@
         <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BG18">
         <v>19.5</v>
@@ -5423,22 +5423,22 @@
         <v>197</v>
       </c>
       <c r="F19">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G19">
         <v>6.2</v>
       </c>
       <c r="H19">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="I19">
         <v>1.83</v>
       </c>
       <c r="J19">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="K19">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5459,22 +5459,22 @@
         <v>1.43</v>
       </c>
       <c r="R19">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="S19">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="T19">
         <v>1.42</v>
       </c>
       <c r="U19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
         <v>2.2</v>
       </c>
       <c r="W19">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X19">
         <v>500</v>
@@ -5495,7 +5495,7 @@
         <v>95</v>
       </c>
       <c r="AD19">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AE19">
         <v>500</v>
@@ -5507,13 +5507,13 @@
         <v>500</v>
       </c>
       <c r="AH19">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AI19">
         <v>500</v>
       </c>
       <c r="AJ19">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK19">
         <v>500</v>
@@ -5531,55 +5531,55 @@
         <v>55</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BF19">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="BG19">
         <v>1.84</v>
@@ -5665,19 +5665,19 @@
         <v>198</v>
       </c>
       <c r="F20">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H20">
         <v>1.75</v>
       </c>
       <c r="I20">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K20">
         <v>4.6</v>
@@ -5698,16 +5698,16 @@
         <v>2.58</v>
       </c>
       <c r="Q20">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R20">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S20">
         <v>2.44</v>
       </c>
       <c r="T20">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U20">
         <v>2.46</v>
@@ -5716,22 +5716,22 @@
         <v>2.2</v>
       </c>
       <c r="W20">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X20">
         <v>25</v>
       </c>
       <c r="Y20">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z20">
         <v>13.5</v>
       </c>
       <c r="AA20">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AB20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC20">
         <v>10.5</v>
@@ -5743,10 +5743,10 @@
         <v>20</v>
       </c>
       <c r="AF20">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AG20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH20">
         <v>19</v>
@@ -5755,7 +5755,7 @@
         <v>26</v>
       </c>
       <c r="AJ20">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AK20">
         <v>60</v>
@@ -5770,7 +5770,7 @@
         <v>38</v>
       </c>
       <c r="AO20">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AP20">
         <v>19</v>
@@ -5779,25 +5779,25 @@
         <v>11</v>
       </c>
       <c r="AR20">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS20">
         <v>17</v>
       </c>
       <c r="AT20">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU20">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV20">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AW20">
         <v>14.5</v>
       </c>
       <c r="AX20">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AY20">
         <v>15.5</v>
@@ -5806,19 +5806,19 @@
         <v>14</v>
       </c>
       <c r="BA20">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="BB20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC20">
         <v>36</v>
       </c>
       <c r="BD20">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="BE20">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF20">
         <v>22</v>
@@ -5910,7 +5910,7 @@
         <v>2.78</v>
       </c>
       <c r="G21">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="H21">
         <v>2.2</v>
@@ -5925,7 +5925,7 @@
         <v>5.2</v>
       </c>
       <c r="L21">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="M21">
         <v>1.01</v>
@@ -5937,7 +5937,7 @@
         <v>1.06</v>
       </c>
       <c r="P21">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q21">
         <v>1.2</v>
@@ -5952,7 +5952,7 @@
         <v>1.25</v>
       </c>
       <c r="U21">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="V21">
         <v>1.65</v>
@@ -5961,10 +5961,10 @@
         <v>1.4</v>
       </c>
       <c r="X21">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="Y21">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="Z21">
         <v>65</v>
@@ -6009,25 +6009,25 @@
         <v>27</v>
       </c>
       <c r="AN21">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO21">
         <v>5.6</v>
       </c>
       <c r="AP21">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ21">
         <v>24</v>
       </c>
       <c r="AR21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS21">
         <v>25</v>
       </c>
       <c r="AT21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU21">
         <v>16</v>
@@ -6042,7 +6042,7 @@
         <v>25</v>
       </c>
       <c r="AY21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ21">
         <v>12</v>
@@ -6054,7 +6054,7 @@
         <v>30</v>
       </c>
       <c r="BC21">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="BD21">
         <v>18.5</v>
@@ -6072,52 +6072,52 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BJ21">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK21">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BM21">
         <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BO21">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="BQ21">
         <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BS21">
         <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BU21">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX21">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BY21">
         <v>1.01</v>
@@ -6155,7 +6155,7 @@
         <v>3.35</v>
       </c>
       <c r="H22">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I22">
         <v>3.35</v>
@@ -6164,13 +6164,13 @@
         <v>2.72</v>
       </c>
       <c r="K22">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M22">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N22">
         <v>2.24</v>
@@ -6179,7 +6179,7 @@
         <v>1.65</v>
       </c>
       <c r="P22">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -6191,7 +6191,7 @@
         <v>3</v>
       </c>
       <c r="T22">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U22">
         <v>1.57</v>
@@ -6212,7 +6212,7 @@
         <v>500</v>
       </c>
       <c r="AA22">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB22">
         <v>970</v>
@@ -6239,7 +6239,7 @@
         <v>540</v>
       </c>
       <c r="AJ22">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK22">
         <v>500</v>
@@ -6257,58 +6257,58 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>3.85</v>
+        <v>1.84</v>
       </c>
       <c r="AQ22">
         <v>5.7</v>
       </c>
       <c r="AR22">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="AS22">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="AT22">
         <v>5.7</v>
       </c>
       <c r="AU22">
-        <v>5.1</v>
+        <v>1.71</v>
       </c>
       <c r="AV22">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="AW22">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="AX22">
-        <v>1.12</v>
+        <v>1.57</v>
       </c>
       <c r="AY22">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AZ22">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BA22">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="BB22">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="BC22">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="BD22">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BE22">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="BF22">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="BG22">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6391,22 +6391,22 @@
         <v>201</v>
       </c>
       <c r="F23">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="G23">
         <v>200</v>
       </c>
       <c r="H23">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I23">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="J23">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="K23">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L23">
         <v>1.37</v>
@@ -6415,34 +6415,34 @@
         <v>1.02</v>
       </c>
       <c r="N23">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O23">
         <v>1.35</v>
       </c>
       <c r="P23">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R23">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S23">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="T23">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U23">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="V23">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6460,7 +6460,7 @@
         <v>1000</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD23">
         <v>1000</v>
@@ -6499,28 +6499,28 @@
         <v>29</v>
       </c>
       <c r="AP23">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AQ23">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AR23">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AS23">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AT23">
         <v>2.5</v>
       </c>
       <c r="AU23">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AV23">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AW23">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AX23">
         <v>2.5</v>
@@ -6529,10 +6529,10 @@
         <v>2.5</v>
       </c>
       <c r="AZ23">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BA23">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BB23">
         <v>2.5</v>
@@ -6544,7 +6544,7 @@
         <v>2.5</v>
       </c>
       <c r="BE23">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BF23">
         <v>4.2</v>
@@ -6633,7 +6633,7 @@
         <v>202</v>
       </c>
       <c r="F24">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G24">
         <v>1.71</v>
@@ -6642,16 +6642,16 @@
         <v>5.1</v>
       </c>
       <c r="I24">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K24">
         <v>5.2</v>
       </c>
       <c r="L24">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M24">
         <v>1.01</v>
@@ -6669,10 +6669,10 @@
         <v>1.43</v>
       </c>
       <c r="R24">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S24">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="T24">
         <v>1.53</v>
@@ -6699,7 +6699,7 @@
         <v>700</v>
       </c>
       <c r="AB24">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC24">
         <v>12.5</v>
@@ -6741,13 +6741,13 @@
         <v>50</v>
       </c>
       <c r="AP24">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ24">
         <v>26</v>
       </c>
       <c r="AR24">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="AS24">
         <v>7.6</v>
@@ -6762,7 +6762,7 @@
         <v>18.5</v>
       </c>
       <c r="AW24">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="AX24">
         <v>11.5</v>
@@ -6774,22 +6774,22 @@
         <v>14</v>
       </c>
       <c r="BA24">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB24">
         <v>15</v>
       </c>
       <c r="BC24">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE24">
         <v>7.2</v>
       </c>
       <c r="BF24">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG24">
         <v>6.6</v>
@@ -6875,22 +6875,22 @@
         <v>203</v>
       </c>
       <c r="F25">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G25">
         <v>3.05</v>
       </c>
       <c r="H25">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I25">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="J25">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K25">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L25">
         <v>1.25</v>
@@ -6899,7 +6899,7 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>1.16</v>
@@ -6908,7 +6908,7 @@
         <v>2.68</v>
       </c>
       <c r="Q25">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="R25">
         <v>1.69</v>
@@ -6917,13 +6917,13 @@
         <v>2.22</v>
       </c>
       <c r="T25">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U25">
         <v>2.72</v>
       </c>
       <c r="V25">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="W25">
         <v>1.49</v>
@@ -6950,7 +6950,7 @@
         <v>13</v>
       </c>
       <c r="AE25">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AF25">
         <v>26</v>
@@ -6974,7 +6974,7 @@
         <v>32</v>
       </c>
       <c r="AM25">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AN25">
         <v>15</v>
@@ -7019,7 +7019,7 @@
         <v>18.5</v>
       </c>
       <c r="BB25">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC25">
         <v>19</v>
@@ -7028,7 +7028,7 @@
         <v>20</v>
       </c>
       <c r="BE25">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF25">
         <v>11.5</v>
@@ -7135,7 +7135,7 @@
         <v>4.7</v>
       </c>
       <c r="L26">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
         <v>1.01</v>
@@ -7150,7 +7150,7 @@
         <v>2.74</v>
       </c>
       <c r="Q26">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R26">
         <v>1.7</v>
@@ -7359,25 +7359,25 @@
         <v>205</v>
       </c>
       <c r="F27">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G27">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H27">
+        <v>3.1</v>
+      </c>
+      <c r="I27">
+        <v>4.1</v>
+      </c>
+      <c r="J27">
         <v>3.25</v>
       </c>
-      <c r="I27">
-        <v>3.9</v>
-      </c>
-      <c r="J27">
-        <v>3.2</v>
-      </c>
       <c r="K27">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="L27">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
         <v>1.05</v>
@@ -7398,127 +7398,127 @@
         <v>1.24</v>
       </c>
       <c r="S27">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T27">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U27">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X27">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y27">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z27">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AA27">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB27">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AD27">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE27">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF27">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG27">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH27">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AI27">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ27">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AK27">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AL27">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM27">
-        <v>440</v>
+        <v>580</v>
       </c>
       <c r="AN27">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AO27">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AP27">
-        <v>6.2</v>
+        <v>1.69</v>
       </c>
       <c r="AQ27">
-        <v>6.4</v>
+        <v>1.7</v>
       </c>
       <c r="AR27">
-        <v>4.8</v>
+        <v>1.78</v>
       </c>
       <c r="AS27">
-        <v>5.4</v>
+        <v>1.84</v>
       </c>
       <c r="AT27">
         <v>5.6</v>
       </c>
       <c r="AU27">
-        <v>4.9</v>
+        <v>1.63</v>
       </c>
       <c r="AV27">
-        <v>4.2</v>
+        <v>1.74</v>
       </c>
       <c r="AW27">
-        <v>5.3</v>
+        <v>1.82</v>
       </c>
       <c r="AX27">
-        <v>4.3</v>
+        <v>1.76</v>
       </c>
       <c r="AY27">
-        <v>4</v>
+        <v>1.71</v>
       </c>
       <c r="AZ27">
-        <v>4.6</v>
+        <v>1.79</v>
       </c>
       <c r="BA27">
-        <v>5.4</v>
+        <v>1.83</v>
       </c>
       <c r="BB27">
-        <v>5</v>
+        <v>1.81</v>
       </c>
       <c r="BC27">
-        <v>4.8</v>
+        <v>1.81</v>
       </c>
       <c r="BD27">
-        <v>5.2</v>
+        <v>1.82</v>
       </c>
       <c r="BE27">
-        <v>5.6</v>
+        <v>1.84</v>
       </c>
       <c r="BF27">
-        <v>6</v>
+        <v>1.79</v>
       </c>
       <c r="BG27">
-        <v>5.3</v>
+        <v>1.81</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7601,19 +7601,19 @@
         <v>206</v>
       </c>
       <c r="F28">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="G28">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H28">
         <v>4.9</v>
       </c>
       <c r="I28">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J28">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K28">
         <v>4.9</v>
@@ -7628,13 +7628,13 @@
         <v>5.6</v>
       </c>
       <c r="O28">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P28">
         <v>2.62</v>
       </c>
       <c r="Q28">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R28">
         <v>1.65</v>
@@ -7652,7 +7652,7 @@
         <v>1.22</v>
       </c>
       <c r="W28">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X28">
         <v>32</v>
@@ -7661,7 +7661,7 @@
         <v>26</v>
       </c>
       <c r="Z28">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AA28">
         <v>120</v>
@@ -7670,7 +7670,7 @@
         <v>13</v>
       </c>
       <c r="AC28">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD28">
         <v>21</v>
@@ -7709,22 +7709,22 @@
         <v>48</v>
       </c>
       <c r="AP28">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ28">
         <v>20</v>
       </c>
       <c r="AR28">
-        <v>32</v>
+        <v>9.4</v>
       </c>
       <c r="AS28">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT28">
         <v>11</v>
       </c>
       <c r="AU28">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV28">
         <v>16.5</v>
@@ -7742,22 +7742,22 @@
         <v>14.5</v>
       </c>
       <c r="BA28">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB28">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC28">
         <v>13.5</v>
       </c>
       <c r="BD28">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE28">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BF28">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BG28">
         <v>30</v>
@@ -7843,43 +7843,43 @@
         <v>207</v>
       </c>
       <c r="F29">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="G29">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H29">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I29">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="K29">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L29">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="M29">
         <v>1.02</v>
       </c>
       <c r="N29">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O29">
         <v>1.11</v>
       </c>
       <c r="P29">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q29">
         <v>1.35</v>
       </c>
       <c r="R29">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S29">
         <v>1.86</v>
@@ -7888,10 +7888,10 @@
         <v>1.46</v>
       </c>
       <c r="U29">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="V29">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="W29">
         <v>1.22</v>
@@ -7906,7 +7906,7 @@
         <v>19.5</v>
       </c>
       <c r="AA29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB29">
         <v>40</v>
@@ -7915,22 +7915,22 @@
         <v>16</v>
       </c>
       <c r="AD29">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE29">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AF29">
         <v>60</v>
       </c>
       <c r="AG29">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH29">
         <v>18.5</v>
       </c>
       <c r="AI29">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AJ29">
         <v>120</v>
@@ -7942,13 +7942,13 @@
         <v>46</v>
       </c>
       <c r="AM29">
-        <v>55</v>
+        <v>580</v>
       </c>
       <c r="AN29">
         <v>30</v>
       </c>
       <c r="AO29">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="AP29">
         <v>18</v>
@@ -7969,97 +7969,97 @@
         <v>10.5</v>
       </c>
       <c r="AV29">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW29">
         <v>13</v>
       </c>
       <c r="AX29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY29">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AZ29">
         <v>13.5</v>
       </c>
       <c r="BA29">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BB29">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD29">
         <v>32</v>
       </c>
       <c r="BE29">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="BF29">
-        <v>19</v>
+        <v>6.2</v>
       </c>
       <c r="BG29">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH29">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK29">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL29">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BM29">
         <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BO29">
         <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BQ29">
         <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BS29">
         <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU29">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BV29">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BW29">
         <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BY29">
         <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA29">
         <v>1.01</v>
@@ -8085,7 +8085,7 @@
         <v>208</v>
       </c>
       <c r="F30">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G30">
         <v>1.85</v>
@@ -8097,13 +8097,13 @@
         <v>5.1</v>
       </c>
       <c r="J30">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K30">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L30">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M30">
         <v>1.05</v>
@@ -8112,7 +8112,7 @@
         <v>4.4</v>
       </c>
       <c r="O30">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P30">
         <v>2.12</v>
@@ -8139,7 +8139,7 @@
         <v>2.16</v>
       </c>
       <c r="X30">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Y30">
         <v>25</v>
@@ -8151,7 +8151,7 @@
         <v>700</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC30">
         <v>9.4</v>
@@ -8199,10 +8199,10 @@
         <v>18</v>
       </c>
       <c r="AR30">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="AS30">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AT30">
         <v>8.6</v>
@@ -8214,7 +8214,7 @@
         <v>16</v>
       </c>
       <c r="AW30">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX30">
         <v>10</v>
@@ -8223,10 +8223,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ30">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="BA30">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB30">
         <v>16.5</v>
@@ -8235,16 +8235,16 @@
         <v>15.5</v>
       </c>
       <c r="BD30">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BE30">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF30">
         <v>8.800000000000001</v>
       </c>
       <c r="BG30">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BH30">
         <v>4.4</v>
@@ -8271,7 +8271,7 @@
         <v>3.5</v>
       </c>
       <c r="BP30">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ30">
         <v>1.01</v>
@@ -8283,7 +8283,7 @@
         <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU30">
         <v>1.01</v>
@@ -8384,7 +8384,7 @@
         <v>14.5</v>
       </c>
       <c r="Y31">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z31">
         <v>23</v>
@@ -8399,7 +8399,7 @@
         <v>8.4</v>
       </c>
       <c r="AD31">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE31">
         <v>32</v>
@@ -8444,7 +8444,7 @@
         <v>16</v>
       </c>
       <c r="AS31">
-        <v>6.6</v>
+        <v>36</v>
       </c>
       <c r="AT31">
         <v>9.800000000000001</v>
@@ -8456,7 +8456,7 @@
         <v>10.5</v>
       </c>
       <c r="AW31">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AX31">
         <v>13.5</v>
@@ -8468,19 +8468,19 @@
         <v>14</v>
       </c>
       <c r="BA31">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB31">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC31">
         <v>21</v>
       </c>
       <c r="BD31">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE31">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF31">
         <v>17.5</v>
@@ -8584,10 +8584,10 @@
         <v>3.6</v>
       </c>
       <c r="K32">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L32">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M32">
         <v>1.07</v>
@@ -8611,25 +8611,25 @@
         <v>3.4</v>
       </c>
       <c r="T32">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U32">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V32">
         <v>1.35</v>
       </c>
       <c r="W32">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X32">
+        <v>15</v>
+      </c>
+      <c r="Y32">
         <v>14.5</v>
       </c>
-      <c r="Y32">
-        <v>17</v>
-      </c>
       <c r="Z32">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA32">
         <v>80</v>
@@ -8659,25 +8659,25 @@
         <v>60</v>
       </c>
       <c r="AJ32">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK32">
         <v>23</v>
       </c>
       <c r="AL32">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM32">
         <v>500</v>
       </c>
       <c r="AN32">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="AO32">
         <v>50</v>
       </c>
       <c r="AP32">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ32">
         <v>13</v>
@@ -8686,7 +8686,7 @@
         <v>24</v>
       </c>
       <c r="AS32">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="AT32">
         <v>8.4</v>
@@ -8698,7 +8698,7 @@
         <v>14</v>
       </c>
       <c r="AW32">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AX32">
         <v>11.5</v>
@@ -8814,22 +8814,22 @@
         <v>2.76</v>
       </c>
       <c r="G33">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H33">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I33">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J33">
         <v>3.8</v>
       </c>
       <c r="K33">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L33">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M33">
         <v>1.05</v>
@@ -8850,16 +8850,16 @@
         <v>1.48</v>
       </c>
       <c r="S33">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T33">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U33">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V33">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W33">
         <v>1.55</v>
@@ -8883,7 +8883,7 @@
         <v>11</v>
       </c>
       <c r="AD33">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE33">
         <v>25</v>
@@ -8943,7 +8943,7 @@
         <v>23</v>
       </c>
       <c r="AX33">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY33">
         <v>11</v>
@@ -9071,19 +9071,19 @@
         <v>3.95</v>
       </c>
       <c r="L34">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M34">
         <v>1.07</v>
       </c>
       <c r="N34">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O34">
         <v>1.32</v>
       </c>
       <c r="P34">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q34">
         <v>1.98</v>
@@ -9095,10 +9095,10 @@
         <v>3.4</v>
       </c>
       <c r="T34">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U34">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V34">
         <v>1.25</v>
@@ -9110,7 +9110,7 @@
         <v>14.5</v>
       </c>
       <c r="Y34">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z34">
         <v>38</v>
@@ -9122,10 +9122,10 @@
         <v>11</v>
       </c>
       <c r="AC34">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD34">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE34">
         <v>65</v>
@@ -9137,13 +9137,13 @@
         <v>10</v>
       </c>
       <c r="AH34">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AI34">
         <v>70</v>
       </c>
       <c r="AJ34">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK34">
         <v>21</v>
@@ -9152,7 +9152,7 @@
         <v>46</v>
       </c>
       <c r="AM34">
-        <v>110</v>
+        <v>390</v>
       </c>
       <c r="AN34">
         <v>12.5</v>
@@ -9170,7 +9170,7 @@
         <v>32</v>
       </c>
       <c r="AS34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT34">
         <v>8</v>
@@ -9245,16 +9245,16 @@
         <v>1.01</v>
       </c>
       <c r="BR34">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS34">
         <v>1.01</v>
       </c>
       <c r="BT34">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU34">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV34">
         <v>50</v>
@@ -9295,16 +9295,16 @@
         <v>213</v>
       </c>
       <c r="F35">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G35">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H35">
         <v>2.72</v>
       </c>
       <c r="I35">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="J35">
         <v>3.5</v>
@@ -9313,43 +9313,43 @@
         <v>3.6</v>
       </c>
       <c r="L35">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M35">
         <v>1.07</v>
       </c>
       <c r="N35">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O35">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P35">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Q35">
         <v>2</v>
       </c>
       <c r="R35">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S35">
         <v>3.55</v>
       </c>
       <c r="T35">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="U35">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V35">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W35">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X35">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y35">
         <v>12.5</v>
@@ -9373,7 +9373,7 @@
         <v>36</v>
       </c>
       <c r="AF35">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG35">
         <v>13</v>
@@ -9385,13 +9385,13 @@
         <v>150</v>
       </c>
       <c r="AJ35">
+        <v>100</v>
+      </c>
+      <c r="AK35">
+        <v>32</v>
+      </c>
+      <c r="AL35">
         <v>44</v>
-      </c>
-      <c r="AK35">
-        <v>36</v>
-      </c>
-      <c r="AL35">
-        <v>50</v>
       </c>
       <c r="AM35">
         <v>320</v>
@@ -9412,7 +9412,7 @@
         <v>16</v>
       </c>
       <c r="AS35">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT35">
         <v>9.800000000000001</v>
@@ -9436,31 +9436,31 @@
         <v>15.5</v>
       </c>
       <c r="BA35">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB35">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC35">
         <v>14.5</v>
       </c>
       <c r="BD35">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE35">
+        <v>5.9</v>
+      </c>
+      <c r="BF35">
         <v>6</v>
       </c>
-      <c r="BF35">
-        <v>5.4</v>
-      </c>
       <c r="BG35">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BH35">
         <v>3.75</v>
       </c>
       <c r="BI35">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ35">
         <v>11</v>
@@ -9537,19 +9537,19 @@
         <v>214</v>
       </c>
       <c r="F36">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="G36">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="H36">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="I36">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="J36">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K36">
         <v>3.55</v>
@@ -9567,7 +9567,7 @@
         <v>1.32</v>
       </c>
       <c r="P36">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q36">
         <v>1.97</v>
@@ -9582,19 +9582,19 @@
         <v>1.77</v>
       </c>
       <c r="U36">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V36">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W36">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X36">
         <v>14</v>
       </c>
       <c r="Y36">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z36">
         <v>19</v>
@@ -9609,16 +9609,16 @@
         <v>8</v>
       </c>
       <c r="AD36">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE36">
         <v>32</v>
       </c>
       <c r="AF36">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG36">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH36">
         <v>17</v>
@@ -9642,7 +9642,7 @@
         <v>26</v>
       </c>
       <c r="AO36">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP36">
         <v>12.5</v>
@@ -9651,10 +9651,10 @@
         <v>10.5</v>
       </c>
       <c r="AR36">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS36">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT36">
         <v>10.5</v>
@@ -9663,16 +9663,16 @@
         <v>7.2</v>
       </c>
       <c r="AV36">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW36">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="AX36">
         <v>16.5</v>
       </c>
       <c r="AY36">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ36">
         <v>15</v>
@@ -9684,7 +9684,7 @@
         <v>36</v>
       </c>
       <c r="BC36">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD36">
         <v>36</v>
@@ -9702,7 +9702,7 @@
         <v>4</v>
       </c>
       <c r="BI36">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="BJ36">
         <v>11.5</v>
@@ -9785,7 +9785,7 @@
         <v>2.02</v>
       </c>
       <c r="H37">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I37">
         <v>4</v>
@@ -9797,13 +9797,13 @@
         <v>4.2</v>
       </c>
       <c r="L37">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M37">
         <v>1.05</v>
       </c>
       <c r="N37">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O37">
         <v>1.23</v>
@@ -9812,19 +9812,19 @@
         <v>2.38</v>
       </c>
       <c r="Q37">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R37">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="S37">
         <v>2.74</v>
       </c>
       <c r="T37">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U37">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V37">
         <v>1.33</v>
@@ -9839,19 +9839,19 @@
         <v>19</v>
       </c>
       <c r="Z37">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AA37">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AB37">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC37">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD37">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE37">
         <v>42</v>
@@ -9866,7 +9866,7 @@
         <v>19.5</v>
       </c>
       <c r="AI37">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AJ37">
         <v>24</v>
@@ -9884,7 +9884,7 @@
         <v>11.5</v>
       </c>
       <c r="AO37">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AP37">
         <v>17.5</v>
@@ -9896,7 +9896,7 @@
         <v>26</v>
       </c>
       <c r="AS37">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT37">
         <v>10.5</v>
@@ -10045,16 +10045,16 @@
         <v>1.07</v>
       </c>
       <c r="N38">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O38">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P38">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q38">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R38">
         <v>1.38</v>
@@ -10063,10 +10063,10 @@
         <v>3.4</v>
       </c>
       <c r="T38">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U38">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V38">
         <v>1.22</v>
@@ -10090,7 +10090,7 @@
         <v>8.6</v>
       </c>
       <c r="AC38">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD38">
         <v>22</v>
@@ -10126,7 +10126,7 @@
         <v>11</v>
       </c>
       <c r="AO38">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP38">
         <v>13.5</v>
@@ -10135,13 +10135,13 @@
         <v>16</v>
       </c>
       <c r="AR38">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AS38">
         <v>42</v>
       </c>
       <c r="AT38">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU38">
         <v>8.199999999999999</v>
@@ -10150,7 +10150,7 @@
         <v>18.5</v>
       </c>
       <c r="AW38">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX38">
         <v>9.4</v>
@@ -10162,7 +10162,7 @@
         <v>18.5</v>
       </c>
       <c r="BA38">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BB38">
         <v>16.5</v>
@@ -10174,7 +10174,7 @@
         <v>30</v>
       </c>
       <c r="BE38">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BF38">
         <v>9.800000000000001</v>
@@ -10263,22 +10263,22 @@
         <v>217</v>
       </c>
       <c r="F39">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G39">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H39">
+        <v>3.7</v>
+      </c>
+      <c r="I39">
         <v>3.8</v>
       </c>
-      <c r="I39">
-        <v>3.9</v>
-      </c>
       <c r="J39">
+        <v>3.7</v>
+      </c>
+      <c r="K39">
         <v>3.75</v>
-      </c>
-      <c r="K39">
-        <v>3.8</v>
       </c>
       <c r="L39">
         <v>1.34</v>
@@ -10305,22 +10305,22 @@
         <v>3.05</v>
       </c>
       <c r="T39">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U39">
         <v>2.36</v>
       </c>
       <c r="V39">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W39">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X39">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y39">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z39">
         <v>28</v>
@@ -10332,13 +10332,13 @@
         <v>11.5</v>
       </c>
       <c r="AC39">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD39">
         <v>15.5</v>
       </c>
       <c r="AE39">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF39">
         <v>14</v>
@@ -10350,10 +10350,10 @@
         <v>16</v>
       </c>
       <c r="AI39">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ39">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK39">
         <v>20</v>
@@ -10371,7 +10371,7 @@
         <v>38</v>
       </c>
       <c r="AP39">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ39">
         <v>15</v>
@@ -10380,13 +10380,13 @@
         <v>25</v>
       </c>
       <c r="AS39">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AT39">
         <v>10.5</v>
       </c>
       <c r="AU39">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV39">
         <v>15</v>
@@ -10398,13 +10398,13 @@
         <v>13</v>
       </c>
       <c r="AY39">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ39">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA39">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB39">
         <v>24</v>
@@ -10422,7 +10422,7 @@
         <v>12</v>
       </c>
       <c r="BG39">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH39">
         <v>970</v>
@@ -10535,10 +10535,10 @@
         <v>1.32</v>
       </c>
       <c r="P40">
+        <v>1.98</v>
+      </c>
+      <c r="Q40">
         <v>1.97</v>
-      </c>
-      <c r="Q40">
-        <v>1.96</v>
       </c>
       <c r="R40">
         <v>1.37</v>
@@ -10577,7 +10577,7 @@
         <v>8.4</v>
       </c>
       <c r="AD40">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE40">
         <v>55</v>
@@ -10604,7 +10604,7 @@
         <v>38</v>
       </c>
       <c r="AM40">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN40">
         <v>14</v>
@@ -10622,7 +10622,7 @@
         <v>28</v>
       </c>
       <c r="AS40">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AT40">
         <v>8.800000000000001</v>
@@ -10664,7 +10664,7 @@
         <v>12.5</v>
       </c>
       <c r="BG40">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BH40">
         <v>970</v>
@@ -10822,7 +10822,7 @@
         <v>14</v>
       </c>
       <c r="AE41">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF41">
         <v>15.5</v>
@@ -10846,10 +10846,10 @@
         <v>40</v>
       </c>
       <c r="AM41">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN41">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO41">
         <v>36</v>
@@ -10912,7 +10912,7 @@
         <v>3.4</v>
       </c>
       <c r="BI41">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ41">
         <v>11</v>
@@ -10989,16 +10989,16 @@
         <v>220</v>
       </c>
       <c r="F42">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G42">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H42">
         <v>2.58</v>
       </c>
       <c r="I42">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J42">
         <v>3.6</v>
@@ -11034,7 +11034,7 @@
         <v>1.71</v>
       </c>
       <c r="U42">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="V42">
         <v>1.55</v>
@@ -11043,7 +11043,7 @@
         <v>1.52</v>
       </c>
       <c r="X42">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y42">
         <v>13</v>
@@ -11052,7 +11052,7 @@
         <v>20</v>
       </c>
       <c r="AA42">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB42">
         <v>13</v>
@@ -11064,7 +11064,7 @@
         <v>13</v>
       </c>
       <c r="AE42">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF42">
         <v>20</v>
@@ -11076,28 +11076,28 @@
         <v>17</v>
       </c>
       <c r="AI42">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AJ42">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK42">
         <v>32</v>
       </c>
       <c r="AL42">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM42">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN42">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AO42">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AP42">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AQ42">
         <v>10.5</v>
@@ -11106,7 +11106,7 @@
         <v>16</v>
       </c>
       <c r="AS42">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT42">
         <v>10.5</v>
@@ -11130,10 +11130,10 @@
         <v>14</v>
       </c>
       <c r="BA42">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB42">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC42">
         <v>24</v>
@@ -11142,7 +11142,7 @@
         <v>32</v>
       </c>
       <c r="BE42">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF42">
         <v>17.5</v>
@@ -11187,7 +11187,7 @@
         <v>1.01</v>
       </c>
       <c r="BT42">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU42">
         <v>4.6</v>
@@ -11231,19 +11231,19 @@
         <v>221</v>
       </c>
       <c r="F43">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="G43">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="H43">
-        <v>1.08</v>
+        <v>3</v>
       </c>
       <c r="I43">
         <v>110</v>
       </c>
       <c r="J43">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="K43">
         <v>1000</v>
@@ -11279,10 +11279,10 @@
         <v>1.01</v>
       </c>
       <c r="V43">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W43">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="X43">
         <v>1000</v>
@@ -11333,7 +11333,7 @@
         <v>1000</v>
       </c>
       <c r="AN43">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO43">
         <v>1000</v>
@@ -11390,7 +11390,7 @@
         <v>1.01</v>
       </c>
       <c r="BG43">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH43">
         <v>1000</v>
@@ -11473,16 +11473,16 @@
         <v>222</v>
       </c>
       <c r="F44">
+        <v>2.3</v>
+      </c>
+      <c r="G44">
         <v>2.32</v>
-      </c>
-      <c r="G44">
-        <v>2.34</v>
       </c>
       <c r="H44">
         <v>3.5</v>
       </c>
       <c r="I44">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J44">
         <v>3.45</v>
@@ -11491,7 +11491,7 @@
         <v>3.5</v>
       </c>
       <c r="L44">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M44">
         <v>1.08</v>
@@ -11521,10 +11521,10 @@
         <v>2.1</v>
       </c>
       <c r="V44">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W44">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X44">
         <v>13</v>
@@ -11551,7 +11551,7 @@
         <v>44</v>
       </c>
       <c r="AF44">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG44">
         <v>11.5</v>
@@ -11566,7 +11566,7 @@
         <v>30</v>
       </c>
       <c r="AK44">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL44">
         <v>42</v>
@@ -11590,7 +11590,7 @@
         <v>21</v>
       </c>
       <c r="AS44">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AT44">
         <v>8.800000000000001</v>
@@ -11632,7 +11632,7 @@
         <v>18.5</v>
       </c>
       <c r="BG44">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BH44">
         <v>3.6</v>
@@ -11644,16 +11644,16 @@
         <v>11.5</v>
       </c>
       <c r="BK44">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BL44">
         <v>160</v>
       </c>
       <c r="BM44">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BN44">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BO44">
         <v>4.4</v>
@@ -11662,13 +11662,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ44">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BR44">
         <v>34</v>
       </c>
       <c r="BS44">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BT44">
         <v>7</v>
@@ -11680,19 +11680,19 @@
         <v>32</v>
       </c>
       <c r="BW44">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BX44">
         <v>44</v>
       </c>
       <c r="BY44">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BZ44">
         <v>32</v>
       </c>
       <c r="CA44">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="CB44" t="s">
         <v>233</v>
@@ -11715,10 +11715,10 @@
         <v>223</v>
       </c>
       <c r="F45">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G45">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="H45">
         <v>4.6</v>
@@ -11730,7 +11730,7 @@
         <v>3.5</v>
       </c>
       <c r="K45">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L45">
         <v>1.38</v>
@@ -11739,22 +11739,22 @@
         <v>1.01</v>
       </c>
       <c r="N45">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O45">
         <v>1.38</v>
       </c>
       <c r="P45">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q45">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R45">
         <v>1.23</v>
       </c>
       <c r="S45">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T45">
         <v>1.01</v>
@@ -11763,118 +11763,118 @@
         <v>1.01</v>
       </c>
       <c r="V45">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W45">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA45">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ45">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM45">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN45">
         <v>55</v>
       </c>
       <c r="AO45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP45">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AQ45">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AR45">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AS45">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AT45">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AU45">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AV45">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AW45">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AX45">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AY45">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AZ45">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BA45">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BB45">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BC45">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BD45">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BE45">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BF45">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG45">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH45">
         <v>1000</v>
@@ -11957,25 +11957,25 @@
         <v>224</v>
       </c>
       <c r="F46">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G46">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H46">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="I46">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="J46">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K46">
         <v>3.7</v>
       </c>
       <c r="L46">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M46">
         <v>1.06</v>
@@ -11993,7 +11993,7 @@
         <v>1.86</v>
       </c>
       <c r="R46">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S46">
         <v>3.15</v>
@@ -12005,10 +12005,10 @@
         <v>2.34</v>
       </c>
       <c r="V46">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W46">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X46">
         <v>16</v>
@@ -12017,37 +12017,37 @@
         <v>11.5</v>
       </c>
       <c r="Z46">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA46">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB46">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC46">
         <v>8</v>
       </c>
       <c r="AD46">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE46">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF46">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG46">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH46">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI46">
         <v>36</v>
       </c>
       <c r="AJ46">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK46">
         <v>34</v>
@@ -12056,13 +12056,13 @@
         <v>44</v>
       </c>
       <c r="AM46">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AN46">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO46">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP46">
         <v>14.5</v>
@@ -12071,16 +12071,16 @@
         <v>10.5</v>
       </c>
       <c r="AR46">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS46">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AT46">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU46">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV46">
         <v>10</v>
@@ -12089,7 +12089,7 @@
         <v>21</v>
       </c>
       <c r="AX46">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY46">
         <v>12.5</v>
@@ -12098,25 +12098,25 @@
         <v>15</v>
       </c>
       <c r="BA46">
+        <v>32</v>
+      </c>
+      <c r="BB46">
+        <v>50</v>
+      </c>
+      <c r="BC46">
         <v>30</v>
       </c>
-      <c r="BB46">
-        <v>46</v>
-      </c>
-      <c r="BC46">
-        <v>21</v>
-      </c>
       <c r="BD46">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE46">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF46">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BG46">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH46">
         <v>4</v>
@@ -12134,7 +12134,7 @@
         <v>120</v>
       </c>
       <c r="BM46">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BN46">
         <v>7.4</v>
@@ -12146,37 +12146,37 @@
         <v>26</v>
       </c>
       <c r="BQ46">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR46">
         <v>36</v>
       </c>
       <c r="BS46">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BT46">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU46">
         <v>4.6</v>
       </c>
       <c r="BV46">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW46">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BX46">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY46">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BZ46">
         <v>24</v>
       </c>
       <c r="CA46">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="CB46" t="s">
         <v>233</v>
@@ -12262,16 +12262,16 @@
         <v>20</v>
       </c>
       <c r="AA47">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB47">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC47">
         <v>8</v>
       </c>
       <c r="AD47">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE47">
         <v>30</v>
@@ -12286,10 +12286,10 @@
         <v>16.5</v>
       </c>
       <c r="AI47">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ47">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK47">
         <v>26</v>
@@ -12298,13 +12298,13 @@
         <v>38</v>
       </c>
       <c r="AM47">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN47">
         <v>21</v>
       </c>
       <c r="AO47">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP47">
         <v>14.5</v>
@@ -12313,10 +12313,10 @@
         <v>12</v>
       </c>
       <c r="AR47">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS47">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AT47">
         <v>11.5</v>
@@ -12331,7 +12331,7 @@
         <v>27</v>
       </c>
       <c r="AX47">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY47">
         <v>11</v>
@@ -12343,10 +12343,10 @@
         <v>34</v>
       </c>
       <c r="BB47">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC47">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD47">
         <v>32</v>
@@ -12355,7 +12355,7 @@
         <v>44</v>
       </c>
       <c r="BF47">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG47">
         <v>21</v>
@@ -12453,10 +12453,10 @@
         <v>3.7</v>
       </c>
       <c r="J48">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K48">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L48">
         <v>1.01</v>
@@ -12465,10 +12465,10 @@
         <v>1.12</v>
       </c>
       <c r="N48">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O48">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="P48">
         <v>1.53</v>
@@ -12477,10 +12477,10 @@
         <v>2.6</v>
       </c>
       <c r="R48">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S48">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="T48">
         <v>2.08</v>
@@ -12501,7 +12501,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z48">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA48">
         <v>85</v>
@@ -12534,13 +12534,13 @@
         <v>48</v>
       </c>
       <c r="AK48">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AL48">
         <v>75</v>
       </c>
       <c r="AM48">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN48">
         <v>48</v>
@@ -12555,7 +12555,7 @@
         <v>8.6</v>
       </c>
       <c r="AR48">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AS48">
         <v>1.01</v>
@@ -12567,7 +12567,7 @@
         <v>6.2</v>
       </c>
       <c r="AV48">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW48">
         <v>1.01</v>
@@ -12588,7 +12588,7 @@
         <v>30</v>
       </c>
       <c r="BC48">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BD48">
         <v>1.01</v>
@@ -12597,10 +12597,10 @@
         <v>1.01</v>
       </c>
       <c r="BF48">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG48">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH48">
         <v>1000</v>
@@ -12683,16 +12683,16 @@
         <v>227</v>
       </c>
       <c r="F49">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="G49">
         <v>3.1</v>
       </c>
       <c r="H49">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="I49">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J49">
         <v>2.82</v>
@@ -12704,7 +12704,7 @@
         <v>1.41</v>
       </c>
       <c r="M49">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N49">
         <v>2.92</v>
@@ -12716,13 +12716,13 @@
         <v>1.64</v>
       </c>
       <c r="Q49">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R49">
         <v>1.24</v>
       </c>
       <c r="S49">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T49">
         <v>1.87</v>
@@ -12731,19 +12731,19 @@
         <v>1.96</v>
       </c>
       <c r="V49">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W49">
         <v>1.48</v>
       </c>
       <c r="X49">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y49">
         <v>10.5</v>
       </c>
       <c r="Z49">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA49">
         <v>65</v>
@@ -12782,10 +12782,10 @@
         <v>65</v>
       </c>
       <c r="AM49">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN49">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AO49">
         <v>44</v>
@@ -12812,7 +12812,7 @@
         <v>11</v>
       </c>
       <c r="AW49">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="AX49">
         <v>13</v>
@@ -12827,10 +12827,10 @@
         <v>6.8</v>
       </c>
       <c r="BB49">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC49">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD49">
         <v>6.8</v>
@@ -12839,7 +12839,7 @@
         <v>7.2</v>
       </c>
       <c r="BF49">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG49">
         <v>6.4</v>
@@ -12943,22 +12943,22 @@
         <v>3.65</v>
       </c>
       <c r="L50">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M50">
         <v>1.1</v>
       </c>
       <c r="N50">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="O50">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="P50">
         <v>1.61</v>
       </c>
       <c r="Q50">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R50">
         <v>1.22</v>
@@ -12967,7 +12967,7 @@
         <v>4.5</v>
       </c>
       <c r="T50">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="U50">
         <v>1.8</v>
@@ -12982,7 +12982,7 @@
         <v>12</v>
       </c>
       <c r="Y50">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z50">
         <v>36</v>
@@ -12994,13 +12994,13 @@
         <v>7.4</v>
       </c>
       <c r="AC50">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD50">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE50">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF50">
         <v>12.5</v>
@@ -13009,13 +13009,13 @@
         <v>11.5</v>
       </c>
       <c r="AH50">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI50">
         <v>100</v>
       </c>
       <c r="AJ50">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK50">
         <v>28</v>
@@ -13027,7 +13027,7 @@
         <v>580</v>
       </c>
       <c r="AN50">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO50">
         <v>120</v>
@@ -13087,10 +13087,10 @@
         <v>1.55</v>
       </c>
       <c r="BH50">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="BI50">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="BJ50">
         <v>11.5</v>
@@ -13129,13 +13129,13 @@
         <v>5.7</v>
       </c>
       <c r="BV50">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BW50">
         <v>1.01</v>
       </c>
       <c r="BX50">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BY50">
         <v>1.01</v>
@@ -13170,22 +13170,22 @@
         <v>2.28</v>
       </c>
       <c r="G51">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H51">
         <v>3.3</v>
       </c>
       <c r="I51">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J51">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K51">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L51">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M51">
         <v>1.09</v>
@@ -13218,7 +13218,7 @@
         <v>1.36</v>
       </c>
       <c r="W51">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X51">
         <v>13</v>
@@ -13245,7 +13245,7 @@
         <v>130</v>
       </c>
       <c r="AF51">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AG51">
         <v>14</v>
@@ -13284,7 +13284,7 @@
         <v>17.5</v>
       </c>
       <c r="AS51">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT51">
         <v>6.4</v>
@@ -13293,10 +13293,10 @@
         <v>5.6</v>
       </c>
       <c r="AV51">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW51">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX51">
         <v>10.5</v>
@@ -13308,25 +13308,25 @@
         <v>14.5</v>
       </c>
       <c r="BA51">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB51">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BC51">
         <v>21</v>
       </c>
       <c r="BD51">
+        <v>4.6</v>
+      </c>
+      <c r="BE51">
+        <v>4.9</v>
+      </c>
+      <c r="BF51">
         <v>4.4</v>
       </c>
-      <c r="BE51">
+      <c r="BG51">
         <v>4.7</v>
-      </c>
-      <c r="BF51">
-        <v>4.2</v>
-      </c>
-      <c r="BG51">
-        <v>4.5</v>
       </c>
       <c r="BH51">
         <v>1000</v>
@@ -13409,22 +13409,22 @@
         <v>230</v>
       </c>
       <c r="F52">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G52">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="H52">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I52">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J52">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K52">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L52">
         <v>1.01</v>
@@ -13433,7 +13433,7 @@
         <v>1.15</v>
       </c>
       <c r="N52">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O52">
         <v>1.41</v>
@@ -13445,10 +13445,10 @@
         <v>2.26</v>
       </c>
       <c r="R52">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S52">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T52">
         <v>1.01</v>
@@ -13457,64 +13457,64 @@
         <v>1.01</v>
       </c>
       <c r="V52">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W52">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="X52">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA52">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ52">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO52">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP52">
         <v>1.01</v>
@@ -13565,10 +13565,10 @@
         <v>1.01</v>
       </c>
       <c r="BF52">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG52">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH52">
         <v>1000</v>
@@ -13651,22 +13651,22 @@
         <v>231</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G53">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H53">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I53">
         <v>4.2</v>
       </c>
       <c r="J53">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K53">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="L53">
         <v>1.01</v>
@@ -13675,100 +13675,100 @@
         <v>1.1</v>
       </c>
       <c r="N53">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O53">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="P53">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q53">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R53">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S53">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="T53">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U53">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="V53">
         <v>1.32</v>
       </c>
       <c r="W53">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA53">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB53">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC53">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="AD53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ53">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO53">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP53">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="AQ53">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR53">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="AS53">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="AT53">
         <v>5.4</v>
@@ -13777,40 +13777,40 @@
         <v>5.4</v>
       </c>
       <c r="AV53">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="AW53">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="AX53">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="AY53">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AZ53">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BA53">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BB53">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BC53">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BD53">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BE53">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BF53">
         <v>1.55</v>
       </c>
       <c r="BG53">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH53">
         <v>1000</v>
@@ -13893,19 +13893,19 @@
         <v>232</v>
       </c>
       <c r="F54">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="G54">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="H54">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="I54">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="J54">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K54">
         <v>3.05</v>
@@ -13917,7 +13917,7 @@
         <v>1.14</v>
       </c>
       <c r="N54">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O54">
         <v>1.56</v>
@@ -13929,7 +13929,7 @@
         <v>2.74</v>
       </c>
       <c r="R54">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S54">
         <v>5.5</v>
@@ -13938,31 +13938,31 @@
         <v>2.14</v>
       </c>
       <c r="U54">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V54">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W54">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="X54">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y54">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z54">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA54">
         <v>44</v>
       </c>
       <c r="AB54">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AC54">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD54">
         <v>13.5</v>
@@ -13971,88 +13971,88 @@
         <v>40</v>
       </c>
       <c r="AF54">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AG54">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH54">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI54">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ54">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AK54">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL54">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AM54">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN54">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AO54">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP54">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ54">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AR54">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS54">
+        <v>36</v>
+      </c>
+      <c r="AT54">
+        <v>8.6</v>
+      </c>
+      <c r="AU54">
+        <v>6.4</v>
+      </c>
+      <c r="AV54">
+        <v>12</v>
+      </c>
+      <c r="AW54">
         <v>34</v>
-      </c>
-      <c r="AT54">
-        <v>8.4</v>
-      </c>
-      <c r="AU54">
-        <v>6.2</v>
-      </c>
-      <c r="AV54">
-        <v>10</v>
-      </c>
-      <c r="AW54">
-        <v>6.6</v>
       </c>
       <c r="AX54">
         <v>18.5</v>
       </c>
       <c r="AY54">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AZ54">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA54">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="BB54">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BC54">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="BD54">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BE54">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="BF54">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="BG54">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BH54">
         <v>2.92</v>
@@ -14094,7 +14094,7 @@
         <v>5.4</v>
       </c>
       <c r="BU54">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV54">
         <v>24</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
@@ -661,7 +661,7 @@
     <t>Juventude</t>
   </si>
   <si>
-    <t>2026-09-01 00:10:39</t>
+    <t>2026-09-01 02:23:02</t>
   </si>
 </sst>
 </file>
@@ -1255,31 +1255,31 @@
         <v>167</v>
       </c>
       <c r="F2">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G2">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="H2">
         <v>2.9</v>
       </c>
       <c r="I2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
         <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
         <v>1.38</v>
@@ -1288,16 +1288,16 @@
         <v>1.78</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R2">
         <v>1.3</v>
       </c>
       <c r="S2">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="U2">
         <v>2.06</v>
@@ -1306,10 +1306,10 @@
         <v>1.47</v>
       </c>
       <c r="W2">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y2">
         <v>11.5</v>
@@ -1324,7 +1324,7 @@
         <v>10.5</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
         <v>14</v>
@@ -1333,7 +1333,7 @@
         <v>38</v>
       </c>
       <c r="AF2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG2">
         <v>13</v>
@@ -1357,10 +1357,10 @@
         <v>580</v>
       </c>
       <c r="AN2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
@@ -1396,37 +1396,37 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB2">
         <v>28</v>
       </c>
       <c r="BC2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BG2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI2">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL2">
         <v>160</v>
@@ -1441,7 +1441,7 @@
         <v>4.8</v>
       </c>
       <c r="BP2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
@@ -1453,25 +1453,25 @@
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BU2">
         <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA2">
         <v>1.01</v>
@@ -1497,64 +1497,64 @@
         <v>168</v>
       </c>
       <c r="F3">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G3">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="H3">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="I3">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="J3">
         <v>2.56</v>
       </c>
       <c r="K3">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="M3">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="N3">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="O3">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="P3">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Q3">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="S3">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T3">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="U3">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X3">
         <v>970</v>
       </c>
       <c r="Y3">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z3">
         <v>500</v>
@@ -1563,10 +1563,10 @@
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC3">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AD3">
         <v>970</v>
@@ -1605,58 +1605,58 @@
         <v>600</v>
       </c>
       <c r="AP3">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="AQ3">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR3">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AS3">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AT3">
-        <v>1.59</v>
+        <v>5.7</v>
       </c>
       <c r="AU3">
-        <v>5.1</v>
+        <v>1.53</v>
       </c>
       <c r="AV3">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AW3">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AX3">
+        <v>1.75</v>
+      </c>
+      <c r="AY3">
+        <v>1.74</v>
+      </c>
+      <c r="AZ3">
         <v>1.87</v>
-      </c>
-      <c r="AY3">
-        <v>1.78</v>
-      </c>
-      <c r="AZ3">
-        <v>1.9</v>
       </c>
       <c r="BA3">
         <v>2.14</v>
       </c>
       <c r="BB3">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="BC3">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BD3">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="BE3">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="BF3">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="BG3">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="BH3">
         <v>2.68</v>
@@ -1739,67 +1739,67 @@
         <v>169</v>
       </c>
       <c r="F4">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="G4">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="H4">
+        <v>3.65</v>
+      </c>
+      <c r="I4">
         <v>4</v>
       </c>
-      <c r="I4">
-        <v>4.5</v>
-      </c>
       <c r="J4">
+        <v>2.82</v>
+      </c>
+      <c r="K4">
         <v>2.96</v>
       </c>
-      <c r="K4">
-        <v>3.2</v>
-      </c>
       <c r="L4">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="M4">
+        <v>1.17</v>
+      </c>
+      <c r="N4">
+        <v>2.32</v>
+      </c>
+      <c r="O4">
+        <v>1.71</v>
+      </c>
+      <c r="P4">
+        <v>1.41</v>
+      </c>
+      <c r="Q4">
+        <v>3.25</v>
+      </c>
+      <c r="R4">
         <v>1.14</v>
       </c>
-      <c r="N4">
-        <v>2.44</v>
-      </c>
-      <c r="O4">
-        <v>1.6</v>
-      </c>
-      <c r="P4">
-        <v>1.47</v>
-      </c>
-      <c r="Q4">
-        <v>2.82</v>
-      </c>
-      <c r="R4">
-        <v>1.17</v>
-      </c>
       <c r="S4">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="T4">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="U4">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="V4">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="X4">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Z4">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AA4">
         <v>900</v>
@@ -1814,13 +1814,13 @@
         <v>22</v>
       </c>
       <c r="AE4">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AF4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="AH4">
         <v>32</v>
@@ -1829,10 +1829,10 @@
         <v>500</v>
       </c>
       <c r="AJ4">
+        <v>46</v>
+      </c>
+      <c r="AK4">
         <v>42</v>
-      </c>
-      <c r="AK4">
-        <v>55</v>
       </c>
       <c r="AL4">
         <v>170</v>
@@ -1841,25 +1841,25 @@
         <v>500</v>
       </c>
       <c r="AN4">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AO4">
         <v>600</v>
       </c>
       <c r="AP4">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AS4">
-        <v>70</v>
+        <v>9.6</v>
       </c>
       <c r="AT4">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU4">
         <v>6.4</v>
@@ -1868,88 +1868,88 @@
         <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX4">
         <v>11</v>
       </c>
       <c r="AY4">
+        <v>11</v>
+      </c>
+      <c r="AZ4">
+        <v>24</v>
+      </c>
+      <c r="BA4">
+        <v>9.6</v>
+      </c>
+      <c r="BB4">
+        <v>29</v>
+      </c>
+      <c r="BC4">
+        <v>24</v>
+      </c>
+      <c r="BD4">
+        <v>26</v>
+      </c>
+      <c r="BE4">
         <v>10.5</v>
       </c>
-      <c r="AZ4">
-        <v>22</v>
-      </c>
-      <c r="BA4">
-        <v>55</v>
-      </c>
-      <c r="BB4">
-        <v>23</v>
-      </c>
-      <c r="BC4">
-        <v>23</v>
-      </c>
-      <c r="BD4">
-        <v>42</v>
-      </c>
-      <c r="BE4">
-        <v>65</v>
-      </c>
       <c r="BF4">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BG4">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="BH4">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="BI4">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="BJ4">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
         <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BO4">
         <v>4.3</v>
       </c>
       <c r="BP4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU4">
         <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BY4">
         <v>1.01</v>
@@ -1984,55 +1984,55 @@
         <v>2.7</v>
       </c>
       <c r="G5">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="H5">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J5">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K5">
         <v>3.3</v>
       </c>
       <c r="L5">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="M5">
         <v>1.12</v>
       </c>
       <c r="N5">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O5">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P5">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q5">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="R5">
         <v>1.2</v>
       </c>
       <c r="S5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="T5">
         <v>2.12</v>
       </c>
       <c r="U5">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X5">
         <v>10.5</v>
@@ -2050,7 +2050,7 @@
         <v>8.4</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
         <v>14.5</v>
@@ -2068,7 +2068,7 @@
         <v>27</v>
       </c>
       <c r="AI5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ5">
         <v>55</v>
@@ -2089,19 +2089,19 @@
         <v>70</v>
       </c>
       <c r="AP5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ5">
         <v>7.4</v>
       </c>
       <c r="AR5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU5">
         <v>6.4</v>
@@ -2110,40 +2110,40 @@
         <v>12</v>
       </c>
       <c r="AW5">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AX5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY5">
         <v>11.5</v>
       </c>
       <c r="AZ5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA5">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BC5">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BD5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BE5">
         <v>100</v>
       </c>
       <c r="BF5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BG5">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BH5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI5">
         <v>2.2</v>
@@ -2161,7 +2161,7 @@
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO5">
         <v>4.9</v>
@@ -2185,10 +2185,10 @@
         <v>5.2</v>
       </c>
       <c r="BV5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX5">
         <v>55</v>
@@ -2223,91 +2223,91 @@
         <v>171</v>
       </c>
       <c r="F6">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G6">
         <v>2.86</v>
       </c>
       <c r="H6">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I6">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L6">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M6">
         <v>1.09</v>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
         <v>1.38</v>
       </c>
       <c r="P6">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q6">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S6">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T6">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="U6">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V6">
         <v>1.45</v>
       </c>
       <c r="W6">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA6">
         <v>60</v>
       </c>
       <c r="AB6">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC6">
         <v>7.6</v>
       </c>
       <c r="AD6">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE6">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF6">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AG6">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI6">
         <v>65</v>
@@ -2316,76 +2316,76 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AL6">
         <v>60</v>
       </c>
       <c r="AM6">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AN6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO6">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP6">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ6">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="AR6">
-        <v>4.6</v>
+        <v>14</v>
       </c>
       <c r="AS6">
-        <v>5.3</v>
+        <v>22</v>
       </c>
       <c r="AT6">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="AU6">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AV6">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AW6">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="AX6">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY6">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>4.6</v>
+        <v>14</v>
       </c>
       <c r="BA6">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="BB6">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="BC6">
-        <v>5.1</v>
+        <v>15</v>
       </c>
       <c r="BD6">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="BE6">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="BF6">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="BG6">
-        <v>5.2</v>
+        <v>15.5</v>
       </c>
       <c r="BH6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI6">
         <v>2.56</v>
@@ -2406,7 +2406,7 @@
         <v>6.4</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP6">
         <v>26</v>
@@ -2424,7 +2424,7 @@
         <v>6.8</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV6">
         <v>29</v>
@@ -2433,13 +2433,13 @@
         <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY6">
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2465,97 +2465,97 @@
         <v>172</v>
       </c>
       <c r="F7">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G7">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H7">
         <v>3.2</v>
       </c>
       <c r="I7">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J7">
         <v>3.25</v>
       </c>
       <c r="K7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L7">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S7">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T7">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="U7">
         <v>1.97</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="X7">
         <v>13.5</v>
       </c>
       <c r="Y7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z7">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA7">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AB7">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC7">
         <v>8</v>
       </c>
       <c r="AD7">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE7">
-        <v>55</v>
+        <v>230</v>
       </c>
       <c r="AF7">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI7">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AJ7">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AK7">
         <v>34</v>
@@ -2567,121 +2567,121 @@
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO7">
         <v>60</v>
       </c>
       <c r="AP7">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="AQ7">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="AR7">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AS7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT7">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="AU7">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="AV7">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW7">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AX7">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY7">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="AZ7">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB7">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC7">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD7">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE7">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF7">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BG7">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK7">
         <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM7">
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO7">
         <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ7">
         <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS7">
         <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU7">
         <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW7">
         <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY7">
         <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA7">
         <v>1.01</v>
@@ -2707,13 +2707,13 @@
         <v>173</v>
       </c>
       <c r="F8">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G8">
         <v>2.1</v>
       </c>
       <c r="H8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I8">
         <v>5.2</v>
@@ -2725,13 +2725,13 @@
         <v>3.6</v>
       </c>
       <c r="L8">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
         <v>1.1</v>
       </c>
       <c r="N8">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O8">
         <v>1.44</v>
@@ -2746,16 +2746,16 @@
         <v>1.23</v>
       </c>
       <c r="S8">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="T8">
         <v>2.02</v>
       </c>
       <c r="U8">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V8">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W8">
         <v>1.9</v>
@@ -2773,7 +2773,7 @@
         <v>900</v>
       </c>
       <c r="AB8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC8">
         <v>8.199999999999999</v>
@@ -2782,10 +2782,10 @@
         <v>21</v>
       </c>
       <c r="AE8">
-        <v>190</v>
+        <v>470</v>
       </c>
       <c r="AF8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG8">
         <v>11.5</v>
@@ -2812,7 +2812,7 @@
         <v>22</v>
       </c>
       <c r="AO8">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP8">
         <v>9</v>
@@ -2824,7 +2824,7 @@
         <v>14.5</v>
       </c>
       <c r="AS8">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT8">
         <v>6.2</v>
@@ -2833,43 +2833,43 @@
         <v>6.6</v>
       </c>
       <c r="AV8">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AW8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX8">
+        <v>8.6</v>
+      </c>
+      <c r="AY8">
+        <v>9</v>
+      </c>
+      <c r="AZ8">
+        <v>17</v>
+      </c>
+      <c r="BA8">
+        <v>8.4</v>
+      </c>
+      <c r="BB8">
+        <v>18</v>
+      </c>
+      <c r="BC8">
+        <v>19</v>
+      </c>
+      <c r="BD8">
         <v>7.8</v>
       </c>
-      <c r="AX8">
-        <v>9.4</v>
-      </c>
-      <c r="AY8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8">
-        <v>19</v>
-      </c>
-      <c r="BA8">
-        <v>7.8</v>
-      </c>
-      <c r="BB8">
-        <v>20</v>
-      </c>
-      <c r="BC8">
-        <v>21</v>
-      </c>
-      <c r="BD8">
-        <v>7.4</v>
-      </c>
       <c r="BE8">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG8">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI8">
         <v>2.46</v>
@@ -2887,7 +2887,7 @@
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO8">
         <v>3.6</v>
@@ -2908,7 +2908,7 @@
         <v>9</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV8">
         <v>55</v>
@@ -2917,7 +2917,7 @@
         <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY8">
         <v>1.01</v>
@@ -2949,136 +2949,136 @@
         <v>174</v>
       </c>
       <c r="F9">
+        <v>2.32</v>
+      </c>
+      <c r="G9">
+        <v>2.42</v>
+      </c>
+      <c r="H9">
+        <v>3.85</v>
+      </c>
+      <c r="I9">
+        <v>4.2</v>
+      </c>
+      <c r="J9">
+        <v>2.92</v>
+      </c>
+      <c r="K9">
+        <v>3.15</v>
+      </c>
+      <c r="L9">
+        <v>1.65</v>
+      </c>
+      <c r="M9">
+        <v>1.15</v>
+      </c>
+      <c r="N9">
+        <v>2.5</v>
+      </c>
+      <c r="O9">
+        <v>1.64</v>
+      </c>
+      <c r="P9">
+        <v>1.47</v>
+      </c>
+      <c r="Q9">
+        <v>3</v>
+      </c>
+      <c r="R9">
+        <v>1.16</v>
+      </c>
+      <c r="S9">
+        <v>6.4</v>
+      </c>
+      <c r="T9">
         <v>2.26</v>
       </c>
-      <c r="G9">
-        <v>2.4</v>
-      </c>
-      <c r="H9">
-        <v>3.8</v>
-      </c>
-      <c r="I9">
-        <v>4.1</v>
-      </c>
-      <c r="J9">
-        <v>3.05</v>
-      </c>
-      <c r="K9">
-        <v>3.3</v>
-      </c>
-      <c r="L9">
-        <v>1.44</v>
-      </c>
-      <c r="M9">
-        <v>1.12</v>
-      </c>
-      <c r="N9">
-        <v>2.72</v>
-      </c>
-      <c r="O9">
-        <v>1.52</v>
-      </c>
-      <c r="P9">
-        <v>1.56</v>
-      </c>
-      <c r="Q9">
-        <v>2.56</v>
-      </c>
-      <c r="R9">
-        <v>1.21</v>
-      </c>
-      <c r="S9">
-        <v>5.1</v>
-      </c>
-      <c r="T9">
-        <v>2.08</v>
-      </c>
       <c r="U9">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="V9">
         <v>1.32</v>
       </c>
       <c r="W9">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="Y9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AA9">
         <v>900</v>
       </c>
       <c r="AB9">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD9">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AE9">
-        <v>70</v>
+        <v>440</v>
       </c>
       <c r="AF9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH9">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AI9">
-        <v>200</v>
+        <v>540</v>
       </c>
       <c r="AJ9">
         <v>75</v>
       </c>
       <c r="AK9">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AL9">
-        <v>70</v>
+        <v>450</v>
       </c>
       <c r="AM9">
         <v>500</v>
       </c>
       <c r="AN9">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AO9">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP9">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ9">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR9">
         <v>19.5</v>
       </c>
       <c r="AS9">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="AT9">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AU9">
         <v>6.4</v>
       </c>
       <c r="AV9">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AW9">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="AX9">
         <v>10.5</v>
@@ -3087,10 +3087,10 @@
         <v>10</v>
       </c>
       <c r="AZ9">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BA9">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="BB9">
         <v>28</v>
@@ -3099,73 +3099,73 @@
         <v>27</v>
       </c>
       <c r="BD9">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="BE9">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="BF9">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="BG9">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK9">
         <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="BM9">
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ9">
         <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS9">
         <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW9">
         <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY9">
         <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA9">
         <v>1.01</v>
@@ -3191,28 +3191,28 @@
         <v>175</v>
       </c>
       <c r="F10">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G10">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H10">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="I10">
-        <v>8.6</v>
+        <v>2.88</v>
       </c>
       <c r="J10">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K10">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
         <v>3.75</v>
@@ -3224,13 +3224,13 @@
         <v>2.02</v>
       </c>
       <c r="Q10">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="R10">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3239,10 +3239,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W10">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="X10">
         <v>500</v>
@@ -3260,7 +3260,7 @@
         <v>500</v>
       </c>
       <c r="AC10">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AD10">
         <v>970</v>
@@ -3290,13 +3290,13 @@
         <v>500</v>
       </c>
       <c r="AM10">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN10">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO10">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10">
         <v>1.01</v>
@@ -3433,58 +3433,58 @@
         <v>176</v>
       </c>
       <c r="F11">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G11">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J11">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K11">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M11">
         <v>1.05</v>
       </c>
       <c r="N11">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P11">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q11">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R11">
         <v>1.52</v>
       </c>
       <c r="S11">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="T11">
         <v>1.62</v>
       </c>
       <c r="U11">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="V11">
         <v>1.41</v>
       </c>
       <c r="W11">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X11">
         <v>21</v>
@@ -3499,10 +3499,10 @@
         <v>60</v>
       </c>
       <c r="AB11">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC11">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD11">
         <v>15</v>
@@ -3511,7 +3511,7 @@
         <v>36</v>
       </c>
       <c r="AF11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG11">
         <v>12</v>
@@ -3523,10 +3523,10 @@
         <v>40</v>
       </c>
       <c r="AJ11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL11">
         <v>32</v>
@@ -3535,13 +3535,13 @@
         <v>65</v>
       </c>
       <c r="AN11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO11">
         <v>27</v>
       </c>
       <c r="AP11">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AQ11">
         <v>14</v>
@@ -3556,7 +3556,7 @@
         <v>10.5</v>
       </c>
       <c r="AU11">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV11">
         <v>12</v>
@@ -3574,7 +3574,7 @@
         <v>13</v>
       </c>
       <c r="BA11">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BB11">
         <v>21</v>
@@ -3583,16 +3583,16 @@
         <v>18</v>
       </c>
       <c r="BD11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE11">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="BF11">
         <v>11</v>
       </c>
       <c r="BG11">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3675,31 +3675,31 @@
         <v>177</v>
       </c>
       <c r="F12">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="G12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H12">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="I12">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="J12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L12">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M12">
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O12">
         <v>1.2</v>
@@ -3708,22 +3708,22 @@
         <v>2.46</v>
       </c>
       <c r="Q12">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R12">
         <v>1.58</v>
       </c>
       <c r="S12">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="T12">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="V12">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="W12">
         <v>1.18</v>
@@ -3738,10 +3738,10 @@
         <v>13.5</v>
       </c>
       <c r="AA12">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AB12">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AC12">
         <v>11</v>
@@ -3750,7 +3750,7 @@
         <v>10.5</v>
       </c>
       <c r="AE12">
-        <v>65</v>
+        <v>15.5</v>
       </c>
       <c r="AF12">
         <v>220</v>
@@ -3768,7 +3768,7 @@
         <v>700</v>
       </c>
       <c r="AK12">
-        <v>170</v>
+        <v>400</v>
       </c>
       <c r="AL12">
         <v>160</v>
@@ -3777,25 +3777,25 @@
         <v>500</v>
       </c>
       <c r="AN12">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AO12">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AP12">
         <v>20</v>
       </c>
       <c r="AQ12">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR12">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AS12">
         <v>13.5</v>
       </c>
       <c r="AT12">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AU12">
         <v>9.6</v>
@@ -3804,37 +3804,37 @@
         <v>9</v>
       </c>
       <c r="AW12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX12">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AY12">
         <v>20</v>
       </c>
       <c r="AZ12">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BA12">
-        <v>24</v>
+        <v>6.4</v>
       </c>
       <c r="BB12">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC12">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BD12">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BE12">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF12">
+        <v>7.4</v>
+      </c>
+      <c r="BG12">
         <v>5.9</v>
-      </c>
-      <c r="BG12">
-        <v>5.1</v>
       </c>
       <c r="BH12">
         <v>4.9</v>
@@ -3843,10 +3843,10 @@
         <v>3.35</v>
       </c>
       <c r="BJ12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL12">
         <v>120</v>
@@ -3855,7 +3855,7 @@
         <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BO12">
         <v>1.01</v>
@@ -3879,7 +3879,7 @@
         <v>3.95</v>
       </c>
       <c r="BV12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BW12">
         <v>1.01</v>
@@ -3920,67 +3920,67 @@
         <v>2.32</v>
       </c>
       <c r="G13">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H13">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I13">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J13">
         <v>3.45</v>
       </c>
       <c r="K13">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L13">
+        <v>1.44</v>
+      </c>
+      <c r="M13">
+        <v>1.07</v>
+      </c>
+      <c r="N13">
+        <v>3.55</v>
+      </c>
+      <c r="O13">
         <v>1.35</v>
       </c>
-      <c r="M13">
-        <v>1.06</v>
-      </c>
-      <c r="N13">
-        <v>3.6</v>
-      </c>
-      <c r="O13">
+      <c r="P13">
+        <v>1.88</v>
+      </c>
+      <c r="Q13">
+        <v>2.06</v>
+      </c>
+      <c r="R13">
         <v>1.34</v>
       </c>
-      <c r="P13">
-        <v>1.89</v>
-      </c>
-      <c r="Q13">
-        <v>2</v>
-      </c>
-      <c r="R13">
-        <v>1.35</v>
-      </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T13">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U13">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
         <v>1.67</v>
       </c>
       <c r="X13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z13">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA13">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AB13">
         <v>10.5</v>
@@ -3989,64 +3989,64 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE13">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AF13">
         <v>16</v>
       </c>
       <c r="AG13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH13">
         <v>19</v>
       </c>
       <c r="AI13">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AJ13">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AK13">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AL13">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AM13">
         <v>580</v>
       </c>
       <c r="AN13">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AO13">
         <v>48</v>
       </c>
       <c r="AP13">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AQ13">
         <v>10</v>
       </c>
       <c r="AR13">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS13">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AT13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU13">
         <v>6.8</v>
       </c>
       <c r="AV13">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW13">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="AX13">
         <v>13</v>
@@ -4055,28 +4055,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA13">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="BB13">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BC13">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD13">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BE13">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="BF13">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BG13">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="BH13">
         <v>3.4</v>
@@ -4097,19 +4097,19 @@
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO13">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ13">
         <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS13">
         <v>1.01</v>
@@ -4118,16 +4118,16 @@
         <v>7.8</v>
       </c>
       <c r="BU13">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV13">
         <v>34</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX13">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY13">
         <v>1.01</v>
@@ -4159,31 +4159,31 @@
         <v>179</v>
       </c>
       <c r="F14">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G14">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="H14">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="I14">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="J14">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K14">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>1.14</v>
@@ -4192,13 +4192,13 @@
         <v>3</v>
       </c>
       <c r="Q14">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R14">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="S14">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="T14">
         <v>1.42</v>
@@ -4207,10 +4207,10 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="W14">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X14">
         <v>500</v>
@@ -4261,58 +4261,58 @@
         <v>580</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AO14">
         <v>55</v>
       </c>
       <c r="AP14">
+        <v>1.68</v>
+      </c>
+      <c r="AQ14">
+        <v>1.62</v>
+      </c>
+      <c r="AR14">
+        <v>1.62</v>
+      </c>
+      <c r="AS14">
         <v>1.67</v>
       </c>
-      <c r="AQ14">
-        <v>1.61</v>
-      </c>
-      <c r="AR14">
-        <v>1.6</v>
-      </c>
-      <c r="AS14">
-        <v>1.66</v>
-      </c>
       <c r="AT14">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AU14">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AV14">
         <v>6.2</v>
       </c>
       <c r="AW14">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AX14">
+        <v>1.7</v>
+      </c>
+      <c r="AY14">
         <v>1.69</v>
       </c>
-      <c r="AY14">
-        <v>1.68</v>
-      </c>
       <c r="AZ14">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BA14">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="BB14">
+        <v>1.71</v>
+      </c>
+      <c r="BC14">
         <v>1.7</v>
       </c>
-      <c r="BC14">
-        <v>1.69</v>
-      </c>
       <c r="BD14">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BE14">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BF14">
         <v>1.7</v>
@@ -4401,67 +4401,67 @@
         <v>180</v>
       </c>
       <c r="F15">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G15">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="H15">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="I15">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K15">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="O15">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P15">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="Q15">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="R15">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="S15">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="T15">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="U15">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="V15">
         <v>1.58</v>
       </c>
       <c r="W15">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X15">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="Y15">
         <v>22</v>
       </c>
       <c r="Z15">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AA15">
         <v>85</v>
@@ -4470,7 +4470,7 @@
         <v>22</v>
       </c>
       <c r="AC15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD15">
         <v>13.5</v>
@@ -4479,7 +4479,7 @@
         <v>60</v>
       </c>
       <c r="AF15">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AG15">
         <v>16</v>
@@ -4488,10 +4488,10 @@
         <v>17.5</v>
       </c>
       <c r="AI15">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AJ15">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK15">
         <v>29</v>
@@ -4503,25 +4503,25 @@
         <v>60</v>
       </c>
       <c r="AN15">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO15">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP15">
         <v>21</v>
       </c>
       <c r="AQ15">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR15">
         <v>18.5</v>
       </c>
       <c r="AS15">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT15">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AU15">
         <v>9.199999999999999</v>
@@ -4539,7 +4539,7 @@
         <v>11</v>
       </c>
       <c r="AZ15">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA15">
         <v>20</v>
@@ -4554,70 +4554,70 @@
         <v>19.5</v>
       </c>
       <c r="BE15">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="BF15">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH15">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BI15">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BJ15">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL15">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BM15">
         <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO15">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ15">
         <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BS15">
         <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU15">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW15">
         <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BY15">
         <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CA15">
         <v>1.01</v>
@@ -4643,76 +4643,76 @@
         <v>181</v>
       </c>
       <c r="F16">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G16">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="H16">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="I16">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L16">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N16">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q16">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="R16">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S16">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="T16">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="U16">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="V16">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="W16">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="X16">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Y16">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Z16">
         <v>21</v>
       </c>
       <c r="AA16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB16">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AC16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD16">
         <v>12.5</v>
@@ -4721,34 +4721,34 @@
         <v>24</v>
       </c>
       <c r="AF16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH16">
         <v>15.5</v>
       </c>
       <c r="AI16">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AJ16">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK16">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL16">
         <v>32</v>
       </c>
       <c r="AM16">
-        <v>55</v>
+        <v>580</v>
       </c>
       <c r="AN16">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP16">
         <v>20</v>
@@ -4763,10 +4763,10 @@
         <v>16</v>
       </c>
       <c r="AT16">
-        <v>15.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU16">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV16">
         <v>9</v>
@@ -4787,7 +4787,7 @@
         <v>18.5</v>
       </c>
       <c r="BB16">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC16">
         <v>19</v>
@@ -4796,7 +4796,7 @@
         <v>20</v>
       </c>
       <c r="BE16">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF16">
         <v>11.5</v>
@@ -4885,67 +4885,67 @@
         <v>182</v>
       </c>
       <c r="F17">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="G17">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="H17">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J17">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K17">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L17">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O17">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P17">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="Q17">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="R17">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="S17">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="T17">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="U17">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="V17">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W17">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="X17">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Y17">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="Z17">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA17">
         <v>700</v>
@@ -4954,13 +4954,13 @@
         <v>16</v>
       </c>
       <c r="AC17">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD17">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE17">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF17">
         <v>14.5</v>
@@ -4969,10 +4969,10 @@
         <v>11.5</v>
       </c>
       <c r="AH17">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI17">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ17">
         <v>19</v>
@@ -4984,25 +4984,25 @@
         <v>25</v>
       </c>
       <c r="AM17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN17">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AO17">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AP17">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR17">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AS17">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT17">
         <v>12.5</v>
@@ -5011,7 +5011,7 @@
         <v>10</v>
       </c>
       <c r="AV17">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW17">
         <v>23</v>
@@ -5026,7 +5026,7 @@
         <v>14</v>
       </c>
       <c r="BA17">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BB17">
         <v>15</v>
@@ -5038,25 +5038,25 @@
         <v>19.5</v>
       </c>
       <c r="BE17">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF17">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BG17">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BH17">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BI17">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ17">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK17">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL17">
         <v>85</v>
@@ -5068,43 +5068,43 @@
         <v>5.1</v>
       </c>
       <c r="BO17">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BQ17">
         <v>7.6</v>
       </c>
       <c r="BR17">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BS17">
         <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BV17">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BW17">
         <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BY17">
         <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB17" t="s">
         <v>215</v>
@@ -5127,58 +5127,58 @@
         <v>183</v>
       </c>
       <c r="F18">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G18">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="H18">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="I18">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="J18">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="K18">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="L18">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="M18">
         <v>1.12</v>
       </c>
       <c r="N18">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="O18">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="P18">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="Q18">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="R18">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S18">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="T18">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V18">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="X18">
         <v>970</v>
@@ -5193,7 +5193,7 @@
         <v>900</v>
       </c>
       <c r="AB18">
-        <v>16.5</v>
+        <v>500</v>
       </c>
       <c r="AC18">
         <v>42</v>
@@ -5235,58 +5235,58 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AQ18">
         <v>5.7</v>
       </c>
       <c r="AR18">
-        <v>1.79</v>
+        <v>2.24</v>
       </c>
       <c r="AS18">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AT18">
-        <v>5.7</v>
+        <v>1.51</v>
       </c>
       <c r="AU18">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AV18">
         <v>1.76</v>
       </c>
       <c r="AW18">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AX18">
-        <v>1.73</v>
+        <v>2.22</v>
       </c>
       <c r="AY18">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="AZ18">
-        <v>2.18</v>
+        <v>18</v>
       </c>
       <c r="BA18">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BB18">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="BC18">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BD18">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BE18">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="BF18">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BG18">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5369,127 +5369,127 @@
         <v>184</v>
       </c>
       <c r="F19">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="G19">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="H19">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I19">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="J19">
         <v>4.7</v>
       </c>
       <c r="K19">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L19">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="M19">
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="O19">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P19">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q19">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="R19">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="S19">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T19">
         <v>1.25</v>
       </c>
       <c r="U19">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="V19">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W19">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X19">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="Y19">
+        <v>44</v>
+      </c>
+      <c r="Z19">
+        <v>60</v>
+      </c>
+      <c r="AA19">
         <v>90</v>
       </c>
-      <c r="Z19">
-        <v>65</v>
-      </c>
-      <c r="AA19">
-        <v>42</v>
-      </c>
       <c r="AB19">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AC19">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AD19">
         <v>17</v>
       </c>
       <c r="AE19">
+        <v>21</v>
+      </c>
+      <c r="AF19">
+        <v>55</v>
+      </c>
+      <c r="AG19">
         <v>22</v>
-      </c>
-      <c r="AF19">
-        <v>50</v>
-      </c>
-      <c r="AG19">
-        <v>19.5</v>
       </c>
       <c r="AH19">
         <v>15</v>
       </c>
       <c r="AI19">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AJ19">
         <v>120</v>
       </c>
       <c r="AK19">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AL19">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AM19">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN19">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AO19">
         <v>5.6</v>
       </c>
       <c r="AP19">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="AQ19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR19">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AS19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT19">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AU19">
         <v>16</v>
@@ -5498,22 +5498,22 @@
         <v>14</v>
       </c>
       <c r="AW19">
+        <v>17</v>
+      </c>
+      <c r="AX19">
+        <v>26</v>
+      </c>
+      <c r="AY19">
         <v>17.5</v>
-      </c>
-      <c r="AX19">
-        <v>25</v>
-      </c>
-      <c r="AY19">
-        <v>16.5</v>
       </c>
       <c r="AZ19">
         <v>12</v>
       </c>
       <c r="BA19">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BB19">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC19">
         <v>22</v>
@@ -5522,19 +5522,19 @@
         <v>18.5</v>
       </c>
       <c r="BE19">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BF19">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG19">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BH19">
         <v>9.199999999999999</v>
       </c>
       <c r="BI19">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
         <v>8.6</v>
@@ -5543,7 +5543,7 @@
         <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BM19">
         <v>1.01</v>
@@ -5561,7 +5561,7 @@
         <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS19">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
         <v>14.5</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX19">
         <v>15.5</v>
@@ -5611,112 +5611,112 @@
         <v>185</v>
       </c>
       <c r="F20">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="G20">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="H20">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="I20">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="J20">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K20">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L20">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M20">
         <v>1.04</v>
       </c>
       <c r="N20">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="O20">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P20">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="Q20">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R20">
+        <v>1.68</v>
+      </c>
+      <c r="S20">
+        <v>2.4</v>
+      </c>
+      <c r="T20">
         <v>1.62</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>2.44</v>
       </c>
-      <c r="T20">
-        <v>1.61</v>
-      </c>
-      <c r="U20">
-        <v>2.46</v>
-      </c>
       <c r="V20">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="W20">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="X20">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Y20">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z20">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA20">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AB20">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AC20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD20">
         <v>10.5</v>
       </c>
       <c r="AE20">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AF20">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AG20">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AH20">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI20">
         <v>26</v>
       </c>
       <c r="AJ20">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AK20">
         <v>60</v>
       </c>
       <c r="AL20">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM20">
         <v>75</v>
       </c>
       <c r="AN20">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AO20">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AP20">
         <v>19</v>
@@ -5725,37 +5725,37 @@
         <v>11</v>
       </c>
       <c r="AR20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS20">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AT20">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV20">
         <v>9</v>
       </c>
       <c r="AW20">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX20">
         <v>32</v>
       </c>
       <c r="AY20">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ20">
         <v>14</v>
       </c>
       <c r="BA20">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB20">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BC20">
         <v>36</v>
@@ -5764,22 +5764,22 @@
         <v>34</v>
       </c>
       <c r="BE20">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BF20">
         <v>22</v>
       </c>
       <c r="BG20">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BH20">
         <v>5</v>
       </c>
       <c r="BI20">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BJ20">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK20">
         <v>7</v>
@@ -5791,46 +5791,46 @@
         <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BP20">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ20">
         <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BS20">
         <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BU20">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BV20">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BW20">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BX20">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BY20">
         <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB20" t="s">
         <v>215</v>
@@ -5856,163 +5856,163 @@
         <v>12.5</v>
       </c>
       <c r="G21">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21">
         <v>1.33</v>
       </c>
       <c r="I21">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="J21">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K21">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M21">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N21">
-        <v>2.64</v>
+        <v>3.7</v>
       </c>
       <c r="O21">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P21">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="Q21">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="R21">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S21">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T21">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="U21">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="V21">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="W21">
         <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y21">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AA21">
-        <v>900</v>
+        <v>12</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC21">
-        <v>95</v>
+        <v>13.5</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ21">
         <v>1000</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AN21">
         <v>1000</v>
       </c>
       <c r="AO21">
-        <v>29</v>
+        <v>7.2</v>
       </c>
       <c r="AP21">
-        <v>1.23</v>
+        <v>11.5</v>
       </c>
       <c r="AQ21">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AR21">
-        <v>1.23</v>
+        <v>5.9</v>
       </c>
       <c r="AS21">
-        <v>2.52</v>
+        <v>8.4</v>
       </c>
       <c r="AT21">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU21">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AV21">
-        <v>1.23</v>
+        <v>9.4</v>
       </c>
       <c r="AW21">
-        <v>1.23</v>
+        <v>14.5</v>
       </c>
       <c r="AX21">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="AY21">
-        <v>2.5</v>
+        <v>32</v>
       </c>
       <c r="AZ21">
-        <v>1.23</v>
+        <v>21</v>
       </c>
       <c r="BA21">
-        <v>1.23</v>
+        <v>21</v>
       </c>
       <c r="BB21">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC21">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD21">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE21">
-        <v>1.23</v>
+        <v>6.2</v>
       </c>
       <c r="BF21">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG21">
-        <v>2.18</v>
+        <v>6</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6095,46 +6095,46 @@
         <v>187</v>
       </c>
       <c r="F22">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G22">
         <v>2.44</v>
       </c>
       <c r="H22">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I22">
         <v>3.9</v>
       </c>
       <c r="J22">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K22">
         <v>3.65</v>
       </c>
       <c r="L22">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="M22">
         <v>1.08</v>
       </c>
       <c r="N22">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O22">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="P22">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q22">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R22">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S22">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="T22">
         <v>1.73</v>
@@ -6143,118 +6143,118 @@
         <v>2.02</v>
       </c>
       <c r="V22">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W22">
         <v>1.69</v>
       </c>
       <c r="X22">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y22">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z22">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AA22">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AB22">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AC22">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD22">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE22">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AF22">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AG22">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH22">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AI22">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AJ22">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AK22">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AL22">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AM22">
-        <v>580</v>
+        <v>440</v>
       </c>
       <c r="AN22">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AO22">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AP22">
-        <v>1.69</v>
+        <v>4.3</v>
       </c>
       <c r="AQ22">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="AR22">
-        <v>1.78</v>
+        <v>5.2</v>
       </c>
       <c r="AS22">
-        <v>1.84</v>
+        <v>5.9</v>
       </c>
       <c r="AT22">
+        <v>3.8</v>
+      </c>
+      <c r="AU22">
+        <v>3.5</v>
+      </c>
+      <c r="AV22">
+        <v>4.5</v>
+      </c>
+      <c r="AW22">
+        <v>5.7</v>
+      </c>
+      <c r="AX22">
+        <v>4.6</v>
+      </c>
+      <c r="AY22">
+        <v>4.2</v>
+      </c>
+      <c r="AZ22">
+        <v>4.9</v>
+      </c>
+      <c r="BA22">
+        <v>5.8</v>
+      </c>
+      <c r="BB22">
+        <v>5.4</v>
+      </c>
+      <c r="BC22">
+        <v>5.1</v>
+      </c>
+      <c r="BD22">
         <v>5.6</v>
       </c>
-      <c r="AU22">
-        <v>1.63</v>
-      </c>
-      <c r="AV22">
-        <v>1.74</v>
-      </c>
-      <c r="AW22">
-        <v>1.82</v>
-      </c>
-      <c r="AX22">
-        <v>1.76</v>
-      </c>
-      <c r="AY22">
-        <v>1.71</v>
-      </c>
-      <c r="AZ22">
-        <v>1.79</v>
-      </c>
-      <c r="BA22">
-        <v>1.83</v>
-      </c>
-      <c r="BB22">
-        <v>1.81</v>
-      </c>
-      <c r="BC22">
-        <v>1.81</v>
-      </c>
-      <c r="BD22">
-        <v>1.82</v>
-      </c>
       <c r="BE22">
-        <v>1.84</v>
+        <v>6</v>
       </c>
       <c r="BF22">
-        <v>1.79</v>
+        <v>5.1</v>
       </c>
       <c r="BG22">
-        <v>1.81</v>
+        <v>5.7</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6337,73 +6337,73 @@
         <v>188</v>
       </c>
       <c r="F23">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G23">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J23">
         <v>4.4</v>
       </c>
       <c r="K23">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M23">
         <v>1.03</v>
       </c>
       <c r="N23">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O23">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P23">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="Q23">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="R23">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="S23">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="T23">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U23">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="V23">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W23">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="X23">
+        <v>25</v>
+      </c>
+      <c r="Y23">
         <v>34</v>
       </c>
-      <c r="Y23">
-        <v>26</v>
-      </c>
       <c r="Z23">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AA23">
         <v>120</v>
       </c>
       <c r="AB23">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC23">
         <v>11</v>
@@ -6418,16 +6418,16 @@
         <v>12.5</v>
       </c>
       <c r="AG23">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AH23">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI23">
         <v>55</v>
       </c>
       <c r="AJ23">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AK23">
         <v>15</v>
@@ -6436,25 +6436,25 @@
         <v>25</v>
       </c>
       <c r="AM23">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AN23">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO23">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP23">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AQ23">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR23">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="AS23">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="AT23">
         <v>11</v>
@@ -6463,40 +6463,40 @@
         <v>9.6</v>
       </c>
       <c r="AV23">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AW23">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX23">
         <v>11</v>
       </c>
       <c r="AY23">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA23">
-        <v>8.6</v>
+        <v>46</v>
       </c>
       <c r="BB23">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BC23">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD23">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE23">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BF23">
         <v>6.6</v>
       </c>
       <c r="BG23">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6582,127 +6582,127 @@
         <v>5.4</v>
       </c>
       <c r="G24">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H24">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="I24">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="J24">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L24">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="M24">
         <v>1.02</v>
       </c>
       <c r="N24">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P24">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="Q24">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="R24">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="S24">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="T24">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="U24">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="V24">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="W24">
         <v>1.21</v>
       </c>
       <c r="X24">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Y24">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z24">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA24">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AB24">
         <v>40</v>
       </c>
       <c r="AC24">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AD24">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE24">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF24">
         <v>60</v>
       </c>
       <c r="AG24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH24">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI24">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AJ24">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AK24">
         <v>55</v>
       </c>
       <c r="AL24">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM24">
-        <v>580</v>
+        <v>55</v>
       </c>
       <c r="AN24">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO24">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AP24">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AQ24">
+        <v>16</v>
+      </c>
+      <c r="AR24">
+        <v>13.5</v>
+      </c>
+      <c r="AS24">
         <v>16.5</v>
-      </c>
-      <c r="AR24">
-        <v>12</v>
-      </c>
-      <c r="AS24">
-        <v>17</v>
       </c>
       <c r="AT24">
         <v>16</v>
       </c>
       <c r="AU24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV24">
         <v>10</v>
@@ -6711,91 +6711,91 @@
         <v>13</v>
       </c>
       <c r="AX24">
-        <v>7.4</v>
+        <v>50</v>
       </c>
       <c r="AY24">
         <v>20</v>
       </c>
       <c r="AZ24">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA24">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB24">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BC24">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BD24">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BE24">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="BF24">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG24">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH24">
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BJ24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK24">
         <v>5.4</v>
       </c>
       <c r="BL24">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BM24">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BN24">
         <v>13.5</v>
       </c>
       <c r="BO24">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="BP24">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BQ24">
         <v>2.02</v>
       </c>
       <c r="BR24">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BS24">
         <v>2.02</v>
       </c>
       <c r="BT24">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU24">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BV24">
         <v>14.5</v>
       </c>
       <c r="BW24">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="BX24">
         <v>24</v>
       </c>
       <c r="BY24">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BZ24">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA24">
         <v>1.84</v>
@@ -6821,7 +6821,7 @@
         <v>190</v>
       </c>
       <c r="F25">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G25">
         <v>1.86</v>
@@ -6830,49 +6830,49 @@
         <v>4.8</v>
       </c>
       <c r="I25">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K25">
         <v>3.95</v>
       </c>
       <c r="L25">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M25">
         <v>1.07</v>
       </c>
       <c r="N25">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O25">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P25">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q25">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R25">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S25">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T25">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U25">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V25">
         <v>1.25</v>
       </c>
       <c r="W25">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X25">
         <v>14.5</v>
@@ -6929,7 +6929,7 @@
         <v>75</v>
       </c>
       <c r="AP25">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ25">
         <v>15</v>
@@ -6983,22 +6983,22 @@
         <v>11</v>
       </c>
       <c r="BH25">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BI25">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="BJ25">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK25">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL25">
         <v>150</v>
       </c>
       <c r="BM25">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BN25">
         <v>5.3</v>
@@ -7010,37 +7010,37 @@
         <v>15</v>
       </c>
       <c r="BQ25">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BR25">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT25">
         <v>9.800000000000001</v>
       </c>
       <c r="BU25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BV25">
+        <v>42</v>
+      </c>
+      <c r="BW25">
+        <v>5.8</v>
+      </c>
+      <c r="BX25">
         <v>50</v>
       </c>
-      <c r="BW25">
-        <v>1.01</v>
-      </c>
-      <c r="BX25">
-        <v>60</v>
-      </c>
       <c r="BY25">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BZ25">
         <v>27</v>
       </c>
       <c r="CA25">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="CB25" t="s">
         <v>215</v>
@@ -7063,25 +7063,25 @@
         <v>191</v>
       </c>
       <c r="F26">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G26">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="H26">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I26">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J26">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K26">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L26">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M26">
         <v>1.05</v>
@@ -7093,28 +7093,28 @@
         <v>1.26</v>
       </c>
       <c r="P26">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q26">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R26">
         <v>1.45</v>
       </c>
       <c r="S26">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T26">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U26">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
         <v>1.25</v>
       </c>
       <c r="W26">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="X26">
         <v>22</v>
@@ -7123,7 +7123,7 @@
         <v>25</v>
       </c>
       <c r="Z26">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="AA26">
         <v>700</v>
@@ -7132,16 +7132,16 @@
         <v>12</v>
       </c>
       <c r="AC26">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD26">
         <v>18.5</v>
       </c>
       <c r="AE26">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AF26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG26">
         <v>12</v>
@@ -7156,7 +7156,7 @@
         <v>23</v>
       </c>
       <c r="AK26">
-        <v>18.5</v>
+        <v>65</v>
       </c>
       <c r="AL26">
         <v>40</v>
@@ -7165,7 +7165,7 @@
         <v>320</v>
       </c>
       <c r="AN26">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO26">
         <v>270</v>
@@ -7180,7 +7180,7 @@
         <v>18</v>
       </c>
       <c r="AS26">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AT26">
         <v>8.6</v>
@@ -7192,7 +7192,7 @@
         <v>16</v>
       </c>
       <c r="AW26">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX26">
         <v>10</v>
@@ -7204,7 +7204,7 @@
         <v>12</v>
       </c>
       <c r="BA26">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB26">
         <v>16.5</v>
@@ -7213,13 +7213,13 @@
         <v>15.5</v>
       </c>
       <c r="BD26">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE26">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BF26">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG26">
         <v>8</v>
@@ -7228,19 +7228,19 @@
         <v>4.4</v>
       </c>
       <c r="BI26">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BJ26">
         <v>12</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BL26">
         <v>140</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BN26">
         <v>5.3</v>
@@ -7249,40 +7249,40 @@
         <v>3.5</v>
       </c>
       <c r="BP26">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BR26">
         <v>30</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BT26">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV26">
         <v>48</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BX26">
         <v>55</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BZ26">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="CB26" t="s">
         <v>215</v>
@@ -7305,16 +7305,16 @@
         <v>192</v>
       </c>
       <c r="F27">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G27">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H27">
         <v>2.8</v>
       </c>
       <c r="I27">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J27">
         <v>3.55</v>
@@ -7323,34 +7323,34 @@
         <v>3.7</v>
       </c>
       <c r="L27">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M27">
         <v>1.07</v>
       </c>
       <c r="N27">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O27">
         <v>1.32</v>
       </c>
       <c r="P27">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Q27">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R27">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S27">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T27">
         <v>1.73</v>
       </c>
       <c r="U27">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V27">
         <v>1.53</v>
@@ -7476,13 +7476,13 @@
         <v>11.5</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BL27">
         <v>140</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN27">
         <v>6.8</v>
@@ -7494,13 +7494,13 @@
         <v>25</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BR27">
         <v>40</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BT27">
         <v>7.2</v>
@@ -7512,19 +7512,19 @@
         <v>27</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BX27">
         <v>42</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BZ27">
         <v>32</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="CB27" t="s">
         <v>215</v>
@@ -7553,52 +7553,52 @@
         <v>2.18</v>
       </c>
       <c r="H28">
+        <v>3.65</v>
+      </c>
+      <c r="I28">
         <v>3.75</v>
       </c>
-      <c r="I28">
-        <v>3.85</v>
-      </c>
       <c r="J28">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K28">
         <v>3.7</v>
       </c>
       <c r="L28">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M28">
         <v>1.07</v>
       </c>
       <c r="N28">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O28">
         <v>1.32</v>
       </c>
       <c r="P28">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q28">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="R28">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S28">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T28">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U28">
         <v>2.12</v>
       </c>
       <c r="V28">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="X28">
         <v>15</v>
@@ -7610,76 +7610,76 @@
         <v>27</v>
       </c>
       <c r="AA28">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB28">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC28">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE28">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AF28">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG28">
         <v>11</v>
       </c>
       <c r="AH28">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AI28">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AJ28">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK28">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL28">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AM28">
         <v>500</v>
       </c>
       <c r="AN28">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AO28">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP28">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ28">
         <v>13</v>
       </c>
       <c r="AR28">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AS28">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AT28">
         <v>8.4</v>
       </c>
       <c r="AU28">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV28">
         <v>14</v>
       </c>
       <c r="AW28">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX28">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY28">
         <v>9.4</v>
@@ -7688,10 +7688,10 @@
         <v>16</v>
       </c>
       <c r="BA28">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BB28">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC28">
         <v>20</v>
@@ -7700,73 +7700,73 @@
         <v>32</v>
       </c>
       <c r="BE28">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="BF28">
         <v>14</v>
       </c>
       <c r="BG28">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="BH28">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI28">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BJ28">
         <v>11</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL28">
         <v>140</v>
       </c>
       <c r="BM28">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BN28">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BO28">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BP28">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ28">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BR28">
+        <v>36</v>
+      </c>
+      <c r="BS28">
+        <v>5.1</v>
+      </c>
+      <c r="BT28">
+        <v>7.8</v>
+      </c>
+      <c r="BU28">
+        <v>5.4</v>
+      </c>
+      <c r="BV28">
         <v>34</v>
       </c>
-      <c r="BS28">
-        <v>1.01</v>
-      </c>
-      <c r="BT28">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU28">
-        <v>1.01</v>
-      </c>
-      <c r="BV28">
-        <v>38</v>
-      </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BX28">
         <v>48</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BZ28">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="CA28">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="CB28" t="s">
         <v>215</v>
@@ -7813,7 +7813,7 @@
         <v>1.05</v>
       </c>
       <c r="N29">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O29">
         <v>1.23</v>
@@ -7822,19 +7822,19 @@
         <v>2.38</v>
       </c>
       <c r="Q29">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R29">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="S29">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T29">
         <v>1.65</v>
       </c>
       <c r="U29">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
         <v>1.33</v>
@@ -7843,7 +7843,7 @@
         <v>2</v>
       </c>
       <c r="X29">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Y29">
         <v>19</v>
@@ -7855,7 +7855,7 @@
         <v>160</v>
       </c>
       <c r="AB29">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AC29">
         <v>9.6</v>
@@ -7867,7 +7867,7 @@
         <v>42</v>
       </c>
       <c r="AF29">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG29">
         <v>10.5</v>
@@ -7936,13 +7936,13 @@
         <v>21</v>
       </c>
       <c r="BC29">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD29">
         <v>26</v>
       </c>
       <c r="BE29">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BF29">
         <v>9.800000000000001</v>
@@ -7954,10 +7954,10 @@
         <v>4.5</v>
       </c>
       <c r="BI29">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ29">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK29">
         <v>7.2</v>
@@ -7966,7 +7966,7 @@
         <v>110</v>
       </c>
       <c r="BM29">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN29">
         <v>5</v>
@@ -7978,16 +7978,16 @@
         <v>15.5</v>
       </c>
       <c r="BQ29">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="BR29">
         <v>28</v>
       </c>
       <c r="BS29">
-        <v>1.02</v>
+        <v>6.6</v>
       </c>
       <c r="BT29">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU29">
         <v>5.9</v>
@@ -7996,19 +7996,19 @@
         <v>40</v>
       </c>
       <c r="BW29">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX29">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY29">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ29">
         <v>21</v>
       </c>
       <c r="CA29">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB29" t="s">
         <v>215</v>
@@ -8031,16 +8031,16 @@
         <v>195</v>
       </c>
       <c r="F30">
+        <v>2.68</v>
+      </c>
+      <c r="G30">
         <v>2.74</v>
       </c>
-      <c r="G30">
-        <v>2.82</v>
-      </c>
       <c r="H30">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="I30">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="J30">
         <v>3.8</v>
@@ -8049,49 +8049,49 @@
         <v>3.9</v>
       </c>
       <c r="L30">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M30">
         <v>1.05</v>
       </c>
       <c r="N30">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O30">
         <v>1.25</v>
       </c>
       <c r="P30">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q30">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R30">
         <v>1.48</v>
       </c>
       <c r="S30">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="T30">
         <v>1.64</v>
       </c>
       <c r="U30">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="V30">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W30">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="X30">
         <v>19</v>
       </c>
       <c r="Y30">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA30">
         <v>38</v>
@@ -8103,7 +8103,7 @@
         <v>11</v>
       </c>
       <c r="AD30">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE30">
         <v>25</v>
@@ -8115,13 +8115,13 @@
         <v>12.5</v>
       </c>
       <c r="AH30">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI30">
         <v>36</v>
       </c>
       <c r="AJ30">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK30">
         <v>28</v>
@@ -8133,13 +8133,13 @@
         <v>75</v>
       </c>
       <c r="AN30">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO30">
         <v>18</v>
       </c>
       <c r="AP30">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ30">
         <v>11.5</v>
@@ -8175,7 +8175,7 @@
         <v>30</v>
       </c>
       <c r="BB30">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BC30">
         <v>24</v>
@@ -8184,7 +8184,7 @@
         <v>30</v>
       </c>
       <c r="BE30">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BF30">
         <v>17</v>
@@ -8202,31 +8202,31 @@
         <v>10.5</v>
       </c>
       <c r="BK30">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BL30">
         <v>110</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BN30">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO30">
         <v>5.2</v>
       </c>
       <c r="BP30">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ30">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BR30">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS30">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BT30">
         <v>7</v>
@@ -8238,19 +8238,19 @@
         <v>23</v>
       </c>
       <c r="BW30">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BX30">
         <v>34</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BZ30">
         <v>25</v>
       </c>
       <c r="CA30">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="CB30" t="s">
         <v>215</v>
@@ -8279,7 +8279,7 @@
         <v>2.8</v>
       </c>
       <c r="H31">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I31">
         <v>2.86</v>
@@ -8291,7 +8291,7 @@
         <v>3.6</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M31">
         <v>1.07</v>
@@ -8303,19 +8303,19 @@
         <v>1.33</v>
       </c>
       <c r="P31">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R31">
         <v>1.35</v>
       </c>
       <c r="S31">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T31">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U31">
         <v>2.18</v>
@@ -8324,10 +8324,10 @@
         <v>1.53</v>
       </c>
       <c r="W31">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X31">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y31">
         <v>12.5</v>
@@ -8339,13 +8339,13 @@
         <v>50</v>
       </c>
       <c r="AB31">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC31">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD31">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AE31">
         <v>36</v>
@@ -8372,7 +8372,7 @@
         <v>44</v>
       </c>
       <c r="AM31">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN31">
         <v>32</v>
@@ -8387,16 +8387,16 @@
         <v>9.6</v>
       </c>
       <c r="AR31">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS31">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT31">
         <v>9.800000000000001</v>
       </c>
       <c r="AU31">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV31">
         <v>10.5</v>
@@ -8414,25 +8414,25 @@
         <v>15.5</v>
       </c>
       <c r="BA31">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB31">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC31">
         <v>14.5</v>
       </c>
       <c r="BD31">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE31">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BF31">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG31">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH31">
         <v>3.75</v>
@@ -8444,13 +8444,13 @@
         <v>11</v>
       </c>
       <c r="BK31">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BL31">
         <v>140</v>
       </c>
       <c r="BM31">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BN31">
         <v>6.6</v>
@@ -8462,13 +8462,13 @@
         <v>24</v>
       </c>
       <c r="BQ31">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BR31">
         <v>40</v>
       </c>
       <c r="BS31">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BT31">
         <v>6.8</v>
@@ -8480,19 +8480,19 @@
         <v>26</v>
       </c>
       <c r="BW31">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BX31">
         <v>40</v>
       </c>
       <c r="BY31">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BZ31">
         <v>34</v>
       </c>
       <c r="CA31">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB31" t="s">
         <v>215</v>
@@ -8515,40 +8515,40 @@
         <v>197</v>
       </c>
       <c r="F32">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>1.37</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="I32">
-        <v>160</v>
+        <v>27</v>
       </c>
       <c r="J32">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="K32">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="L32">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N32">
         <v>1.26</v>
       </c>
       <c r="O32">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="P32">
         <v>1.25</v>
       </c>
       <c r="Q32">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="R32">
         <v>1.18</v>
@@ -8566,10 +8566,10 @@
         <v>1.05</v>
       </c>
       <c r="W32">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="X32">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y32">
         <v>1000</v>
@@ -8617,64 +8617,64 @@
         <v>1000</v>
       </c>
       <c r="AN32">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="AO32">
         <v>1000</v>
       </c>
       <c r="AP32">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AQ32">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AS32">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AT32">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU32">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV32">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AW32">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AX32">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY32">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ32">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA32">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BB32">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC32">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD32">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE32">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BG32">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8757,22 +8757,22 @@
         <v>198</v>
       </c>
       <c r="F33">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G33">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="H33">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="I33">
+        <v>4.1</v>
+      </c>
+      <c r="J33">
         <v>3.6</v>
       </c>
-      <c r="J33">
-        <v>3.45</v>
-      </c>
       <c r="K33">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L33">
         <v>1.44</v>
@@ -8781,16 +8781,16 @@
         <v>1.08</v>
       </c>
       <c r="N33">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O33">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P33">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q33">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R33">
         <v>1.33</v>
@@ -8799,58 +8799,58 @@
         <v>3.85</v>
       </c>
       <c r="T33">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U33">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V33">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="W33">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="X33">
         <v>13</v>
       </c>
       <c r="Y33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z33">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AA33">
         <v>140</v>
       </c>
       <c r="AB33">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC33">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD33">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE33">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF33">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG33">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH33">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AI33">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ33">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AK33">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL33">
         <v>42</v>
@@ -8859,124 +8859,124 @@
         <v>110</v>
       </c>
       <c r="AN33">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AO33">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AP33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ33">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR33">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AS33">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AT33">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU33">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV33">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW33">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AX33">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY33">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ33">
         <v>17</v>
       </c>
       <c r="BA33">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB33">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BC33">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD33">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE33">
         <v>55</v>
       </c>
       <c r="BF33">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG33">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH33">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BI33">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ33">
         <v>11.5</v>
       </c>
       <c r="BK33">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BL33">
         <v>160</v>
       </c>
       <c r="BM33">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BN33">
         <v>5.3</v>
       </c>
       <c r="BO33">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BP33">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ33">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BR33">
         <v>34</v>
       </c>
       <c r="BS33">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT33">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BU33">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV33">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BW33">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX33">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY33">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BZ33">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA33">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB33" t="s">
         <v>215</v>
@@ -8999,76 +8999,76 @@
         <v>199</v>
       </c>
       <c r="F34">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="G34">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="H34">
         <v>5.3</v>
       </c>
       <c r="I34">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J34">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K34">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L34">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M34">
         <v>1.06</v>
       </c>
       <c r="N34">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O34">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P34">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q34">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="R34">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S34">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="T34">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="U34">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V34">
         <v>1.22</v>
       </c>
       <c r="W34">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="X34">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Y34">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z34">
         <v>42</v>
       </c>
       <c r="AA34">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB34">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC34">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD34">
         <v>21</v>
@@ -9080,142 +9080,142 @@
         <v>10.5</v>
       </c>
       <c r="AG34">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH34">
         <v>20</v>
       </c>
       <c r="AI34">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ34">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK34">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL34">
         <v>36</v>
       </c>
       <c r="AM34">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN34">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AO34">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP34">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ34">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR34">
         <v>38</v>
       </c>
       <c r="AS34">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT34">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU34">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AV34">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW34">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AX34">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY34">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ34">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA34">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB34">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC34">
         <v>16</v>
       </c>
       <c r="BD34">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE34">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="BF34">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG34">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="BH34">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BI34">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BJ34">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK34">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="BL34">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="BM34">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN34">
         <v>4.4</v>
       </c>
       <c r="BO34">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP34">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ34">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR34">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BS34">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT34">
         <v>11</v>
       </c>
       <c r="BU34">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV34">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW34">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX34">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY34">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ34">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="CA34">
         <v>6.8</v>
@@ -9241,73 +9241,73 @@
         <v>200</v>
       </c>
       <c r="F35">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G35">
         <v>2.18</v>
       </c>
       <c r="H35">
+        <v>3.55</v>
+      </c>
+      <c r="I35">
         <v>3.65</v>
-      </c>
-      <c r="I35">
-        <v>3.75</v>
       </c>
       <c r="J35">
         <v>3.7</v>
       </c>
       <c r="K35">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L35">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M35">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N35">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O35">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P35">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q35">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R35">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S35">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="T35">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="U35">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W35">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="X35">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y35">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z35">
         <v>27</v>
       </c>
       <c r="AA35">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB35">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC35">
         <v>8.4</v>
@@ -9316,7 +9316,7 @@
         <v>15</v>
       </c>
       <c r="AE35">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF35">
         <v>14.5</v>
@@ -9325,16 +9325,16 @@
         <v>10.5</v>
       </c>
       <c r="AH35">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI35">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ35">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK35">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AL35">
         <v>32</v>
@@ -9343,58 +9343,58 @@
         <v>75</v>
       </c>
       <c r="AN35">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO35">
         <v>34</v>
       </c>
       <c r="AP35">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AQ35">
         <v>15</v>
       </c>
       <c r="AR35">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS35">
         <v>55</v>
       </c>
       <c r="AT35">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU35">
         <v>7.8</v>
       </c>
       <c r="AV35">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW35">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX35">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY35">
         <v>10</v>
       </c>
       <c r="AZ35">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA35">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB35">
         <v>24</v>
       </c>
       <c r="BC35">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD35">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE35">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF35">
         <v>12</v>
@@ -9406,61 +9406,61 @@
         <v>970</v>
       </c>
       <c r="BI35">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="BJ35">
         <v>970</v>
       </c>
       <c r="BK35">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BL35">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM35">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BN35">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO35">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BP35">
         <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BT35">
         <v>970</v>
       </c>
       <c r="BU35">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="BV35">
         <v>34</v>
       </c>
       <c r="BW35">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BZ35">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA35">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="CB35" t="s">
         <v>215</v>
@@ -9486,7 +9486,7 @@
         <v>1.98</v>
       </c>
       <c r="G36">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H36">
         <v>4.2</v>
@@ -9501,7 +9501,7 @@
         <v>3.8</v>
       </c>
       <c r="L36">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M36">
         <v>1.07</v>
@@ -9513,22 +9513,22 @@
         <v>1.32</v>
       </c>
       <c r="P36">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q36">
         <v>1.97</v>
       </c>
       <c r="R36">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S36">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T36">
         <v>1.84</v>
       </c>
       <c r="U36">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V36">
         <v>1.3</v>
@@ -9543,16 +9543,16 @@
         <v>15.5</v>
       </c>
       <c r="Z36">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA36">
         <v>110</v>
       </c>
       <c r="AB36">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC36">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD36">
         <v>17</v>
@@ -9567,19 +9567,19 @@
         <v>10.5</v>
       </c>
       <c r="AH36">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI36">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ36">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK36">
         <v>20</v>
       </c>
       <c r="AL36">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM36">
         <v>110</v>
@@ -9588,7 +9588,7 @@
         <v>14</v>
       </c>
       <c r="AO36">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP36">
         <v>13.5</v>
@@ -9597,16 +9597,16 @@
         <v>14.5</v>
       </c>
       <c r="AR36">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS36">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AT36">
         <v>8.800000000000001</v>
       </c>
       <c r="AU36">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV36">
         <v>16</v>
@@ -9615,22 +9615,22 @@
         <v>48</v>
       </c>
       <c r="AX36">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY36">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ36">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA36">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BB36">
         <v>20</v>
       </c>
       <c r="BC36">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD36">
         <v>32</v>
@@ -9639,10 +9639,10 @@
         <v>55</v>
       </c>
       <c r="BF36">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG36">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="BH36">
         <v>970</v>
@@ -9654,10 +9654,10 @@
         <v>1000</v>
       </c>
       <c r="BK36">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="BL36">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM36">
         <v>1.67</v>
@@ -9666,7 +9666,7 @@
         <v>970</v>
       </c>
       <c r="BO36">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="BP36">
         <v>1000</v>
@@ -9678,28 +9678,28 @@
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="BT36">
         <v>1000</v>
       </c>
       <c r="BU36">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="BV36">
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="BZ36">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA36">
         <v>1.67</v>
@@ -9725,13 +9725,13 @@
         <v>202</v>
       </c>
       <c r="F37">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G37">
         <v>2.42</v>
       </c>
       <c r="H37">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I37">
         <v>3.35</v>
@@ -9743,31 +9743,31 @@
         <v>3.6</v>
       </c>
       <c r="L37">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M37">
         <v>1.07</v>
       </c>
       <c r="N37">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O37">
         <v>1.33</v>
       </c>
       <c r="P37">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q37">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R37">
         <v>1.37</v>
       </c>
       <c r="S37">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T37">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U37">
         <v>2.2</v>
@@ -9803,7 +9803,7 @@
         <v>38</v>
       </c>
       <c r="AF37">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG37">
         <v>11.5</v>
@@ -9812,10 +9812,10 @@
         <v>17.5</v>
       </c>
       <c r="AI37">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ37">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AK37">
         <v>25</v>
@@ -9830,7 +9830,7 @@
         <v>19.5</v>
       </c>
       <c r="AO37">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP37">
         <v>13</v>
@@ -9854,10 +9854,10 @@
         <v>12.5</v>
       </c>
       <c r="AW37">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX37">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY37">
         <v>10.5</v>
@@ -9872,7 +9872,7 @@
         <v>29</v>
       </c>
       <c r="BC37">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD37">
         <v>34</v>
@@ -9887,40 +9887,40 @@
         <v>30</v>
       </c>
       <c r="BH37">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BI37">
         <v>3.15</v>
       </c>
       <c r="BJ37">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BK37">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BL37">
         <v>140</v>
       </c>
       <c r="BM37">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BN37">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BO37">
         <v>4.7</v>
       </c>
       <c r="BP37">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BQ37">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BR37">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BS37">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BT37">
         <v>7.4</v>
@@ -9929,22 +9929,22 @@
         <v>5.8</v>
       </c>
       <c r="BV37">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BW37">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BX37">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BY37">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ37">
         <v>32</v>
       </c>
       <c r="CA37">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB37" t="s">
         <v>215</v>
@@ -9970,16 +9970,16 @@
         <v>2.62</v>
       </c>
       <c r="G38">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="H38">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I38">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J38">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K38">
         <v>3.95</v>
@@ -9988,40 +9988,40 @@
         <v>1.37</v>
       </c>
       <c r="M38">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N38">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O38">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P38">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q38">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R38">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S38">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T38">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U38">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="V38">
         <v>1.55</v>
       </c>
       <c r="W38">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X38">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y38">
         <v>13</v>
@@ -10033,7 +10033,7 @@
         <v>900</v>
       </c>
       <c r="AB38">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC38">
         <v>8.800000000000001</v>
@@ -10051,7 +10051,7 @@
         <v>13</v>
       </c>
       <c r="AH38">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI38">
         <v>95</v>
@@ -10060,22 +10060,22 @@
         <v>900</v>
       </c>
       <c r="AK38">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL38">
         <v>95</v>
       </c>
       <c r="AM38">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN38">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="AO38">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="AP38">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ38">
         <v>10.5</v>
@@ -10084,7 +10084,7 @@
         <v>16</v>
       </c>
       <c r="AS38">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT38">
         <v>10.5</v>
@@ -10108,19 +10108,19 @@
         <v>14</v>
       </c>
       <c r="BA38">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB38">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BC38">
         <v>14.5</v>
       </c>
       <c r="BD38">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE38">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BF38">
         <v>17.5</v>
@@ -10132,7 +10132,7 @@
         <v>4.1</v>
       </c>
       <c r="BI38">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BJ38">
         <v>10.5</v>
@@ -10141,7 +10141,7 @@
         <v>1.01</v>
       </c>
       <c r="BL38">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM38">
         <v>1.01</v>
@@ -10153,13 +10153,13 @@
         <v>5.1</v>
       </c>
       <c r="BP38">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ38">
         <v>1.01</v>
       </c>
       <c r="BR38">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS38">
         <v>1.01</v>
@@ -10177,7 +10177,7 @@
         <v>1.01</v>
       </c>
       <c r="BX38">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY38">
         <v>1.01</v>
@@ -10209,31 +10209,31 @@
         <v>204</v>
       </c>
       <c r="F39">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="G39">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="H39">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="I39">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="J39">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K39">
         <v>3.55</v>
       </c>
       <c r="L39">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M39">
         <v>1.07</v>
       </c>
       <c r="N39">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O39">
         <v>1.32</v>
@@ -10242,13 +10242,13 @@
         <v>1.97</v>
       </c>
       <c r="Q39">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R39">
         <v>1.37</v>
       </c>
       <c r="S39">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T39">
         <v>1.77</v>
@@ -10257,25 +10257,25 @@
         <v>2.22</v>
       </c>
       <c r="V39">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W39">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="X39">
         <v>14</v>
       </c>
       <c r="Y39">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z39">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA39">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB39">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC39">
         <v>7.8</v>
@@ -10284,52 +10284,52 @@
         <v>12.5</v>
       </c>
       <c r="AE39">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF39">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG39">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH39">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI39">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ39">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AK39">
         <v>32</v>
       </c>
       <c r="AL39">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM39">
         <v>90</v>
       </c>
       <c r="AN39">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AO39">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP39">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ39">
         <v>10</v>
       </c>
       <c r="AR39">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS39">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT39">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU39">
         <v>7.2</v>
@@ -10338,13 +10338,13 @@
         <v>11</v>
       </c>
       <c r="AW39">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AX39">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AY39">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ39">
         <v>15</v>
@@ -10353,7 +10353,7 @@
         <v>36</v>
       </c>
       <c r="BB39">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BC39">
         <v>27</v>
@@ -10365,31 +10365,31 @@
         <v>46</v>
       </c>
       <c r="BF39">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG39">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BH39">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI39">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="BJ39">
         <v>11.5</v>
       </c>
       <c r="BK39">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BL39">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM39">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BN39">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BO39">
         <v>5</v>
@@ -10398,37 +10398,37 @@
         <v>25</v>
       </c>
       <c r="BQ39">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BR39">
         <v>40</v>
       </c>
       <c r="BS39">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BT39">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BU39">
         <v>5</v>
       </c>
       <c r="BV39">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BW39">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BX39">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY39">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BZ39">
         <v>32</v>
       </c>
       <c r="CA39">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="CB39" t="s">
         <v>215</v>
@@ -10451,166 +10451,166 @@
         <v>205</v>
       </c>
       <c r="F40">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G40">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="H40">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="I40">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J40">
         <v>3.5</v>
       </c>
       <c r="K40">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L40">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="M40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N40">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="O40">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P40">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q40">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R40">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S40">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T40">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U40">
         <v>1.11</v>
       </c>
       <c r="V40">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W40">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="X40">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="Y40">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="Z40">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AA40">
         <v>900</v>
       </c>
       <c r="AB40">
-        <v>500</v>
+        <v>7.4</v>
       </c>
       <c r="AC40">
-        <v>500</v>
+        <v>8.6</v>
       </c>
       <c r="AD40">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AE40">
         <v>500</v>
       </c>
       <c r="AF40">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AG40">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AH40">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AI40">
         <v>500</v>
       </c>
       <c r="AJ40">
-        <v>900</v>
+        <v>22</v>
       </c>
       <c r="AK40">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AL40">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AM40">
         <v>580</v>
       </c>
       <c r="AN40">
-        <v>55</v>
+        <v>16.5</v>
       </c>
       <c r="AO40">
         <v>500</v>
       </c>
       <c r="AP40">
-        <v>1.27</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ40">
-        <v>1.34</v>
+        <v>12</v>
       </c>
       <c r="AR40">
-        <v>1.34</v>
+        <v>7.6</v>
       </c>
       <c r="AS40">
-        <v>1.35</v>
+        <v>8.6</v>
       </c>
       <c r="AT40">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="AU40">
-        <v>1.31</v>
+        <v>6.4</v>
       </c>
       <c r="AV40">
-        <v>1.34</v>
+        <v>18</v>
       </c>
       <c r="AW40">
-        <v>1.35</v>
+        <v>8.4</v>
       </c>
       <c r="AX40">
-        <v>1.31</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY40">
-        <v>1.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ40">
-        <v>1.32</v>
+        <v>17</v>
       </c>
       <c r="BA40">
-        <v>1.35</v>
+        <v>8.4</v>
       </c>
       <c r="BB40">
-        <v>1.34</v>
+        <v>17</v>
       </c>
       <c r="BC40">
-        <v>1.32</v>
+        <v>18.5</v>
       </c>
       <c r="BD40">
-        <v>1.34</v>
+        <v>34</v>
       </c>
       <c r="BE40">
-        <v>1.35</v>
+        <v>8.6</v>
       </c>
       <c r="BF40">
-        <v>1.55</v>
+        <v>13</v>
       </c>
       <c r="BG40">
-        <v>1.55</v>
+        <v>8.6</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10693,7 +10693,7 @@
         <v>206</v>
       </c>
       <c r="F41">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G41">
         <v>3.45</v>
@@ -10702,7 +10702,7 @@
         <v>2.3</v>
       </c>
       <c r="I41">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J41">
         <v>3.6</v>
@@ -10711,7 +10711,7 @@
         <v>3.7</v>
       </c>
       <c r="L41">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M41">
         <v>1.06</v>
@@ -10720,7 +10720,7 @@
         <v>4.3</v>
       </c>
       <c r="O41">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P41">
         <v>2.12</v>
@@ -10729,22 +10729,22 @@
         <v>1.86</v>
       </c>
       <c r="R41">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S41">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T41">
         <v>1.71</v>
       </c>
       <c r="U41">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V41">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W41">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X41">
         <v>15.5</v>
@@ -10753,7 +10753,7 @@
         <v>11.5</v>
       </c>
       <c r="Z41">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA41">
         <v>30</v>
@@ -10786,13 +10786,13 @@
         <v>60</v>
       </c>
       <c r="AK41">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL41">
         <v>44</v>
       </c>
       <c r="AM41">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="AN41">
         <v>32</v>
@@ -10816,7 +10816,7 @@
         <v>13.5</v>
       </c>
       <c r="AU41">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV41">
         <v>10</v>
@@ -10828,25 +10828,25 @@
         <v>23</v>
       </c>
       <c r="AY41">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ41">
         <v>15</v>
       </c>
       <c r="BA41">
+        <v>30</v>
+      </c>
+      <c r="BB41">
+        <v>55</v>
+      </c>
+      <c r="BC41">
         <v>32</v>
-      </c>
-      <c r="BB41">
-        <v>50</v>
-      </c>
-      <c r="BC41">
-        <v>30</v>
       </c>
       <c r="BD41">
         <v>40</v>
       </c>
       <c r="BE41">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BF41">
         <v>29</v>
@@ -10861,7 +10861,7 @@
         <v>3.3</v>
       </c>
       <c r="BJ41">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK41">
         <v>7.2</v>
@@ -10870,10 +10870,10 @@
         <v>120</v>
       </c>
       <c r="BM41">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BN41">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BO41">
         <v>5.6</v>
@@ -10882,37 +10882,37 @@
         <v>26</v>
       </c>
       <c r="BQ41">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BR41">
         <v>36</v>
       </c>
       <c r="BS41">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BT41">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BU41">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV41">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BW41">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BX41">
         <v>29</v>
       </c>
       <c r="BY41">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BZ41">
         <v>24</v>
       </c>
       <c r="CA41">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="CB41" t="s">
         <v>215</v>
@@ -10935,7 +10935,7 @@
         <v>207</v>
       </c>
       <c r="F42">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G42">
         <v>2.64</v>
@@ -10953,7 +10953,7 @@
         <v>3.7</v>
       </c>
       <c r="L42">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M42">
         <v>1.06</v>
@@ -10968,19 +10968,19 @@
         <v>2.1</v>
       </c>
       <c r="Q42">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S42">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T42">
         <v>1.71</v>
       </c>
       <c r="U42">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V42">
         <v>1.53</v>
@@ -10989,7 +10989,7 @@
         <v>1.6</v>
       </c>
       <c r="X42">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y42">
         <v>13</v>
@@ -11001,7 +11001,7 @@
         <v>44</v>
       </c>
       <c r="AB42">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC42">
         <v>8</v>
@@ -11010,7 +11010,7 @@
         <v>12.5</v>
       </c>
       <c r="AE42">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF42">
         <v>17.5</v>
@@ -11034,7 +11034,7 @@
         <v>38</v>
       </c>
       <c r="AM42">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN42">
         <v>21</v>
@@ -11052,19 +11052,19 @@
         <v>18</v>
       </c>
       <c r="AS42">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AT42">
         <v>11.5</v>
       </c>
       <c r="AU42">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV42">
         <v>11.5</v>
       </c>
       <c r="AW42">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX42">
         <v>16.5</v>
@@ -11106,7 +11106,7 @@
         <v>9.4</v>
       </c>
       <c r="BK42">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BL42">
         <v>120</v>
@@ -11130,7 +11130,7 @@
         <v>36</v>
       </c>
       <c r="BS42">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BT42">
         <v>6.2</v>
@@ -11142,19 +11142,19 @@
         <v>22</v>
       </c>
       <c r="BW42">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BX42">
         <v>34</v>
       </c>
       <c r="BY42">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BZ42">
         <v>25</v>
       </c>
       <c r="CA42">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB42" t="s">
         <v>215</v>
@@ -11189,55 +11189,55 @@
         <v>3.7</v>
       </c>
       <c r="J43">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K43">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L43">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M43">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N43">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O43">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P43">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q43">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="R43">
         <v>1.19</v>
       </c>
       <c r="S43">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T43">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U43">
         <v>1.79</v>
       </c>
       <c r="V43">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W43">
         <v>1.59</v>
       </c>
       <c r="X43">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y43">
         <v>9.800000000000001</v>
       </c>
       <c r="Z43">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA43">
         <v>85</v>
@@ -11288,13 +11288,13 @@
         <v>6.8</v>
       </c>
       <c r="AQ43">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR43">
         <v>19.5</v>
       </c>
       <c r="AS43">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT43">
         <v>6.8</v>
@@ -11306,7 +11306,7 @@
         <v>11.5</v>
       </c>
       <c r="AW43">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX43">
         <v>13</v>
@@ -11318,82 +11318,82 @@
         <v>17</v>
       </c>
       <c r="BA43">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB43">
         <v>30</v>
       </c>
       <c r="BC43">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD43">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE43">
+        <v>8.4</v>
+      </c>
+      <c r="BF43">
+        <v>7.2</v>
+      </c>
+      <c r="BG43">
         <v>8</v>
       </c>
-      <c r="BF43">
-        <v>7</v>
-      </c>
-      <c r="BG43">
-        <v>7.6</v>
-      </c>
       <c r="BH43">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI43">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ43">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK43">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BL43">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM43">
         <v>1.01</v>
       </c>
       <c r="BN43">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO43">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP43">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ43">
         <v>1.01</v>
       </c>
       <c r="BR43">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS43">
         <v>1.01</v>
       </c>
       <c r="BT43">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU43">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV43">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW43">
         <v>1.01</v>
       </c>
       <c r="BX43">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY43">
         <v>1.01</v>
       </c>
       <c r="BZ43">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA43">
         <v>1.01</v>
@@ -11419,61 +11419,61 @@
         <v>209</v>
       </c>
       <c r="F44">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G44">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H44">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="I44">
         <v>3.1</v>
       </c>
       <c r="J44">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="K44">
         <v>3.2</v>
       </c>
       <c r="L44">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="M44">
         <v>1.11</v>
       </c>
       <c r="N44">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="O44">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P44">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="Q44">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R44">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S44">
         <v>4.4</v>
       </c>
       <c r="T44">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="U44">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V44">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W44">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X44">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y44">
         <v>10.5</v>
@@ -11494,10 +11494,10 @@
         <v>16.5</v>
       </c>
       <c r="AE44">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF44">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG44">
         <v>14</v>
@@ -11506,13 +11506,13 @@
         <v>19</v>
       </c>
       <c r="AI44">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ44">
         <v>60</v>
       </c>
       <c r="AK44">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL44">
         <v>65</v>
@@ -11527,16 +11527,16 @@
         <v>44</v>
       </c>
       <c r="AP44">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ44">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR44">
         <v>16</v>
       </c>
       <c r="AS44">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT44">
         <v>8.4</v>
@@ -11548,7 +11548,7 @@
         <v>11</v>
       </c>
       <c r="AW44">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AX44">
         <v>13</v>
@@ -11557,28 +11557,28 @@
         <v>11</v>
       </c>
       <c r="AZ44">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BA44">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB44">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC44">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD44">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BF44">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BG44">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BH44">
         <v>3.4</v>
@@ -11596,7 +11596,7 @@
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN44">
         <v>6.8</v>
@@ -11608,16 +11608,16 @@
         <v>29</v>
       </c>
       <c r="BQ44">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR44">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS44">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT44">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU44">
         <v>4.4</v>
@@ -11661,58 +11661,58 @@
         <v>210</v>
       </c>
       <c r="F45">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="G45">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H45">
         <v>4.4</v>
       </c>
       <c r="I45">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J45">
         <v>3.2</v>
       </c>
       <c r="K45">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L45">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="M45">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N45">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="O45">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P45">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q45">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="R45">
         <v>1.23</v>
       </c>
       <c r="S45">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="T45">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="U45">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V45">
         <v>1.26</v>
       </c>
       <c r="W45">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X45">
         <v>12</v>
@@ -11733,13 +11733,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD45">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE45">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF45">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG45">
         <v>11.5</v>
@@ -11751,7 +11751,7 @@
         <v>100</v>
       </c>
       <c r="AJ45">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK45">
         <v>28</v>
@@ -11766,7 +11766,7 @@
         <v>24</v>
       </c>
       <c r="AO45">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AP45">
         <v>7.6</v>
@@ -11802,7 +11802,7 @@
         <v>19</v>
       </c>
       <c r="BA45">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB45">
         <v>21</v>
@@ -11814,7 +11814,7 @@
         <v>6.6</v>
       </c>
       <c r="BE45">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF45">
         <v>20</v>
@@ -11826,13 +11826,13 @@
         <v>3.3</v>
       </c>
       <c r="BI45">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ45">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK45">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BL45">
         <v>240</v>
@@ -11841,13 +11841,13 @@
         <v>1.01</v>
       </c>
       <c r="BN45">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BO45">
         <v>3.95</v>
       </c>
       <c r="BP45">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ45">
         <v>1.01</v>
@@ -11862,7 +11862,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU45">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV45">
         <v>55</v>
@@ -11871,13 +11871,13 @@
         <v>1.01</v>
       </c>
       <c r="BX45">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="BY45">
         <v>1.01</v>
       </c>
       <c r="BZ45">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="CA45">
         <v>1.01</v>
@@ -11903,16 +11903,16 @@
         <v>211</v>
       </c>
       <c r="F46">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G46">
         <v>2.5</v>
       </c>
       <c r="H46">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I46">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J46">
         <v>3.2</v>
@@ -11921,28 +11921,28 @@
         <v>3.45</v>
       </c>
       <c r="L46">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="M46">
         <v>1.09</v>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O46">
         <v>1.43</v>
       </c>
       <c r="P46">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q46">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R46">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S46">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T46">
         <v>1.9</v>
@@ -11951,16 +11951,16 @@
         <v>1.92</v>
       </c>
       <c r="V46">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W46">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X46">
         <v>13</v>
       </c>
       <c r="Y46">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z46">
         <v>48</v>
@@ -11969,7 +11969,7 @@
         <v>900</v>
       </c>
       <c r="AB46">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC46">
         <v>9</v>
@@ -11990,7 +11990,7 @@
         <v>21</v>
       </c>
       <c r="AI46">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AJ46">
         <v>95</v>
@@ -11999,7 +11999,7 @@
         <v>32</v>
       </c>
       <c r="AL46">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AM46">
         <v>580</v>
@@ -12020,7 +12020,7 @@
         <v>17.5</v>
       </c>
       <c r="AS46">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT46">
         <v>6.4</v>
@@ -12032,7 +12032,7 @@
         <v>11</v>
       </c>
       <c r="AW46">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AX46">
         <v>10.5</v>
@@ -12044,25 +12044,25 @@
         <v>14.5</v>
       </c>
       <c r="BA46">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB46">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BC46">
         <v>21</v>
       </c>
       <c r="BD46">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE46">
+        <v>5.6</v>
+      </c>
+      <c r="BF46">
         <v>5</v>
       </c>
-      <c r="BF46">
-        <v>4.5</v>
-      </c>
       <c r="BG46">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH46">
         <v>1000</v>
@@ -12145,46 +12145,46 @@
         <v>212</v>
       </c>
       <c r="F47">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G47">
         <v>2.82</v>
       </c>
       <c r="H47">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="I47">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J47">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="K47">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="L47">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="M47">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="N47">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="O47">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="P47">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Q47">
-        <v>2.26</v>
+        <v>2.62</v>
       </c>
       <c r="R47">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S47">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T47">
         <v>1.11</v>
@@ -12193,7 +12193,7 @@
         <v>1.11</v>
       </c>
       <c r="V47">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W47">
         <v>1.54</v>
@@ -12244,7 +12244,7 @@
         <v>500</v>
       </c>
       <c r="AM47">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN47">
         <v>500</v>
@@ -12387,46 +12387,46 @@
         <v>213</v>
       </c>
       <c r="F48">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="G48">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="H48">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="I48">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J48">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="K48">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="L48">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M48">
         <v>1.1</v>
       </c>
       <c r="N48">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="O48">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="P48">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="Q48">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R48">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="S48">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="T48">
         <v>1.83</v>
@@ -12435,10 +12435,10 @@
         <v>1.76</v>
       </c>
       <c r="V48">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W48">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="X48">
         <v>500</v>
@@ -12468,7 +12468,7 @@
         <v>500</v>
       </c>
       <c r="AG48">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH48">
         <v>500</v>
@@ -12495,16 +12495,16 @@
         <v>500</v>
       </c>
       <c r="AP48">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AQ48">
         <v>7.4</v>
       </c>
       <c r="AR48">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="AS48">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AT48">
         <v>5.7</v>
@@ -12513,34 +12513,34 @@
         <v>5.7</v>
       </c>
       <c r="AV48">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AW48">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AX48">
-        <v>1.41</v>
+        <v>8.4</v>
       </c>
       <c r="AY48">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AZ48">
+        <v>1.6</v>
+      </c>
+      <c r="BA48">
         <v>1.55</v>
       </c>
-      <c r="BA48">
-        <v>1.41</v>
-      </c>
       <c r="BB48">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="BC48">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BD48">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="BE48">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="BF48">
         <v>1.55</v>
@@ -12632,16 +12632,16 @@
         <v>3.25</v>
       </c>
       <c r="G49">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H49">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="I49">
         <v>2.74</v>
       </c>
       <c r="J49">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K49">
         <v>3.05</v>
@@ -12653,7 +12653,7 @@
         <v>1.13</v>
       </c>
       <c r="N49">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O49">
         <v>1.57</v>
@@ -12671,7 +12671,7 @@
         <v>5.7</v>
       </c>
       <c r="T49">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U49">
         <v>1.8</v>
@@ -12680,7 +12680,7 @@
         <v>1.57</v>
       </c>
       <c r="W49">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X49">
         <v>8.199999999999999</v>
@@ -12743,7 +12743,7 @@
         <v>7.2</v>
       </c>
       <c r="AR49">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS49">
         <v>36</v>
@@ -12773,7 +12773,7 @@
         <v>55</v>
       </c>
       <c r="BB49">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="BC49">
         <v>20</v>
@@ -12782,13 +12782,13 @@
         <v>28</v>
       </c>
       <c r="BE49">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF49">
         <v>55</v>
       </c>
       <c r="BG49">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BH49">
         <v>2.92</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-01.xlsx
@@ -661,7 +661,7 @@
     <t>Juventude</t>
   </si>
   <si>
-    <t>2026-09-01 02:23:02</t>
+    <t>2026-09-01 03:53:20</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1255,7 @@
         <v>167</v>
       </c>
       <c r="F2">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G2">
         <v>2.74</v>
@@ -1276,7 +1276,7 @@
         <v>1.47</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
         <v>3.35</v>
@@ -1285,16 +1285,16 @@
         <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T2">
         <v>1.85</v>
@@ -1360,13 +1360,13 @@
         <v>32</v>
       </c>
       <c r="AO2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR2">
         <v>17</v>
@@ -1396,7 +1396,7 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB2">
         <v>28</v>
@@ -1408,7 +1408,7 @@
         <v>32</v>
       </c>
       <c r="BE2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF2">
         <v>21</v>
@@ -1441,7 +1441,7 @@
         <v>4.8</v>
       </c>
       <c r="BP2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
@@ -1497,58 +1497,58 @@
         <v>168</v>
       </c>
       <c r="F3">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="G3">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="H3">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="I3">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="J3">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="K3">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="L3">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="M3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="N3">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="O3">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="P3">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Q3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="R3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="S3">
         <v>9.199999999999999</v>
       </c>
       <c r="T3">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="U3">
         <v>1.48</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X3">
         <v>970</v>
@@ -1605,58 +1605,58 @@
         <v>600</v>
       </c>
       <c r="AP3">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AQ3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AR3">
+        <v>1.82</v>
+      </c>
+      <c r="AS3">
+        <v>1.85</v>
+      </c>
+      <c r="AT3">
+        <v>1.54</v>
+      </c>
+      <c r="AU3">
+        <v>1.52</v>
+      </c>
+      <c r="AV3">
+        <v>1.81</v>
+      </c>
+      <c r="AW3">
         <v>1.84</v>
       </c>
-      <c r="AS3">
-        <v>1.86</v>
-      </c>
-      <c r="AT3">
-        <v>5.7</v>
-      </c>
-      <c r="AU3">
-        <v>1.53</v>
-      </c>
-      <c r="AV3">
-        <v>1.83</v>
-      </c>
-      <c r="AW3">
-        <v>1.86</v>
-      </c>
       <c r="AX3">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AY3">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AZ3">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BA3">
         <v>2.14</v>
       </c>
       <c r="BB3">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="BC3">
+        <v>1.83</v>
+      </c>
+      <c r="BD3">
+        <v>1.84</v>
+      </c>
+      <c r="BE3">
         <v>1.85</v>
       </c>
-      <c r="BD3">
-        <v>1.87</v>
-      </c>
-      <c r="BE3">
-        <v>1.87</v>
-      </c>
       <c r="BF3">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="BG3">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="BH3">
         <v>2.68</v>
@@ -1739,88 +1739,88 @@
         <v>169</v>
       </c>
       <c r="F4">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="G4">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="H4">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J4">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="K4">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="L4">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="M4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="N4">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="O4">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="P4">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="Q4">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R4">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="S4">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="T4">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="U4">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W4">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="X4">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="Y4">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AA4">
-        <v>900</v>
+        <v>95</v>
       </c>
       <c r="AB4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AE4">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AF4">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AG4">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AH4">
         <v>32</v>
@@ -1829,52 +1829,52 @@
         <v>500</v>
       </c>
       <c r="AJ4">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AK4">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AL4">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AM4">
         <v>500</v>
       </c>
       <c r="AN4">
-        <v>65</v>
+        <v>600</v>
       </c>
       <c r="AO4">
         <v>600</v>
       </c>
       <c r="AP4">
+        <v>5.5</v>
+      </c>
+      <c r="AQ4">
+        <v>7</v>
+      </c>
+      <c r="AR4">
+        <v>13.5</v>
+      </c>
+      <c r="AS4">
+        <v>9.4</v>
+      </c>
+      <c r="AT4">
+        <v>6</v>
+      </c>
+      <c r="AU4">
         <v>6.2</v>
       </c>
-      <c r="AQ4">
-        <v>8.4</v>
-      </c>
-      <c r="AR4">
-        <v>21</v>
-      </c>
-      <c r="AS4">
-        <v>9.6</v>
-      </c>
-      <c r="AT4">
-        <v>5.7</v>
-      </c>
-      <c r="AU4">
-        <v>6.4</v>
-      </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW4">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AX4">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AY4">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ4">
         <v>24</v>
@@ -1883,55 +1883,55 @@
         <v>9.6</v>
       </c>
       <c r="BB4">
-        <v>29</v>
+        <v>15.5</v>
       </c>
       <c r="BC4">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="BD4">
-        <v>26</v>
+        <v>9.6</v>
       </c>
       <c r="BE4">
         <v>10.5</v>
       </c>
       <c r="BF4">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="BG4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH4">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="BI4">
         <v>2.06</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BK4">
         <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>330</v>
+        <v>410</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BO4">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BP4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
@@ -1940,22 +1940,22 @@
         <v>7.2</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV4">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BY4">
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
@@ -1984,52 +1984,52 @@
         <v>2.7</v>
       </c>
       <c r="G5">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H5">
         <v>2.9</v>
       </c>
       <c r="I5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K5">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="L5">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="M5">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N5">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="O5">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="P5">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="Q5">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="R5">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S5">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="U5">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
         <v>1.53</v>
@@ -2038,37 +2038,37 @@
         <v>10.5</v>
       </c>
       <c r="Y5">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z5">
         <v>22</v>
       </c>
       <c r="AA5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB5">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
         <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF5">
         <v>17.5</v>
       </c>
       <c r="AG5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH5">
         <v>27</v>
       </c>
       <c r="AI5">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
         <v>55</v>
@@ -2077,19 +2077,19 @@
         <v>55</v>
       </c>
       <c r="AL5">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AM5">
         <v>500</v>
       </c>
       <c r="AN5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO5">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP5">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AQ5">
         <v>7.4</v>
@@ -2098,7 +2098,7 @@
         <v>16.5</v>
       </c>
       <c r="AS5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT5">
         <v>7.2</v>
@@ -2119,43 +2119,43 @@
         <v>11.5</v>
       </c>
       <c r="AZ5">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BA5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BB5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BC5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BE5">
         <v>100</v>
       </c>
       <c r="BF5">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BG5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH5">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BI5">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="BJ5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BL5">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="BM5">
         <v>1.01</v>
@@ -2173,7 +2173,7 @@
         <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS5">
         <v>1.01</v>
@@ -2185,19 +2185,19 @@
         <v>5.2</v>
       </c>
       <c r="BV5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BW5">
         <v>1.02</v>
       </c>
       <c r="BX5">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BY5">
         <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="CA5">
         <v>1.01</v>
@@ -2223,16 +2223,16 @@
         <v>171</v>
       </c>
       <c r="F6">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="G6">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H6">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J6">
         <v>3.05</v>
@@ -2241,7 +2241,7 @@
         <v>3.45</v>
       </c>
       <c r="L6">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M6">
         <v>1.09</v>
@@ -2253,19 +2253,19 @@
         <v>1.38</v>
       </c>
       <c r="P6">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R6">
         <v>1.27</v>
       </c>
       <c r="S6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T6">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U6">
         <v>2</v>
@@ -2274,22 +2274,22 @@
         <v>1.45</v>
       </c>
       <c r="W6">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X6">
         <v>11.5</v>
       </c>
       <c r="Y6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z6">
         <v>20</v>
       </c>
       <c r="AA6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6">
         <v>7.6</v>
@@ -2313,10 +2313,10 @@
         <v>65</v>
       </c>
       <c r="AJ6">
+        <v>48</v>
+      </c>
+      <c r="AK6">
         <v>50</v>
-      </c>
-      <c r="AK6">
-        <v>55</v>
       </c>
       <c r="AL6">
         <v>60</v>
@@ -2331,31 +2331,31 @@
         <v>55</v>
       </c>
       <c r="AP6">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AQ6">
         <v>8</v>
       </c>
       <c r="AR6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS6">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AT6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU6">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
         <v>10</v>
       </c>
       <c r="AW6">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AX6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY6">
         <v>9.199999999999999</v>
@@ -2364,31 +2364,31 @@
         <v>14</v>
       </c>
       <c r="BA6">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="BB6">
         <v>18</v>
       </c>
       <c r="BC6">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BD6">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="BE6">
         <v>50</v>
       </c>
       <c r="BF6">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="BG6">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="BH6">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI6">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ6">
         <v>11.5</v>
@@ -2433,13 +2433,13 @@
         <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY6">
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2468,10 +2468,10 @@
         <v>2.28</v>
       </c>
       <c r="G7">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I7">
         <v>3.65</v>
@@ -2480,7 +2480,7 @@
         <v>3.25</v>
       </c>
       <c r="K7">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L7">
         <v>1.46</v>
@@ -2507,10 +2507,10 @@
         <v>4</v>
       </c>
       <c r="T7">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U7">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V7">
         <v>1.39</v>
@@ -2576,7 +2576,7 @@
         <v>4.9</v>
       </c>
       <c r="AQ7">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR7">
         <v>6</v>
@@ -2591,16 +2591,16 @@
         <v>3.95</v>
       </c>
       <c r="AV7">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AW7">
         <v>6.8</v>
       </c>
       <c r="AX7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY7">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7">
         <v>5.6</v>
@@ -2609,10 +2609,10 @@
         <v>7</v>
       </c>
       <c r="BB7">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BC7">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BD7">
         <v>6.8</v>
@@ -2621,7 +2621,7 @@
         <v>7.4</v>
       </c>
       <c r="BF7">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="BG7">
         <v>7</v>
@@ -2630,7 +2630,7 @@
         <v>3.45</v>
       </c>
       <c r="BI7">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ7">
         <v>11.5</v>
@@ -2657,7 +2657,7 @@
         <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS7">
         <v>1.01</v>
@@ -2675,7 +2675,7 @@
         <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY7">
         <v>1.01</v>
@@ -2707,13 +2707,13 @@
         <v>173</v>
       </c>
       <c r="F8">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G8">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I8">
         <v>5.2</v>
@@ -2758,7 +2758,7 @@
         <v>1.24</v>
       </c>
       <c r="W8">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X8">
         <v>11</v>
@@ -2821,7 +2821,7 @@
         <v>10</v>
       </c>
       <c r="AR8">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AS8">
         <v>8.6</v>
@@ -2833,19 +2833,19 @@
         <v>6.6</v>
       </c>
       <c r="AV8">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW8">
         <v>8.199999999999999</v>
       </c>
       <c r="AX8">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY8">
         <v>9</v>
       </c>
       <c r="AZ8">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA8">
         <v>8.4</v>
@@ -2857,7 +2857,7 @@
         <v>19</v>
       </c>
       <c r="BD8">
-        <v>7.8</v>
+        <v>17.5</v>
       </c>
       <c r="BE8">
         <v>8.6</v>
@@ -2869,7 +2869,7 @@
         <v>8.6</v>
       </c>
       <c r="BH8">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI8">
         <v>2.46</v>
@@ -2887,7 +2887,7 @@
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO8">
         <v>3.6</v>
@@ -2908,7 +2908,7 @@
         <v>9</v>
       </c>
       <c r="BU8">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
         <v>55</v>
@@ -2917,7 +2917,7 @@
         <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BY8">
         <v>1.01</v>
@@ -2949,13 +2949,13 @@
         <v>174</v>
       </c>
       <c r="F9">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G9">
         <v>2.42</v>
       </c>
       <c r="H9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I9">
         <v>4.2</v>
@@ -2964,64 +2964,64 @@
         <v>2.92</v>
       </c>
       <c r="K9">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L9">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="M9">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N9">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="O9">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="P9">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Q9">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R9">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S9">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="T9">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="U9">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="V9">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W9">
         <v>1.7</v>
       </c>
       <c r="X9">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Z9">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AA9">
         <v>900</v>
       </c>
       <c r="AB9">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD9">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AE9">
         <v>440</v>
@@ -3030,19 +3030,19 @@
         <v>13</v>
       </c>
       <c r="AG9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH9">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AI9">
         <v>540</v>
       </c>
       <c r="AJ9">
+        <v>150</v>
+      </c>
+      <c r="AK9">
         <v>75</v>
-      </c>
-      <c r="AK9">
-        <v>50</v>
       </c>
       <c r="AL9">
         <v>450</v>
@@ -3057,19 +3057,19 @@
         <v>600</v>
       </c>
       <c r="AP9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR9">
         <v>19.5</v>
       </c>
       <c r="AS9">
-        <v>65</v>
+        <v>14.5</v>
       </c>
       <c r="AT9">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AU9">
         <v>6.4</v>
@@ -3078,7 +3078,7 @@
         <v>16</v>
       </c>
       <c r="AW9">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="AX9">
         <v>10.5</v>
@@ -3087,10 +3087,10 @@
         <v>10</v>
       </c>
       <c r="AZ9">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BA9">
-        <v>42</v>
+        <v>14.5</v>
       </c>
       <c r="BB9">
         <v>28</v>
@@ -3099,61 +3099,61 @@
         <v>27</v>
       </c>
       <c r="BD9">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="BE9">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="BF9">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="BG9">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="BH9">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="BI9">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="BJ9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK9">
         <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="BM9">
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BO9">
         <v>3.95</v>
       </c>
       <c r="BP9">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BQ9">
         <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BS9">
         <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BU9">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW9">
         <v>1.01</v>
@@ -3165,7 +3165,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="CA9">
         <v>1.01</v>
@@ -3191,223 +3191,223 @@
         <v>175</v>
       </c>
       <c r="F10">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G10">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="H10">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="I10">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="J10">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="K10">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <v>1.35</v>
       </c>
       <c r="M10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N10">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P10">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q10">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R10">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S10">
-        <v>1.78</v>
+        <v>2.8</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="V10">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W10">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X10">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="Y10">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z10">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AA10">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AB10">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AC10">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE10">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AF10">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AG10">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AH10">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AI10">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AJ10">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AK10">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AL10">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM10">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN10">
-        <v>600</v>
+        <v>25</v>
       </c>
       <c r="AO10">
-        <v>600</v>
+        <v>21</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BF10">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG10">
-        <v>1.55</v>
+        <v>11</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK10">
         <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM10">
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO10">
         <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS10">
         <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU10">
         <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW10">
         <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY10">
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA10">
         <v>1.01</v>
@@ -3433,7 +3433,7 @@
         <v>176</v>
       </c>
       <c r="F11">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G11">
         <v>2.26</v>
@@ -3445,10 +3445,10 @@
         <v>3.4</v>
       </c>
       <c r="J11">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L11">
         <v>1.33</v>
@@ -3457,31 +3457,31 @@
         <v>1.05</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P11">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="Q11">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="R11">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S11">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="T11">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="U11">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="V11">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
         <v>1.79</v>
@@ -3490,7 +3490,7 @@
         <v>21</v>
       </c>
       <c r="Y11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z11">
         <v>27</v>
@@ -3499,19 +3499,19 @@
         <v>60</v>
       </c>
       <c r="AB11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG11">
         <v>12</v>
@@ -3529,7 +3529,7 @@
         <v>22</v>
       </c>
       <c r="AL11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM11">
         <v>65</v>
@@ -3538,10 +3538,10 @@
         <v>13</v>
       </c>
       <c r="AO11">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP11">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ11">
         <v>14</v>
@@ -3556,43 +3556,43 @@
         <v>10.5</v>
       </c>
       <c r="AU11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV11">
         <v>12</v>
       </c>
       <c r="AW11">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AX11">
         <v>13.5</v>
       </c>
       <c r="AY11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BB11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC11">
         <v>18</v>
       </c>
       <c r="BD11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE11">
         <v>50</v>
       </c>
       <c r="BF11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG11">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3681,7 +3681,7 @@
         <v>6.6</v>
       </c>
       <c r="H12">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="I12">
         <v>1.62</v>
@@ -3717,7 +3717,7 @@
         <v>2.58</v>
       </c>
       <c r="T12">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U12">
         <v>2.22</v>
@@ -3732,7 +3732,7 @@
         <v>27</v>
       </c>
       <c r="Y12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z12">
         <v>13.5</v>
@@ -3786,7 +3786,7 @@
         <v>20</v>
       </c>
       <c r="AQ12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR12">
         <v>10</v>
@@ -3795,7 +3795,7 @@
         <v>13.5</v>
       </c>
       <c r="AT12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU12">
         <v>9.6</v>
@@ -3816,7 +3816,7 @@
         <v>15</v>
       </c>
       <c r="BA12">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB12">
         <v>7.6</v>
@@ -3825,13 +3825,13 @@
         <v>7.2</v>
       </c>
       <c r="BD12">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BE12">
         <v>7.4</v>
       </c>
       <c r="BF12">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12">
         <v>5.9</v>
@@ -3885,7 +3885,7 @@
         <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BY12">
         <v>1.01</v>
@@ -3917,7 +3917,7 @@
         <v>178</v>
       </c>
       <c r="F13">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G13">
         <v>2.5</v>
@@ -3926,7 +3926,7 @@
         <v>3.1</v>
       </c>
       <c r="I13">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J13">
         <v>3.45</v>
@@ -3938,13 +3938,13 @@
         <v>1.44</v>
       </c>
       <c r="M13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N13">
         <v>3.55</v>
       </c>
       <c r="O13">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P13">
         <v>1.88</v>
@@ -3959,7 +3959,7 @@
         <v>3.8</v>
       </c>
       <c r="T13">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="U13">
         <v>2.04</v>
@@ -3971,19 +3971,19 @@
         <v>1.67</v>
       </c>
       <c r="X13">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y13">
         <v>12</v>
       </c>
       <c r="Z13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA13">
         <v>150</v>
       </c>
       <c r="AB13">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC13">
         <v>8.199999999999999</v>
@@ -4019,7 +4019,7 @@
         <v>580</v>
       </c>
       <c r="AN13">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO13">
         <v>48</v>
@@ -4037,7 +4037,7 @@
         <v>42</v>
       </c>
       <c r="AT13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU13">
         <v>6.8</v>
@@ -4064,7 +4064,7 @@
         <v>25</v>
       </c>
       <c r="BC13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD13">
         <v>32</v>
@@ -4073,25 +4073,25 @@
         <v>80</v>
       </c>
       <c r="BF13">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG13">
         <v>24</v>
       </c>
       <c r="BH13">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI13">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BJ13">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK13">
         <v>7.4</v>
       </c>
       <c r="BL13">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BM13">
         <v>1.01</v>
@@ -4103,37 +4103,37 @@
         <v>4.5</v>
       </c>
       <c r="BP13">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="BQ13">
         <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BS13">
         <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU13">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV13">
         <v>34</v>
       </c>
       <c r="BW13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BY13">
         <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="CA13">
         <v>1.01</v>
@@ -4159,19 +4159,19 @@
         <v>179</v>
       </c>
       <c r="F14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H14">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="I14">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="J14">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K14">
         <v>5</v>
@@ -4183,16 +4183,16 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O14">
         <v>1.14</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q14">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="R14">
         <v>1.87</v>
@@ -4201,181 +4201,181 @@
         <v>2.06</v>
       </c>
       <c r="T14">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>2.74</v>
       </c>
       <c r="V14">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="W14">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X14">
+        <v>60</v>
+      </c>
+      <c r="Y14">
+        <v>19</v>
+      </c>
+      <c r="Z14">
+        <v>19</v>
+      </c>
+      <c r="AA14">
+        <v>21</v>
+      </c>
+      <c r="AB14">
+        <v>80</v>
+      </c>
+      <c r="AC14">
+        <v>12.5</v>
+      </c>
+      <c r="AD14">
+        <v>11.5</v>
+      </c>
+      <c r="AE14">
+        <v>19</v>
+      </c>
+      <c r="AF14">
+        <v>100</v>
+      </c>
+      <c r="AG14">
+        <v>25</v>
+      </c>
+      <c r="AH14">
+        <v>19.5</v>
+      </c>
+      <c r="AI14">
+        <v>34</v>
+      </c>
+      <c r="AJ14">
         <v>500</v>
       </c>
-      <c r="Y14">
-        <v>500</v>
-      </c>
-      <c r="Z14">
-        <v>500</v>
-      </c>
-      <c r="AA14">
-        <v>900</v>
-      </c>
-      <c r="AB14">
-        <v>500</v>
-      </c>
-      <c r="AC14">
-        <v>95</v>
-      </c>
-      <c r="AD14">
-        <v>36</v>
-      </c>
-      <c r="AE14">
-        <v>500</v>
-      </c>
-      <c r="AF14">
-        <v>500</v>
-      </c>
-      <c r="AG14">
-        <v>500</v>
-      </c>
-      <c r="AH14">
-        <v>85</v>
-      </c>
-      <c r="AI14">
-        <v>500</v>
-      </c>
-      <c r="AJ14">
-        <v>900</v>
-      </c>
       <c r="AK14">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AL14">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AM14">
         <v>580</v>
       </c>
       <c r="AN14">
-        <v>270</v>
+        <v>600</v>
       </c>
       <c r="AO14">
+        <v>5.9</v>
+      </c>
+      <c r="AP14">
+        <v>23</v>
+      </c>
+      <c r="AQ14">
+        <v>15</v>
+      </c>
+      <c r="AR14">
+        <v>14</v>
+      </c>
+      <c r="AS14">
+        <v>17</v>
+      </c>
+      <c r="AT14">
+        <v>24</v>
+      </c>
+      <c r="AU14">
+        <v>11</v>
+      </c>
+      <c r="AV14">
+        <v>10</v>
+      </c>
+      <c r="AW14">
+        <v>13.5</v>
+      </c>
+      <c r="AX14">
+        <v>38</v>
+      </c>
+      <c r="AY14">
+        <v>16.5</v>
+      </c>
+      <c r="AZ14">
+        <v>14</v>
+      </c>
+      <c r="BA14">
+        <v>19</v>
+      </c>
+      <c r="BB14">
         <v>55</v>
       </c>
-      <c r="AP14">
-        <v>1.68</v>
-      </c>
-      <c r="AQ14">
-        <v>1.62</v>
-      </c>
-      <c r="AR14">
-        <v>1.62</v>
-      </c>
-      <c r="AS14">
-        <v>1.67</v>
-      </c>
-      <c r="AT14">
-        <v>1.68</v>
-      </c>
-      <c r="AU14">
-        <v>1.54</v>
-      </c>
-      <c r="AV14">
-        <v>6.2</v>
-      </c>
-      <c r="AW14">
-        <v>1.62</v>
-      </c>
-      <c r="AX14">
-        <v>1.7</v>
-      </c>
-      <c r="AY14">
-        <v>1.69</v>
-      </c>
-      <c r="AZ14">
-        <v>1.59</v>
-      </c>
-      <c r="BA14">
-        <v>1.66</v>
-      </c>
-      <c r="BB14">
-        <v>1.71</v>
-      </c>
       <c r="BC14">
-        <v>1.7</v>
+        <v>32</v>
       </c>
       <c r="BD14">
-        <v>1.7</v>
+        <v>27</v>
       </c>
       <c r="BE14">
-        <v>1.7</v>
+        <v>42</v>
       </c>
       <c r="BF14">
-        <v>1.7</v>
+        <v>18</v>
       </c>
       <c r="BG14">
-        <v>1.84</v>
+        <v>5.4</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK14">
         <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM14">
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO14">
         <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS14">
         <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW14">
         <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY14">
         <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA14">
         <v>1.01</v>
@@ -4401,130 +4401,130 @@
         <v>180</v>
       </c>
       <c r="F15">
+        <v>2.54</v>
+      </c>
+      <c r="G15">
+        <v>2.64</v>
+      </c>
+      <c r="H15">
         <v>2.56</v>
       </c>
-      <c r="G15">
-        <v>2.66</v>
-      </c>
-      <c r="H15">
-        <v>2.6</v>
-      </c>
       <c r="I15">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J15">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K15">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L15">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M15">
         <v>1.02</v>
       </c>
       <c r="N15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O15">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P15">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="Q15">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="R15">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="S15">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="T15">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="U15">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="V15">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W15">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X15">
         <v>80</v>
       </c>
       <c r="Y15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Z15">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AA15">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AB15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AC15">
         <v>11.5</v>
       </c>
       <c r="AD15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE15">
+        <v>30</v>
+      </c>
+      <c r="AF15">
+        <v>32</v>
+      </c>
+      <c r="AG15">
+        <v>15.5</v>
+      </c>
+      <c r="AH15">
+        <v>15</v>
+      </c>
+      <c r="AI15">
         <v>60</v>
-      </c>
-      <c r="AF15">
-        <v>65</v>
-      </c>
-      <c r="AG15">
-        <v>16</v>
-      </c>
-      <c r="AH15">
-        <v>17.5</v>
-      </c>
-      <c r="AI15">
-        <v>75</v>
       </c>
       <c r="AJ15">
         <v>40</v>
       </c>
       <c r="AK15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AN15">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO15">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP15">
+        <v>24</v>
+      </c>
+      <c r="AQ15">
+        <v>18</v>
+      </c>
+      <c r="AR15">
         <v>21</v>
       </c>
-      <c r="AQ15">
-        <v>17.5</v>
-      </c>
-      <c r="AR15">
-        <v>18.5</v>
-      </c>
       <c r="AS15">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="AT15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU15">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AV15">
         <v>11.5</v>
@@ -4533,10 +4533,10 @@
         <v>20</v>
       </c>
       <c r="AX15">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AY15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ15">
         <v>12.5</v>
@@ -4545,64 +4545,64 @@
         <v>20</v>
       </c>
       <c r="BB15">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="BC15">
         <v>20</v>
       </c>
       <c r="BD15">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BE15">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BF15">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BH15">
         <v>6.2</v>
       </c>
       <c r="BI15">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BJ15">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BK15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL15">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BM15">
         <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BO15">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BP15">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BQ15">
         <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="BS15">
         <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU15">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV15">
         <v>20</v>
@@ -4611,13 +4611,13 @@
         <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BY15">
         <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="CA15">
         <v>1.01</v>
@@ -4643,64 +4643,64 @@
         <v>181</v>
       </c>
       <c r="F16">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G16">
         <v>2.84</v>
       </c>
       <c r="H16">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I16">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="J16">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M16">
         <v>1.03</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O16">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P16">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="Q16">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="R16">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="S16">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="T16">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="U16">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="V16">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W16">
         <v>1.54</v>
       </c>
       <c r="X16">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y16">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z16">
         <v>21</v>
@@ -4709,28 +4709,28 @@
         <v>36</v>
       </c>
       <c r="AB16">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AC16">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16">
         <v>12.5</v>
       </c>
       <c r="AE16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG16">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH16">
         <v>15.5</v>
       </c>
       <c r="AI16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ16">
         <v>42</v>
@@ -4742,67 +4742,67 @@
         <v>32</v>
       </c>
       <c r="AM16">
-        <v>580</v>
+        <v>95</v>
       </c>
       <c r="AN16">
+        <v>17</v>
+      </c>
+      <c r="AO16">
         <v>16</v>
-      </c>
-      <c r="AO16">
-        <v>14</v>
       </c>
       <c r="AP16">
         <v>20</v>
       </c>
       <c r="AQ16">
+        <v>13.5</v>
+      </c>
+      <c r="AR16">
+        <v>17</v>
+      </c>
+      <c r="AS16">
+        <v>29</v>
+      </c>
+      <c r="AT16">
         <v>14</v>
       </c>
-      <c r="AR16">
-        <v>15.5</v>
-      </c>
-      <c r="AS16">
-        <v>16</v>
-      </c>
-      <c r="AT16">
-        <v>5.8</v>
-      </c>
       <c r="AU16">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW16">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AX16">
         <v>18.5</v>
       </c>
       <c r="AY16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ16">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BA16">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BB16">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BC16">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD16">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BE16">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BF16">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BG16">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4885,61 +4885,61 @@
         <v>182</v>
       </c>
       <c r="F17">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G17">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I17">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K17">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L17">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M17">
         <v>1.03</v>
       </c>
       <c r="N17">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P17">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="Q17">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="R17">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="S17">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="T17">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="U17">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="V17">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W17">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X17">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="Y17">
         <v>32</v>
@@ -4951,130 +4951,130 @@
         <v>700</v>
       </c>
       <c r="AB17">
+        <v>13.5</v>
+      </c>
+      <c r="AC17">
+        <v>11</v>
+      </c>
+      <c r="AD17">
+        <v>25</v>
+      </c>
+      <c r="AE17">
+        <v>75</v>
+      </c>
+      <c r="AF17">
+        <v>13.5</v>
+      </c>
+      <c r="AG17">
+        <v>11</v>
+      </c>
+      <c r="AH17">
+        <v>17</v>
+      </c>
+      <c r="AI17">
+        <v>60</v>
+      </c>
+      <c r="AJ17">
+        <v>19.5</v>
+      </c>
+      <c r="AK17">
+        <v>17</v>
+      </c>
+      <c r="AL17">
+        <v>27</v>
+      </c>
+      <c r="AM17">
+        <v>75</v>
+      </c>
+      <c r="AN17">
+        <v>7.4</v>
+      </c>
+      <c r="AO17">
+        <v>46</v>
+      </c>
+      <c r="AP17">
+        <v>18</v>
+      </c>
+      <c r="AQ17">
+        <v>22</v>
+      </c>
+      <c r="AR17">
+        <v>36</v>
+      </c>
+      <c r="AS17">
+        <v>75</v>
+      </c>
+      <c r="AT17">
+        <v>11</v>
+      </c>
+      <c r="AU17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV17">
+        <v>17.5</v>
+      </c>
+      <c r="AW17">
+        <v>36</v>
+      </c>
+      <c r="AX17">
+        <v>11</v>
+      </c>
+      <c r="AY17">
+        <v>9</v>
+      </c>
+      <c r="AZ17">
+        <v>13.5</v>
+      </c>
+      <c r="BA17">
+        <v>40</v>
+      </c>
+      <c r="BB17">
         <v>16</v>
       </c>
-      <c r="AC17">
-        <v>12</v>
-      </c>
-      <c r="AD17">
-        <v>22</v>
-      </c>
-      <c r="AE17">
-        <v>60</v>
-      </c>
-      <c r="AF17">
-        <v>14.5</v>
-      </c>
-      <c r="AG17">
+      <c r="BC17">
+        <v>13.5</v>
+      </c>
+      <c r="BD17">
+        <v>21</v>
+      </c>
+      <c r="BE17">
+        <v>46</v>
+      </c>
+      <c r="BF17">
+        <v>6.2</v>
+      </c>
+      <c r="BG17">
+        <v>30</v>
+      </c>
+      <c r="BH17">
+        <v>5.3</v>
+      </c>
+      <c r="BI17">
+        <v>3.6</v>
+      </c>
+      <c r="BJ17">
+        <v>9.4</v>
+      </c>
+      <c r="BK17">
+        <v>1.01</v>
+      </c>
+      <c r="BL17">
+        <v>95</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>5</v>
+      </c>
+      <c r="BO17">
+        <v>4.2</v>
+      </c>
+      <c r="BP17">
         <v>11.5</v>
       </c>
-      <c r="AH17">
-        <v>16.5</v>
-      </c>
-      <c r="AI17">
-        <v>55</v>
-      </c>
-      <c r="AJ17">
-        <v>19</v>
-      </c>
-      <c r="AK17">
-        <v>16</v>
-      </c>
-      <c r="AL17">
-        <v>25</v>
-      </c>
-      <c r="AM17">
-        <v>65</v>
-      </c>
-      <c r="AN17">
-        <v>6.2</v>
-      </c>
-      <c r="AO17">
-        <v>42</v>
-      </c>
-      <c r="AP17">
-        <v>7.2</v>
-      </c>
-      <c r="AQ17">
-        <v>25</v>
-      </c>
-      <c r="AR17">
-        <v>28</v>
-      </c>
-      <c r="AS17">
-        <v>8.6</v>
-      </c>
-      <c r="AT17">
-        <v>12.5</v>
-      </c>
-      <c r="AU17">
-        <v>10</v>
-      </c>
-      <c r="AV17">
-        <v>18</v>
-      </c>
-      <c r="AW17">
-        <v>23</v>
-      </c>
-      <c r="AX17">
-        <v>11.5</v>
-      </c>
-      <c r="AY17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ17">
-        <v>14</v>
-      </c>
-      <c r="BA17">
-        <v>28</v>
-      </c>
-      <c r="BB17">
-        <v>15</v>
-      </c>
-      <c r="BC17">
-        <v>12.5</v>
-      </c>
-      <c r="BD17">
-        <v>19.5</v>
-      </c>
-      <c r="BE17">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF17">
-        <v>5.3</v>
-      </c>
-      <c r="BG17">
-        <v>21</v>
-      </c>
-      <c r="BH17">
-        <v>5.8</v>
-      </c>
-      <c r="BI17">
-        <v>3.95</v>
-      </c>
-      <c r="BJ17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK17">
-        <v>6.4</v>
-      </c>
-      <c r="BL17">
-        <v>85</v>
-      </c>
-      <c r="BM17">
-        <v>1.01</v>
-      </c>
-      <c r="BN17">
-        <v>5.1</v>
-      </c>
-      <c r="BO17">
-        <v>4.3</v>
-      </c>
-      <c r="BP17">
-        <v>11</v>
-      </c>
       <c r="BQ17">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BR17">
         <v>21</v>
@@ -5083,28 +5083,28 @@
         <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU17">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY17">
         <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CA17">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB17" t="s">
         <v>215</v>
@@ -5127,223 +5127,223 @@
         <v>183</v>
       </c>
       <c r="F18">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="G18">
+        <v>2.96</v>
+      </c>
+      <c r="H18">
+        <v>2.82</v>
+      </c>
+      <c r="I18">
+        <v>3.05</v>
+      </c>
+      <c r="J18">
+        <v>3.1</v>
+      </c>
+      <c r="K18">
+        <v>3.45</v>
+      </c>
+      <c r="L18">
+        <v>1.52</v>
+      </c>
+      <c r="M18">
+        <v>1.1</v>
+      </c>
+      <c r="N18">
         <v>3</v>
       </c>
-      <c r="H18">
-        <v>2.86</v>
-      </c>
-      <c r="I18">
-        <v>3.15</v>
-      </c>
-      <c r="J18">
-        <v>2.98</v>
-      </c>
-      <c r="K18">
-        <v>3.25</v>
-      </c>
-      <c r="L18">
-        <v>1.59</v>
-      </c>
-      <c r="M18">
-        <v>1.12</v>
-      </c>
-      <c r="N18">
-        <v>2.8</v>
-      </c>
       <c r="O18">
+        <v>1.44</v>
+      </c>
+      <c r="P18">
+        <v>1.67</v>
+      </c>
+      <c r="Q18">
+        <v>2.32</v>
+      </c>
+      <c r="R18">
+        <v>1.24</v>
+      </c>
+      <c r="S18">
+        <v>4.5</v>
+      </c>
+      <c r="T18">
+        <v>1.91</v>
+      </c>
+      <c r="U18">
+        <v>1.9</v>
+      </c>
+      <c r="V18">
+        <v>1.5</v>
+      </c>
+      <c r="W18">
         <v>1.52</v>
       </c>
-      <c r="P18">
-        <v>1.58</v>
-      </c>
-      <c r="Q18">
-        <v>2.58</v>
-      </c>
-      <c r="R18">
-        <v>1.2</v>
-      </c>
-      <c r="S18">
-        <v>5.3</v>
-      </c>
-      <c r="T18">
-        <v>1.01</v>
-      </c>
-      <c r="U18">
-        <v>1.76</v>
-      </c>
-      <c r="V18">
-        <v>1.47</v>
-      </c>
-      <c r="W18">
-        <v>1.5</v>
-      </c>
       <c r="X18">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y18">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AA18">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AB18">
-        <v>500</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC18">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AD18">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AE18">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AF18">
-        <v>85</v>
+        <v>18.5</v>
       </c>
       <c r="AG18">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="AH18">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AI18">
-        <v>540</v>
+        <v>60</v>
       </c>
       <c r="AJ18">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AK18">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AL18">
-        <v>540</v>
+        <v>60</v>
       </c>
       <c r="AM18">
         <v>500</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP18">
-        <v>2.1</v>
+        <v>9</v>
       </c>
       <c r="AQ18">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AR18">
-        <v>2.24</v>
+        <v>15.5</v>
       </c>
       <c r="AS18">
-        <v>2.14</v>
+        <v>34</v>
       </c>
       <c r="AT18">
-        <v>1.51</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU18">
-        <v>1.77</v>
+        <v>6.2</v>
       </c>
       <c r="AV18">
-        <v>1.76</v>
+        <v>11.5</v>
       </c>
       <c r="AW18">
-        <v>1.8</v>
+        <v>32</v>
       </c>
       <c r="AX18">
-        <v>2.22</v>
+        <v>15</v>
       </c>
       <c r="AY18">
-        <v>2.14</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA18">
-        <v>1.8</v>
+        <v>42</v>
       </c>
       <c r="BB18">
-        <v>2.14</v>
+        <v>30</v>
       </c>
       <c r="BC18">
-        <v>1.8</v>
+        <v>27</v>
       </c>
       <c r="BD18">
-        <v>1.8</v>
+        <v>40</v>
       </c>
       <c r="BE18">
-        <v>2.16</v>
+        <v>90</v>
       </c>
       <c r="BF18">
-        <v>1.81</v>
+        <v>29</v>
       </c>
       <c r="BG18">
-        <v>1.81</v>
+        <v>29</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK18">
         <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM18">
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ18">
         <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS18">
         <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW18">
         <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY18">
         <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA18">
         <v>1.01</v>
@@ -5369,22 +5369,22 @@
         <v>184</v>
       </c>
       <c r="F19">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G19">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H19">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="I19">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J19">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K19">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L19">
         <v>1.13</v>
@@ -5399,19 +5399,19 @@
         <v>1.05</v>
       </c>
       <c r="P19">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Q19">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="R19">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="S19">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T19">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="U19">
         <v>4.6</v>
@@ -5426,13 +5426,13 @@
         <v>500</v>
       </c>
       <c r="Y19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z19">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AA19">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="AB19">
         <v>55</v>
@@ -5450,13 +5450,13 @@
         <v>55</v>
       </c>
       <c r="AG19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH19">
         <v>15</v>
       </c>
       <c r="AI19">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AJ19">
         <v>120</v>
@@ -5465,19 +5465,19 @@
         <v>44</v>
       </c>
       <c r="AL19">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AM19">
         <v>26</v>
       </c>
       <c r="AN19">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO19">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AP19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AQ19">
         <v>23</v>
@@ -5486,22 +5486,22 @@
         <v>26</v>
       </c>
       <c r="AS19">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AT19">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AU19">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AV19">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW19">
         <v>17</v>
       </c>
       <c r="AX19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY19">
         <v>17.5</v>
@@ -5516,7 +5516,7 @@
         <v>30</v>
       </c>
       <c r="BC19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD19">
         <v>18.5</v>
@@ -5525,10 +5525,10 @@
         <v>20</v>
       </c>
       <c r="BF19">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BG19">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BH19">
         <v>9.199999999999999</v>
@@ -5611,172 +5611,172 @@
         <v>185</v>
       </c>
       <c r="F20">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="H20">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="I20">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="J20">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K20">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M20">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N20">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O20">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P20">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Q20">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R20">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="S20">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="T20">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V20">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="W20">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X20">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Y20">
         <v>13</v>
       </c>
       <c r="Z20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA20">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB20">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AC20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD20">
         <v>10.5</v>
       </c>
       <c r="AE20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF20">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AG20">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AH20">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AI20">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ20">
         <v>140</v>
       </c>
       <c r="AK20">
+        <v>70</v>
+      </c>
+      <c r="AL20">
         <v>60</v>
       </c>
-      <c r="AL20">
+      <c r="AM20">
+        <v>70</v>
+      </c>
+      <c r="AN20">
         <v>55</v>
       </c>
-      <c r="AM20">
-        <v>75</v>
-      </c>
-      <c r="AN20">
-        <v>65</v>
-      </c>
       <c r="AO20">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AP20">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AQ20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR20">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS20">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT20">
+        <v>27</v>
+      </c>
+      <c r="AU20">
+        <v>10.5</v>
+      </c>
+      <c r="AV20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW20">
+        <v>13</v>
+      </c>
+      <c r="AX20">
+        <v>44</v>
+      </c>
+      <c r="AY20">
+        <v>21</v>
+      </c>
+      <c r="AZ20">
+        <v>16.5</v>
+      </c>
+      <c r="BA20">
+        <v>22</v>
+      </c>
+      <c r="BB20">
         <v>20</v>
       </c>
-      <c r="AU20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV20">
-        <v>9</v>
-      </c>
-      <c r="AW20">
-        <v>14</v>
-      </c>
-      <c r="AX20">
-        <v>32</v>
-      </c>
-      <c r="AY20">
-        <v>17.5</v>
-      </c>
-      <c r="AZ20">
-        <v>14</v>
-      </c>
-      <c r="BA20">
-        <v>9.6</v>
-      </c>
-      <c r="BB20">
-        <v>14</v>
-      </c>
       <c r="BC20">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD20">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BE20">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BF20">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="BG20">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH20">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BI20">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BJ20">
         <v>9.199999999999999</v>
@@ -5788,46 +5788,46 @@
         <v>90</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BN20">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BO20">
         <v>7</v>
       </c>
       <c r="BP20">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BR20">
         <v>40</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BT20">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU20">
         <v>4.2</v>
       </c>
       <c r="BV20">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BW20">
         <v>6.8</v>
       </c>
       <c r="BX20">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA20">
         <v>8.800000000000001</v>
@@ -5856,7 +5856,7 @@
         <v>12.5</v>
       </c>
       <c r="G21">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H21">
         <v>1.33</v>
@@ -5865,7 +5865,7 @@
         <v>1.35</v>
       </c>
       <c r="J21">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K21">
         <v>6</v>
@@ -5877,10 +5877,10 @@
         <v>1.06</v>
       </c>
       <c r="N21">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O21">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P21">
         <v>1.94</v>
@@ -5892,34 +5892,34 @@
         <v>1.35</v>
       </c>
       <c r="S21">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T21">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="U21">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="V21">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y21">
         <v>6.8</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA21">
         <v>12</v>
       </c>
       <c r="AB21">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC21">
         <v>13.5</v>
@@ -5937,7 +5937,7 @@
         <v>65</v>
       </c>
       <c r="AH21">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="AI21">
         <v>65</v>
@@ -5958,22 +5958,22 @@
         <v>1000</v>
       </c>
       <c r="AO21">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AP21">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ21">
         <v>5.7</v>
       </c>
       <c r="AR21">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS21">
         <v>8.4</v>
       </c>
       <c r="AT21">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU21">
         <v>11</v>
@@ -5985,7 +5985,7 @@
         <v>14.5</v>
       </c>
       <c r="AX21">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AY21">
         <v>32</v>
@@ -5997,82 +5997,82 @@
         <v>21</v>
       </c>
       <c r="BB21">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC21">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD21">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE21">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF21">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG21">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL21">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="CB21" t="s">
         <v>215</v>
@@ -6104,16 +6104,16 @@
         <v>3.4</v>
       </c>
       <c r="I22">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J22">
         <v>3.15</v>
       </c>
       <c r="K22">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L22">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M22">
         <v>1.08</v>
@@ -6128,7 +6128,7 @@
         <v>1.75</v>
       </c>
       <c r="Q22">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R22">
         <v>1.28</v>
@@ -6137,7 +6137,7 @@
         <v>3.9</v>
       </c>
       <c r="T22">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="U22">
         <v>2.02</v>
@@ -6146,16 +6146,16 @@
         <v>1.35</v>
       </c>
       <c r="W22">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X22">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y22">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z22">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA22">
         <v>85</v>
@@ -6173,13 +6173,13 @@
         <v>55</v>
       </c>
       <c r="AF22">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG22">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH22">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI22">
         <v>70</v>
@@ -6203,115 +6203,115 @@
         <v>60</v>
       </c>
       <c r="AP22">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="AQ22">
-        <v>4.3</v>
+        <v>9.4</v>
       </c>
       <c r="AR22">
+        <v>19</v>
+      </c>
+      <c r="AS22">
+        <v>46</v>
+      </c>
+      <c r="AT22">
+        <v>7</v>
+      </c>
+      <c r="AU22">
+        <v>6.6</v>
+      </c>
+      <c r="AV22">
+        <v>11.5</v>
+      </c>
+      <c r="AW22">
+        <v>27</v>
+      </c>
+      <c r="AX22">
+        <v>11</v>
+      </c>
+      <c r="AY22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ22">
+        <v>15.5</v>
+      </c>
+      <c r="BA22">
+        <v>22</v>
+      </c>
+      <c r="BB22">
+        <v>21</v>
+      </c>
+      <c r="BC22">
+        <v>18</v>
+      </c>
+      <c r="BD22">
+        <v>27</v>
+      </c>
+      <c r="BE22">
+        <v>50</v>
+      </c>
+      <c r="BF22">
+        <v>19</v>
+      </c>
+      <c r="BG22">
+        <v>27</v>
+      </c>
+      <c r="BH22">
+        <v>3.5</v>
+      </c>
+      <c r="BI22">
+        <v>2.62</v>
+      </c>
+      <c r="BJ22">
+        <v>11.5</v>
+      </c>
+      <c r="BK22">
+        <v>1.01</v>
+      </c>
+      <c r="BL22">
+        <v>160</v>
+      </c>
+      <c r="BM22">
+        <v>1.01</v>
+      </c>
+      <c r="BN22">
+        <v>5.7</v>
+      </c>
+      <c r="BO22">
+        <v>4</v>
+      </c>
+      <c r="BP22">
+        <v>21</v>
+      </c>
+      <c r="BQ22">
+        <v>1.01</v>
+      </c>
+      <c r="BR22">
+        <v>40</v>
+      </c>
+      <c r="BS22">
+        <v>1.01</v>
+      </c>
+      <c r="BT22">
+        <v>7.6</v>
+      </c>
+      <c r="BU22">
         <v>5.2</v>
       </c>
-      <c r="AS22">
-        <v>5.9</v>
-      </c>
-      <c r="AT22">
-        <v>3.8</v>
-      </c>
-      <c r="AU22">
-        <v>3.5</v>
-      </c>
-      <c r="AV22">
-        <v>4.5</v>
-      </c>
-      <c r="AW22">
-        <v>5.7</v>
-      </c>
-      <c r="AX22">
-        <v>4.6</v>
-      </c>
-      <c r="AY22">
-        <v>4.2</v>
-      </c>
-      <c r="AZ22">
-        <v>4.9</v>
-      </c>
-      <c r="BA22">
-        <v>5.8</v>
-      </c>
-      <c r="BB22">
-        <v>5.4</v>
-      </c>
-      <c r="BC22">
-        <v>5.1</v>
-      </c>
-      <c r="BD22">
-        <v>5.6</v>
-      </c>
-      <c r="BE22">
-        <v>6</v>
-      </c>
-      <c r="BF22">
-        <v>5.1</v>
-      </c>
-      <c r="BG22">
-        <v>5.7</v>
-      </c>
-      <c r="BH22">
-        <v>1000</v>
-      </c>
-      <c r="BI22">
-        <v>1.01</v>
-      </c>
-      <c r="BJ22">
-        <v>1000</v>
-      </c>
-      <c r="BK22">
-        <v>1.01</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>1.01</v>
-      </c>
-      <c r="BN22">
-        <v>1000</v>
-      </c>
-      <c r="BO22">
-        <v>1.01</v>
-      </c>
-      <c r="BP22">
-        <v>1000</v>
-      </c>
-      <c r="BQ22">
-        <v>1.01</v>
-      </c>
-      <c r="BR22">
-        <v>1000</v>
-      </c>
-      <c r="BS22">
-        <v>1.01</v>
-      </c>
-      <c r="BT22">
-        <v>1000</v>
-      </c>
-      <c r="BU22">
-        <v>1.01</v>
-      </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW22">
         <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY22">
         <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA22">
         <v>1.01</v>
@@ -6337,58 +6337,58 @@
         <v>188</v>
       </c>
       <c r="F23">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="G23">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="H23">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="I23">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J23">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M23">
         <v>1.03</v>
       </c>
       <c r="N23">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O23">
         <v>1.19</v>
       </c>
       <c r="P23">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="Q23">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R23">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S23">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="T23">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U23">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W23">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="X23">
         <v>25</v>
@@ -6397,91 +6397,91 @@
         <v>34</v>
       </c>
       <c r="Z23">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA23">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AB23">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC23">
         <v>11</v>
       </c>
       <c r="AD23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE23">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AF23">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG23">
         <v>9.6</v>
       </c>
       <c r="AH23">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI23">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ23">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK23">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL23">
         <v>25</v>
       </c>
       <c r="AM23">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AN23">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO23">
+        <v>55</v>
+      </c>
+      <c r="AP23">
+        <v>22</v>
+      </c>
+      <c r="AQ23">
+        <v>26</v>
+      </c>
+      <c r="AR23">
         <v>46</v>
       </c>
-      <c r="AP23">
-        <v>21</v>
-      </c>
-      <c r="AQ23">
-        <v>23</v>
-      </c>
-      <c r="AR23">
-        <v>40</v>
-      </c>
       <c r="AS23">
-        <v>14.5</v>
+        <v>90</v>
       </c>
       <c r="AT23">
         <v>11</v>
       </c>
       <c r="AU23">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV23">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW23">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AX23">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY23">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ23">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA23">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB23">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC23">
         <v>13.5</v>
@@ -6490,73 +6490,73 @@
         <v>23</v>
       </c>
       <c r="BE23">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF23">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BG23">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL23">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB23" t="s">
         <v>215</v>
@@ -6579,34 +6579,34 @@
         <v>189</v>
       </c>
       <c r="F24">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G24">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H24">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I24">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="J24">
         <v>4.9</v>
       </c>
       <c r="K24">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L24">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M24">
         <v>1.02</v>
       </c>
       <c r="N24">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O24">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P24">
         <v>3.35</v>
@@ -6615,19 +6615,19 @@
         <v>1.4</v>
       </c>
       <c r="R24">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S24">
         <v>2</v>
       </c>
       <c r="T24">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U24">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="V24">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="W24">
         <v>1.21</v>
@@ -6636,19 +6636,19 @@
         <v>38</v>
       </c>
       <c r="Y24">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Z24">
         <v>15</v>
       </c>
       <c r="AA24">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AB24">
         <v>40</v>
       </c>
       <c r="AC24">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD24">
         <v>11</v>
@@ -6663,19 +6663,19 @@
         <v>22</v>
       </c>
       <c r="AH24">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AI24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ24">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AK24">
         <v>55</v>
       </c>
       <c r="AL24">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM24">
         <v>55</v>
@@ -6684,13 +6684,13 @@
         <v>32</v>
       </c>
       <c r="AO24">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AP24">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AQ24">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR24">
         <v>13.5</v>
@@ -6699,10 +6699,10 @@
         <v>16.5</v>
       </c>
       <c r="AT24">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AU24">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV24">
         <v>10</v>
@@ -6717,16 +6717,16 @@
         <v>20</v>
       </c>
       <c r="AZ24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA24">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB24">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BC24">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="BD24">
         <v>40</v>
@@ -6735,70 +6735,70 @@
         <v>40</v>
       </c>
       <c r="BF24">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BG24">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI24">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="BJ24">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BK24">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BL24">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="BM24">
-        <v>2.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN24">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BO24">
-        <v>1.82</v>
+        <v>5</v>
       </c>
       <c r="BP24">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BQ24">
-        <v>2.02</v>
+        <v>8</v>
       </c>
       <c r="BR24">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BS24">
-        <v>2.02</v>
+        <v>8</v>
       </c>
       <c r="BT24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BU24">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BV24">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="BW24">
-        <v>1.84</v>
+        <v>5</v>
       </c>
       <c r="BX24">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="BY24">
-        <v>1.93</v>
+        <v>6.6</v>
       </c>
       <c r="BZ24">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="CA24">
-        <v>1.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB24" t="s">
         <v>215</v>
@@ -6821,10 +6821,10 @@
         <v>190</v>
       </c>
       <c r="F25">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G25">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H25">
         <v>4.8</v>
@@ -6872,7 +6872,7 @@
         <v>1.25</v>
       </c>
       <c r="W25">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X25">
         <v>14.5</v>
@@ -6902,7 +6902,7 @@
         <v>11.5</v>
       </c>
       <c r="AG25">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH25">
         <v>19.5</v>
@@ -6911,7 +6911,7 @@
         <v>70</v>
       </c>
       <c r="AJ25">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK25">
         <v>21</v>
@@ -6938,7 +6938,7 @@
         <v>32</v>
       </c>
       <c r="AS25">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AT25">
         <v>8</v>
@@ -6974,13 +6974,13 @@
         <v>32</v>
       </c>
       <c r="BE25">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="BF25">
         <v>10.5</v>
       </c>
       <c r="BG25">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="BH25">
         <v>3.65</v>
@@ -6992,13 +6992,13 @@
         <v>10.5</v>
       </c>
       <c r="BK25">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL25">
         <v>150</v>
       </c>
       <c r="BM25">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN25">
         <v>5.3</v>
@@ -7010,7 +7010,7 @@
         <v>15</v>
       </c>
       <c r="BQ25">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BR25">
         <v>28</v>
@@ -7022,13 +7022,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU25">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BV25">
         <v>42</v>
       </c>
       <c r="BW25">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BX25">
         <v>50</v>
@@ -7037,7 +7037,7 @@
         <v>5.9</v>
       </c>
       <c r="BZ25">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA25">
         <v>5.3</v>
@@ -7087,7 +7087,7 @@
         <v>1.05</v>
       </c>
       <c r="N26">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O26">
         <v>1.26</v>
@@ -7096,16 +7096,16 @@
         <v>2.18</v>
       </c>
       <c r="Q26">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R26">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S26">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T26">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U26">
         <v>2.18</v>
@@ -7114,10 +7114,10 @@
         <v>1.25</v>
       </c>
       <c r="W26">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X26">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y26">
         <v>25</v>
@@ -7126,10 +7126,10 @@
         <v>140</v>
       </c>
       <c r="AA26">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AB26">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC26">
         <v>9.6</v>
@@ -7138,37 +7138,37 @@
         <v>18.5</v>
       </c>
       <c r="AE26">
-        <v>320</v>
+        <v>75</v>
       </c>
       <c r="AF26">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG26">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI26">
-        <v>700</v>
+        <v>65</v>
       </c>
       <c r="AJ26">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK26">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="AL26">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM26">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="AN26">
         <v>9.800000000000001</v>
       </c>
       <c r="AO26">
-        <v>270</v>
+        <v>65</v>
       </c>
       <c r="AP26">
         <v>15.5</v>
@@ -7177,112 +7177,112 @@
         <v>18</v>
       </c>
       <c r="AR26">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AS26">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="AT26">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU26">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV26">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW26">
-        <v>6.4</v>
+        <v>40</v>
       </c>
       <c r="AX26">
         <v>10</v>
       </c>
       <c r="AY26">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ26">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BA26">
-        <v>6.4</v>
+        <v>40</v>
       </c>
       <c r="BB26">
         <v>16.5</v>
       </c>
       <c r="BC26">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD26">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BE26">
-        <v>6.6</v>
+        <v>70</v>
       </c>
       <c r="BF26">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG26">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BH26">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BI26">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BJ26">
         <v>12</v>
       </c>
       <c r="BK26">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="BL26">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM26">
+        <v>6.6</v>
+      </c>
+      <c r="BN26">
         <v>4.5</v>
       </c>
-      <c r="BN26">
-        <v>5.3</v>
-      </c>
       <c r="BO26">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BP26">
         <v>14</v>
       </c>
       <c r="BQ26">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="BR26">
         <v>30</v>
       </c>
       <c r="BS26">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BT26">
         <v>10.5</v>
       </c>
       <c r="BU26">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV26">
         <v>48</v>
       </c>
       <c r="BW26">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BX26">
         <v>55</v>
       </c>
       <c r="BY26">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BZ26">
         <v>23</v>
       </c>
       <c r="CA26">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="CB26" t="s">
         <v>215</v>
@@ -7305,16 +7305,16 @@
         <v>192</v>
       </c>
       <c r="F27">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="G27">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="H27">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="I27">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J27">
         <v>3.55</v>
@@ -7338,7 +7338,7 @@
         <v>1.98</v>
       </c>
       <c r="Q27">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R27">
         <v>1.37</v>
@@ -7353,10 +7353,10 @@
         <v>2.16</v>
       </c>
       <c r="V27">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W27">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="X27">
         <v>14.5</v>
@@ -7365,10 +7365,10 @@
         <v>12</v>
       </c>
       <c r="Z27">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA27">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB27">
         <v>12</v>
@@ -7389,7 +7389,7 @@
         <v>13</v>
       </c>
       <c r="AH27">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI27">
         <v>44</v>
@@ -7404,16 +7404,16 @@
         <v>44</v>
       </c>
       <c r="AM27">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AN27">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AO27">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ27">
         <v>9.800000000000001</v>
@@ -7422,22 +7422,22 @@
         <v>16</v>
       </c>
       <c r="AS27">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT27">
         <v>9.800000000000001</v>
       </c>
       <c r="AU27">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV27">
         <v>10.5</v>
       </c>
       <c r="AW27">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AX27">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AY27">
         <v>10.5</v>
@@ -7446,31 +7446,31 @@
         <v>14</v>
       </c>
       <c r="BA27">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BB27">
         <v>32</v>
       </c>
       <c r="BC27">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BD27">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BE27">
-        <v>7.4</v>
+        <v>65</v>
       </c>
       <c r="BF27">
         <v>17.5</v>
       </c>
       <c r="BG27">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BH27">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI27">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ27">
         <v>11.5</v>
@@ -7479,7 +7479,7 @@
         <v>3.45</v>
       </c>
       <c r="BL27">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM27">
         <v>4.7</v>
@@ -7488,10 +7488,10 @@
         <v>6.8</v>
       </c>
       <c r="BO27">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP27">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ27">
         <v>4.1</v>
@@ -7503,19 +7503,19 @@
         <v>4.4</v>
       </c>
       <c r="BT27">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU27">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW27">
         <v>4.1</v>
       </c>
       <c r="BX27">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY27">
         <v>4.4</v>
@@ -7524,7 +7524,7 @@
         <v>32</v>
       </c>
       <c r="CA27">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="CB27" t="s">
         <v>215</v>
@@ -7547,22 +7547,22 @@
         <v>193</v>
       </c>
       <c r="F28">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G28">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="H28">
+        <v>3.45</v>
+      </c>
+      <c r="I28">
         <v>3.65</v>
       </c>
-      <c r="I28">
-        <v>3.75</v>
-      </c>
       <c r="J28">
+        <v>3.6</v>
+      </c>
+      <c r="K28">
         <v>3.65</v>
-      </c>
-      <c r="K28">
-        <v>3.7</v>
       </c>
       <c r="L28">
         <v>1.41</v>
@@ -7586,19 +7586,19 @@
         <v>1.36</v>
       </c>
       <c r="S28">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T28">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U28">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="X28">
         <v>15</v>
@@ -7607,52 +7607,52 @@
         <v>14.5</v>
       </c>
       <c r="Z28">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA28">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="AB28">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD28">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE28">
         <v>110</v>
       </c>
       <c r="AF28">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG28">
         <v>11</v>
       </c>
       <c r="AH28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI28">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="AJ28">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL28">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM28">
         <v>500</v>
       </c>
       <c r="AN28">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO28">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AP28">
         <v>12.5</v>
@@ -7664,25 +7664,25 @@
         <v>22</v>
       </c>
       <c r="AS28">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AT28">
         <v>8.4</v>
       </c>
       <c r="AU28">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV28">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW28">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX28">
         <v>12</v>
       </c>
       <c r="AY28">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ28">
         <v>16</v>
@@ -7691,7 +7691,7 @@
         <v>44</v>
       </c>
       <c r="BB28">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC28">
         <v>20</v>
@@ -7700,13 +7700,13 @@
         <v>32</v>
       </c>
       <c r="BE28">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="BF28">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG28">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BH28">
         <v>3.75</v>
@@ -7718,46 +7718,46 @@
         <v>11</v>
       </c>
       <c r="BK28">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BL28">
         <v>140</v>
       </c>
       <c r="BM28">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BN28">
         <v>5.7</v>
       </c>
       <c r="BO28">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP28">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ28">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR28">
         <v>36</v>
       </c>
       <c r="BS28">
+        <v>5.2</v>
+      </c>
+      <c r="BT28">
+        <v>7.6</v>
+      </c>
+      <c r="BU28">
+        <v>5.3</v>
+      </c>
+      <c r="BV28">
+        <v>32</v>
+      </c>
+      <c r="BW28">
         <v>5.1</v>
       </c>
-      <c r="BT28">
-        <v>7.8</v>
-      </c>
-      <c r="BU28">
-        <v>5.4</v>
-      </c>
-      <c r="BV28">
-        <v>34</v>
-      </c>
-      <c r="BW28">
-        <v>5</v>
-      </c>
       <c r="BX28">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY28">
         <v>5.3</v>
@@ -7766,7 +7766,7 @@
         <v>32</v>
       </c>
       <c r="CA28">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB28" t="s">
         <v>215</v>
@@ -7798,7 +7798,7 @@
         <v>3.95</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J29">
         <v>4.1</v>
@@ -7813,7 +7813,7 @@
         <v>1.05</v>
       </c>
       <c r="N29">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>1.23</v>
@@ -7822,7 +7822,7 @@
         <v>2.38</v>
       </c>
       <c r="Q29">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R29">
         <v>1.52</v>
@@ -7834,7 +7834,7 @@
         <v>1.65</v>
       </c>
       <c r="U29">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V29">
         <v>1.33</v>
@@ -7849,7 +7849,7 @@
         <v>19</v>
       </c>
       <c r="Z29">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AA29">
         <v>160</v>
@@ -7861,13 +7861,13 @@
         <v>9.6</v>
       </c>
       <c r="AD29">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE29">
         <v>42</v>
       </c>
       <c r="AF29">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG29">
         <v>10.5</v>
@@ -7882,31 +7882,31 @@
         <v>24</v>
       </c>
       <c r="AK29">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL29">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM29">
         <v>75</v>
       </c>
       <c r="AN29">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO29">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP29">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ29">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AR29">
         <v>26</v>
       </c>
       <c r="AS29">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="AT29">
         <v>10.5</v>
@@ -7924,7 +7924,7 @@
         <v>12.5</v>
       </c>
       <c r="AY29">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ29">
         <v>14.5</v>
@@ -7936,25 +7936,25 @@
         <v>21</v>
       </c>
       <c r="BC29">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD29">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE29">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BF29">
         <v>9.800000000000001</v>
       </c>
       <c r="BG29">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BH29">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BI29">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BJ29">
         <v>9</v>
@@ -7963,10 +7963,10 @@
         <v>7.2</v>
       </c>
       <c r="BL29">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM29">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN29">
         <v>5</v>
@@ -7978,13 +7978,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ29">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BR29">
         <v>28</v>
       </c>
       <c r="BS29">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT29">
         <v>7.4</v>
@@ -7993,22 +7993,22 @@
         <v>5.9</v>
       </c>
       <c r="BV29">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BW29">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX29">
         <v>40</v>
       </c>
       <c r="BY29">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ29">
         <v>21</v>
       </c>
       <c r="CA29">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="CB29" t="s">
         <v>215</v>
@@ -8031,16 +8031,16 @@
         <v>195</v>
       </c>
       <c r="F30">
+        <v>2.74</v>
+      </c>
+      <c r="G30">
+        <v>2.82</v>
+      </c>
+      <c r="H30">
+        <v>2.6</v>
+      </c>
+      <c r="I30">
         <v>2.68</v>
-      </c>
-      <c r="G30">
-        <v>2.74</v>
-      </c>
-      <c r="H30">
-        <v>2.64</v>
-      </c>
-      <c r="I30">
-        <v>2.72</v>
       </c>
       <c r="J30">
         <v>3.8</v>
@@ -8064,34 +8064,34 @@
         <v>2.24</v>
       </c>
       <c r="Q30">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R30">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S30">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T30">
         <v>1.64</v>
       </c>
       <c r="U30">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V30">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W30">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="X30">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y30">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA30">
         <v>38</v>
@@ -8103,7 +8103,7 @@
         <v>11</v>
       </c>
       <c r="AD30">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE30">
         <v>25</v>
@@ -8130,13 +8130,13 @@
         <v>36</v>
       </c>
       <c r="AM30">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO30">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP30">
         <v>16.5</v>
@@ -8175,7 +8175,7 @@
         <v>30</v>
       </c>
       <c r="BB30">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BC30">
         <v>24</v>
@@ -8184,7 +8184,7 @@
         <v>30</v>
       </c>
       <c r="BE30">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BF30">
         <v>17</v>
@@ -8202,7 +8202,7 @@
         <v>10.5</v>
       </c>
       <c r="BK30">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL30">
         <v>110</v>
@@ -8220,13 +8220,13 @@
         <v>23</v>
       </c>
       <c r="BQ30">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BR30">
         <v>34</v>
       </c>
       <c r="BS30">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT30">
         <v>7</v>
@@ -8235,22 +8235,22 @@
         <v>5</v>
       </c>
       <c r="BV30">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW30">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BX30">
         <v>34</v>
       </c>
       <c r="BY30">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BZ30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA30">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="CB30" t="s">
         <v>215</v>
@@ -8273,22 +8273,22 @@
         <v>196</v>
       </c>
       <c r="F31">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="G31">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="H31">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="I31">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="J31">
         <v>3.5</v>
       </c>
       <c r="K31">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L31">
         <v>1.43</v>
@@ -8300,10 +8300,10 @@
         <v>3.75</v>
       </c>
       <c r="O31">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P31">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q31">
         <v>2.02</v>
@@ -8312,67 +8312,67 @@
         <v>1.35</v>
       </c>
       <c r="S31">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T31">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U31">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W31">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="X31">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y31">
         <v>12.5</v>
       </c>
       <c r="Z31">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA31">
         <v>50</v>
       </c>
       <c r="AB31">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD31">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE31">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF31">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG31">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH31">
         <v>21</v>
       </c>
       <c r="AI31">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="AJ31">
         <v>100</v>
       </c>
       <c r="AK31">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AL31">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AM31">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN31">
         <v>32</v>
@@ -8381,19 +8381,19 @@
         <v>32</v>
       </c>
       <c r="AP31">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AQ31">
         <v>9.6</v>
       </c>
       <c r="AR31">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS31">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="AT31">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU31">
         <v>7.2</v>
@@ -8402,97 +8402,97 @@
         <v>10.5</v>
       </c>
       <c r="AW31">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AX31">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY31">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ31">
         <v>15.5</v>
       </c>
       <c r="BA31">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="BB31">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="BC31">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BD31">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="BE31">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BF31">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BG31">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BH31">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="BI31">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="BJ31">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BK31">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL31">
         <v>140</v>
       </c>
       <c r="BM31">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BN31">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BO31">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP31">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ31">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR31">
         <v>40</v>
       </c>
       <c r="BS31">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="BT31">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU31">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV31">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW31">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BX31">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY31">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ31">
         <v>34</v>
       </c>
       <c r="CA31">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB31" t="s">
         <v>215</v>
@@ -8515,22 +8515,22 @@
         <v>197</v>
       </c>
       <c r="F32">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G32">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="H32">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="I32">
         <v>27</v>
       </c>
       <c r="J32">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="K32">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L32">
         <v>1.25</v>
@@ -8548,13 +8548,13 @@
         <v>1.25</v>
       </c>
       <c r="Q32">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="R32">
         <v>1.18</v>
       </c>
       <c r="S32">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
         <v>1.04</v>
@@ -8566,52 +8566,52 @@
         <v>1.05</v>
       </c>
       <c r="W32">
-        <v>3.7</v>
+        <v>1.51</v>
       </c>
       <c r="X32">
         <v>26</v>
       </c>
       <c r="Y32">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Z32">
-        <v>1000</v>
+        <v>620</v>
       </c>
       <c r="AA32">
         <v>1000</v>
       </c>
       <c r="AB32">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC32">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AD32">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AE32">
         <v>1000</v>
       </c>
       <c r="AF32">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG32">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AH32">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AI32">
         <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK32">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL32">
-        <v>1000</v>
+        <v>820</v>
       </c>
       <c r="AM32">
         <v>1000</v>
@@ -8623,58 +8623,58 @@
         <v>1000</v>
       </c>
       <c r="AP32">
-        <v>1.07</v>
+        <v>3.85</v>
       </c>
       <c r="AQ32">
+        <v>19</v>
+      </c>
+      <c r="AR32">
+        <v>4.2</v>
+      </c>
+      <c r="AS32">
+        <v>4.2</v>
+      </c>
+      <c r="AT32">
+        <v>2.74</v>
+      </c>
+      <c r="AU32">
+        <v>11</v>
+      </c>
+      <c r="AV32">
+        <v>25</v>
+      </c>
+      <c r="AW32">
+        <v>4.2</v>
+      </c>
+      <c r="AX32">
+        <v>3.95</v>
+      </c>
+      <c r="AY32">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ32">
+        <v>15.5</v>
+      </c>
+      <c r="BA32">
+        <v>4.2</v>
+      </c>
+      <c r="BB32">
+        <v>8.6</v>
+      </c>
+      <c r="BC32">
+        <v>9.6</v>
+      </c>
+      <c r="BD32">
+        <v>15.5</v>
+      </c>
+      <c r="BE32">
         <v>2.5</v>
       </c>
-      <c r="AR32">
-        <v>2.5</v>
-      </c>
-      <c r="AS32">
-        <v>2.5</v>
-      </c>
-      <c r="AT32">
-        <v>1.11</v>
-      </c>
-      <c r="AU32">
-        <v>1.11</v>
-      </c>
-      <c r="AV32">
-        <v>2.5</v>
-      </c>
-      <c r="AW32">
-        <v>2.5</v>
-      </c>
-      <c r="AX32">
-        <v>1.11</v>
-      </c>
-      <c r="AY32">
-        <v>1.11</v>
-      </c>
-      <c r="AZ32">
-        <v>1.11</v>
-      </c>
-      <c r="BA32">
-        <v>2.5</v>
-      </c>
-      <c r="BB32">
-        <v>1.11</v>
-      </c>
-      <c r="BC32">
-        <v>1.11</v>
-      </c>
-      <c r="BD32">
-        <v>1.11</v>
-      </c>
-      <c r="BE32">
-        <v>1.11</v>
-      </c>
       <c r="BF32">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BG32">
-        <v>4.2</v>
+        <v>28</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8757,16 +8757,16 @@
         <v>198</v>
       </c>
       <c r="F33">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G33">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H33">
+        <v>3.9</v>
+      </c>
+      <c r="I33">
         <v>4</v>
-      </c>
-      <c r="I33">
-        <v>4.1</v>
       </c>
       <c r="J33">
         <v>3.6</v>
@@ -8787,13 +8787,13 @@
         <v>1.36</v>
       </c>
       <c r="P33">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q33">
         <v>2.08</v>
       </c>
       <c r="R33">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S33">
         <v>3.85</v>
@@ -8802,13 +8802,13 @@
         <v>1.87</v>
       </c>
       <c r="U33">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V33">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X33">
         <v>13</v>
@@ -8826,7 +8826,7 @@
         <v>8.6</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD33">
         <v>16</v>
@@ -8838,10 +8838,10 @@
         <v>12.5</v>
       </c>
       <c r="AG33">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH33">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI33">
         <v>65</v>
@@ -8859,7 +8859,7 @@
         <v>110</v>
       </c>
       <c r="AN33">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO33">
         <v>60</v>
@@ -8871,25 +8871,25 @@
         <v>12.5</v>
       </c>
       <c r="AR33">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS33">
         <v>70</v>
       </c>
       <c r="AT33">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU33">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV33">
         <v>15</v>
       </c>
       <c r="AW33">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AX33">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY33">
         <v>10</v>
@@ -8901,22 +8901,22 @@
         <v>50</v>
       </c>
       <c r="BB33">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC33">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD33">
         <v>36</v>
       </c>
       <c r="BE33">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="BF33">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG33">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BH33">
         <v>3.3</v>
@@ -8928,31 +8928,31 @@
         <v>11.5</v>
       </c>
       <c r="BK33">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL33">
         <v>160</v>
       </c>
       <c r="BM33">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BN33">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BO33">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP33">
         <v>15.5</v>
       </c>
       <c r="BQ33">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BR33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS33">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BT33">
         <v>7.4</v>
@@ -8964,19 +8964,19 @@
         <v>36</v>
       </c>
       <c r="BW33">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX33">
         <v>46</v>
       </c>
       <c r="BY33">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ33">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA33">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB33" t="s">
         <v>215</v>
@@ -9002,19 +9002,19 @@
         <v>1.74</v>
       </c>
       <c r="G34">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H34">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I34">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J34">
+        <v>4</v>
+      </c>
+      <c r="K34">
         <v>4.1</v>
-      </c>
-      <c r="K34">
-        <v>4.2</v>
       </c>
       <c r="L34">
         <v>1.38</v>
@@ -9032,7 +9032,7 @@
         <v>2.14</v>
       </c>
       <c r="Q34">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R34">
         <v>1.44</v>
@@ -9044,13 +9044,13 @@
         <v>1.84</v>
       </c>
       <c r="U34">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V34">
         <v>1.22</v>
       </c>
       <c r="W34">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="X34">
         <v>17.5</v>
@@ -9065,10 +9065,10 @@
         <v>130</v>
       </c>
       <c r="AB34">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC34">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD34">
         <v>21</v>
@@ -9080,10 +9080,10 @@
         <v>10.5</v>
       </c>
       <c r="AG34">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH34">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI34">
         <v>70</v>
@@ -9104,7 +9104,7 @@
         <v>9.6</v>
       </c>
       <c r="AO34">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP34">
         <v>15.5</v>
@@ -9122,10 +9122,10 @@
         <v>8.6</v>
       </c>
       <c r="AU34">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV34">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW34">
         <v>60</v>
@@ -9134,7 +9134,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY34">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ34">
         <v>18</v>
@@ -9143,7 +9143,7 @@
         <v>60</v>
       </c>
       <c r="BB34">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC34">
         <v>16</v>
@@ -9158,7 +9158,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG34">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BH34">
         <v>3.8</v>
@@ -9170,7 +9170,7 @@
         <v>10.5</v>
       </c>
       <c r="BK34">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="BL34">
         <v>140</v>
@@ -9182,13 +9182,13 @@
         <v>4.4</v>
       </c>
       <c r="BO34">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP34">
         <v>11.5</v>
       </c>
       <c r="BQ34">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR34">
         <v>25</v>
@@ -9206,7 +9206,7 @@
         <v>46</v>
       </c>
       <c r="BW34">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX34">
         <v>50</v>
@@ -9218,7 +9218,7 @@
         <v>19</v>
       </c>
       <c r="CA34">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB34" t="s">
         <v>215</v>
@@ -9247,19 +9247,19 @@
         <v>2.18</v>
       </c>
       <c r="H35">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I35">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J35">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K35">
         <v>3.8</v>
       </c>
       <c r="L35">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M35">
         <v>1.05</v>
@@ -9271,19 +9271,19 @@
         <v>1.24</v>
       </c>
       <c r="P35">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q35">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R35">
         <v>1.5</v>
       </c>
       <c r="S35">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T35">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U35">
         <v>2.46</v>
@@ -9295,7 +9295,7 @@
         <v>1.84</v>
       </c>
       <c r="X35">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y35">
         <v>16.5</v>
@@ -9304,7 +9304,7 @@
         <v>27</v>
       </c>
       <c r="AA35">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB35">
         <v>12.5</v>
@@ -9319,7 +9319,7 @@
         <v>38</v>
       </c>
       <c r="AF35">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG35">
         <v>10.5</v>
@@ -9334,31 +9334,31 @@
         <v>28</v>
       </c>
       <c r="AK35">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL35">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM35">
         <v>75</v>
       </c>
       <c r="AN35">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO35">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP35">
         <v>18</v>
       </c>
       <c r="AQ35">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR35">
         <v>23</v>
       </c>
       <c r="AS35">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT35">
         <v>11.5</v>
@@ -9388,13 +9388,13 @@
         <v>24</v>
       </c>
       <c r="BC35">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD35">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE35">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF35">
         <v>12</v>
@@ -9403,64 +9403,64 @@
         <v>27</v>
       </c>
       <c r="BH35">
-        <v>970</v>
+        <v>3.9</v>
       </c>
       <c r="BI35">
-        <v>1.27</v>
+        <v>3.55</v>
       </c>
       <c r="BJ35">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="BK35">
-        <v>1.08</v>
+        <v>7</v>
       </c>
       <c r="BL35">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM35">
-        <v>1.07</v>
+        <v>10.5</v>
       </c>
       <c r="BN35">
-        <v>970</v>
+        <v>5.2</v>
       </c>
       <c r="BO35">
-        <v>1.08</v>
+        <v>4.6</v>
       </c>
       <c r="BP35">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ35">
-        <v>1.08</v>
+        <v>6.4</v>
       </c>
       <c r="BR35">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS35">
-        <v>1.08</v>
+        <v>7.8</v>
       </c>
       <c r="BT35">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="BU35">
-        <v>1.27</v>
+        <v>5</v>
       </c>
       <c r="BV35">
+        <v>27</v>
+      </c>
+      <c r="BW35">
+        <v>8</v>
+      </c>
+      <c r="BX35">
         <v>34</v>
       </c>
-      <c r="BW35">
-        <v>1.05</v>
-      </c>
-      <c r="BX35">
-        <v>1000</v>
-      </c>
       <c r="BY35">
-        <v>1.08</v>
+        <v>8.6</v>
       </c>
       <c r="BZ35">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="CA35">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB35" t="s">
         <v>215</v>
@@ -9483,25 +9483,25 @@
         <v>201</v>
       </c>
       <c r="F36">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H36">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I36">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J36">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K36">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L36">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M36">
         <v>1.07</v>
@@ -9519,7 +9519,7 @@
         <v>1.97</v>
       </c>
       <c r="R36">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S36">
         <v>3.5</v>
@@ -9528,19 +9528,19 @@
         <v>1.84</v>
       </c>
       <c r="U36">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W36">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X36">
         <v>15</v>
       </c>
       <c r="Y36">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z36">
         <v>32</v>
@@ -9552,7 +9552,7 @@
         <v>9.4</v>
       </c>
       <c r="AC36">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD36">
         <v>17</v>
@@ -9564,7 +9564,7 @@
         <v>12</v>
       </c>
       <c r="AG36">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH36">
         <v>18.5</v>
@@ -9582,13 +9582,13 @@
         <v>36</v>
       </c>
       <c r="AM36">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN36">
         <v>14</v>
       </c>
       <c r="AO36">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP36">
         <v>13.5</v>
@@ -9600,7 +9600,7 @@
         <v>29</v>
       </c>
       <c r="AS36">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AT36">
         <v>8.800000000000001</v>
@@ -9621,10 +9621,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ36">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA36">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BB36">
         <v>20</v>
@@ -9636,73 +9636,73 @@
         <v>32</v>
       </c>
       <c r="BE36">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BF36">
         <v>12.5</v>
       </c>
       <c r="BG36">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BH36">
-        <v>970</v>
+        <v>3.9</v>
       </c>
       <c r="BI36">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="BJ36">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK36">
-        <v>1.45</v>
+        <v>4.7</v>
       </c>
       <c r="BL36">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="BM36">
-        <v>1.67</v>
+        <v>6.8</v>
       </c>
       <c r="BN36">
-        <v>970</v>
+        <v>5.2</v>
       </c>
       <c r="BO36">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="BP36">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ36">
-        <v>1.67</v>
+        <v>4.7</v>
       </c>
       <c r="BR36">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS36">
-        <v>1.45</v>
+        <v>5.8</v>
       </c>
       <c r="BT36">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU36">
-        <v>1.45</v>
+        <v>6.6</v>
       </c>
       <c r="BV36">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW36">
-        <v>1.45</v>
+        <v>6</v>
       </c>
       <c r="BX36">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY36">
-        <v>1.45</v>
+        <v>6.2</v>
       </c>
       <c r="BZ36">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CA36">
-        <v>1.67</v>
+        <v>5.6</v>
       </c>
       <c r="CB36" t="s">
         <v>215</v>
@@ -9725,10 +9725,10 @@
         <v>202</v>
       </c>
       <c r="F37">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G37">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H37">
         <v>3.25</v>
@@ -9752,7 +9752,7 @@
         <v>3.9</v>
       </c>
       <c r="O37">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P37">
         <v>1.97</v>
@@ -9770,7 +9770,7 @@
         <v>1.77</v>
       </c>
       <c r="U37">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V37">
         <v>1.42</v>
@@ -9779,7 +9779,7 @@
         <v>1.7</v>
       </c>
       <c r="X37">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y37">
         <v>13</v>
@@ -9794,7 +9794,7 @@
         <v>10.5</v>
       </c>
       <c r="AC37">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD37">
         <v>14</v>
@@ -9803,7 +9803,7 @@
         <v>38</v>
       </c>
       <c r="AF37">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG37">
         <v>11.5</v>
@@ -9815,13 +9815,13 @@
         <v>46</v>
       </c>
       <c r="AJ37">
+        <v>34</v>
+      </c>
+      <c r="AK37">
+        <v>24</v>
+      </c>
+      <c r="AL37">
         <v>38</v>
-      </c>
-      <c r="AK37">
-        <v>25</v>
-      </c>
-      <c r="AL37">
-        <v>40</v>
       </c>
       <c r="AM37">
         <v>110</v>
@@ -9830,7 +9830,7 @@
         <v>19.5</v>
       </c>
       <c r="AO37">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP37">
         <v>13</v>
@@ -9866,19 +9866,19 @@
         <v>16</v>
       </c>
       <c r="BA37">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB37">
         <v>29</v>
       </c>
       <c r="BC37">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD37">
         <v>34</v>
       </c>
       <c r="BE37">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BF37">
         <v>17.5</v>
@@ -9887,7 +9887,7 @@
         <v>30</v>
       </c>
       <c r="BH37">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI37">
         <v>3.15</v>
@@ -9896,31 +9896,31 @@
         <v>9.4</v>
       </c>
       <c r="BK37">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL37">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM37">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BN37">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO37">
         <v>4.7</v>
       </c>
       <c r="BP37">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ37">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR37">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS37">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT37">
         <v>7.4</v>
@@ -9932,16 +9932,16 @@
         <v>26</v>
       </c>
       <c r="BW37">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BX37">
         <v>38</v>
       </c>
       <c r="BY37">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ37">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="CA37">
         <v>6.6</v>
@@ -9970,10 +9970,10 @@
         <v>2.62</v>
       </c>
       <c r="G38">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H38">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I38">
         <v>2.82</v>
@@ -10000,25 +10000,25 @@
         <v>2.1</v>
       </c>
       <c r="Q38">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R38">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S38">
         <v>3.1</v>
       </c>
       <c r="T38">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="U38">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="V38">
         <v>1.55</v>
       </c>
       <c r="W38">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X38">
         <v>19</v>
@@ -10045,7 +10045,7 @@
         <v>65</v>
       </c>
       <c r="AF38">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG38">
         <v>13</v>
@@ -10066,7 +10066,7 @@
         <v>95</v>
       </c>
       <c r="AM38">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN38">
         <v>22</v>
@@ -10081,25 +10081,25 @@
         <v>10.5</v>
       </c>
       <c r="AR38">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS38">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="AT38">
         <v>10.5</v>
       </c>
       <c r="AU38">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV38">
         <v>10.5</v>
       </c>
       <c r="AW38">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX38">
-        <v>16</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY38">
         <v>10.5</v>
@@ -10108,25 +10108,25 @@
         <v>14</v>
       </c>
       <c r="BA38">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="BB38">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="BC38">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD38">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="BE38">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF38">
         <v>17.5</v>
       </c>
       <c r="BG38">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH38">
         <v>4.1</v>
@@ -10209,16 +10209,16 @@
         <v>204</v>
       </c>
       <c r="F39">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="G39">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H39">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I39">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J39">
         <v>3.5</v>
@@ -10233,13 +10233,13 @@
         <v>1.07</v>
       </c>
       <c r="N39">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O39">
         <v>1.32</v>
       </c>
       <c r="P39">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q39">
         <v>1.97</v>
@@ -10251,16 +10251,16 @@
         <v>3.5</v>
       </c>
       <c r="T39">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U39">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V39">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W39">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X39">
         <v>14</v>
@@ -10269,7 +10269,7 @@
         <v>11</v>
       </c>
       <c r="Z39">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA39">
         <v>40</v>
@@ -10281,16 +10281,16 @@
         <v>7.8</v>
       </c>
       <c r="AD39">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE39">
         <v>29</v>
       </c>
       <c r="AF39">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG39">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH39">
         <v>16.5</v>
@@ -10311,10 +10311,10 @@
         <v>90</v>
       </c>
       <c r="AN39">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO39">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP39">
         <v>13</v>
@@ -10338,7 +10338,7 @@
         <v>11</v>
       </c>
       <c r="AW39">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX39">
         <v>18</v>
@@ -10347,22 +10347,22 @@
         <v>12</v>
       </c>
       <c r="AZ39">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA39">
         <v>36</v>
       </c>
       <c r="BB39">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC39">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BD39">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE39">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BF39">
         <v>24</v>
@@ -10371,40 +10371,40 @@
         <v>20</v>
       </c>
       <c r="BH39">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI39">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ39">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK39">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BL39">
         <v>130</v>
       </c>
       <c r="BM39">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BN39">
         <v>6.2</v>
       </c>
       <c r="BO39">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BP39">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BQ39">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR39">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BS39">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BT39">
         <v>6.2</v>
@@ -10413,22 +10413,22 @@
         <v>5</v>
       </c>
       <c r="BV39">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BW39">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX39">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BY39">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BZ39">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="CA39">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB39" t="s">
         <v>215</v>
@@ -10454,7 +10454,7 @@
         <v>1.82</v>
       </c>
       <c r="G40">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H40">
         <v>5.1</v>
@@ -10493,10 +10493,10 @@
         <v>4.2</v>
       </c>
       <c r="T40">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U40">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="V40">
         <v>1.22</v>
@@ -10541,7 +10541,7 @@
         <v>500</v>
       </c>
       <c r="AJ40">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK40">
         <v>23</v>
@@ -10565,10 +10565,10 @@
         <v>12</v>
       </c>
       <c r="AR40">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS40">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT40">
         <v>6.2</v>
@@ -10580,7 +10580,7 @@
         <v>18</v>
       </c>
       <c r="AW40">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX40">
         <v>8.800000000000001</v>
@@ -10592,7 +10592,7 @@
         <v>17</v>
       </c>
       <c r="BA40">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB40">
         <v>17</v>
@@ -10604,19 +10604,19 @@
         <v>34</v>
       </c>
       <c r="BE40">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF40">
         <v>13</v>
       </c>
       <c r="BG40">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH40">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI40">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BJ40">
         <v>1000</v>
@@ -10693,19 +10693,19 @@
         <v>206</v>
       </c>
       <c r="F41">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="G41">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="H41">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="I41">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="J41">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K41">
         <v>3.7</v>
@@ -10720,7 +10720,7 @@
         <v>4.3</v>
       </c>
       <c r="O41">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P41">
         <v>2.12</v>
@@ -10741,34 +10741,34 @@
         <v>2.34</v>
       </c>
       <c r="V41">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W41">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X41">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y41">
         <v>11.5</v>
       </c>
       <c r="Z41">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA41">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AB41">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC41">
         <v>8</v>
       </c>
       <c r="AD41">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE41">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF41">
         <v>25</v>
@@ -10780,25 +10780,25 @@
         <v>16</v>
       </c>
       <c r="AI41">
+        <v>34</v>
+      </c>
+      <c r="AJ41">
+        <v>65</v>
+      </c>
+      <c r="AK41">
         <v>36</v>
-      </c>
-      <c r="AJ41">
-        <v>60</v>
-      </c>
-      <c r="AK41">
-        <v>34</v>
       </c>
       <c r="AL41">
         <v>44</v>
       </c>
       <c r="AM41">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AN41">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO41">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP41">
         <v>14.5</v>
@@ -10810,13 +10810,13 @@
         <v>14</v>
       </c>
       <c r="AS41">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT41">
         <v>13.5</v>
       </c>
       <c r="AU41">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV41">
         <v>10</v>
@@ -10852,7 +10852,7 @@
         <v>29</v>
       </c>
       <c r="BG41">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH41">
         <v>4</v>
@@ -10870,7 +10870,7 @@
         <v>120</v>
       </c>
       <c r="BM41">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN41">
         <v>6.8</v>
@@ -10879,40 +10879,40 @@
         <v>5.6</v>
       </c>
       <c r="BP41">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ41">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR41">
         <v>36</v>
       </c>
       <c r="BS41">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT41">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU41">
         <v>4.7</v>
       </c>
       <c r="BV41">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW41">
         <v>6.2</v>
       </c>
       <c r="BX41">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY41">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ41">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA41">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB41" t="s">
         <v>215</v>
@@ -10935,16 +10935,16 @@
         <v>207</v>
       </c>
       <c r="F42">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G42">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H42">
+        <v>2.82</v>
+      </c>
+      <c r="I42">
         <v>2.86</v>
-      </c>
-      <c r="I42">
-        <v>2.88</v>
       </c>
       <c r="J42">
         <v>3.65</v>
@@ -10953,46 +10953,46 @@
         <v>3.7</v>
       </c>
       <c r="L42">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M42">
         <v>1.06</v>
       </c>
       <c r="N42">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O42">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P42">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q42">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R42">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S42">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T42">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U42">
         <v>2.36</v>
       </c>
       <c r="V42">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W42">
         <v>1.6</v>
       </c>
       <c r="X42">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y42">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z42">
         <v>20</v>
@@ -11013,19 +11013,19 @@
         <v>29</v>
       </c>
       <c r="AF42">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG42">
         <v>12</v>
       </c>
       <c r="AH42">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI42">
         <v>40</v>
       </c>
       <c r="AJ42">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK42">
         <v>26</v>
@@ -11034,25 +11034,25 @@
         <v>38</v>
       </c>
       <c r="AM42">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN42">
         <v>21</v>
       </c>
       <c r="AO42">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP42">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ42">
         <v>12</v>
       </c>
       <c r="AR42">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS42">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT42">
         <v>11.5</v>
@@ -11064,7 +11064,7 @@
         <v>11.5</v>
       </c>
       <c r="AW42">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX42">
         <v>16.5</v>
@@ -11073,7 +11073,7 @@
         <v>11</v>
       </c>
       <c r="AZ42">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA42">
         <v>34</v>
@@ -11088,13 +11088,13 @@
         <v>32</v>
       </c>
       <c r="BE42">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="BF42">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG42">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH42">
         <v>4.2</v>
@@ -11112,7 +11112,7 @@
         <v>120</v>
       </c>
       <c r="BM42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN42">
         <v>6.6</v>
@@ -11124,13 +11124,13 @@
         <v>22</v>
       </c>
       <c r="BQ42">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR42">
         <v>36</v>
       </c>
       <c r="BS42">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BT42">
         <v>6.2</v>
@@ -11142,16 +11142,16 @@
         <v>22</v>
       </c>
       <c r="BW42">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX42">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY42">
         <v>5.7</v>
       </c>
       <c r="BZ42">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA42">
         <v>5.4</v>
@@ -11219,7 +11219,7 @@
         <v>5.5</v>
       </c>
       <c r="T43">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="U43">
         <v>1.79</v>
@@ -11348,7 +11348,7 @@
         <v>13</v>
       </c>
       <c r="BK43">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL43">
         <v>240</v>
@@ -11357,10 +11357,10 @@
         <v>1.01</v>
       </c>
       <c r="BN43">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BO43">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP43">
         <v>26</v>
@@ -11375,7 +11375,7 @@
         <v>1.01</v>
       </c>
       <c r="BT43">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU43">
         <v>5</v>
@@ -11419,16 +11419,16 @@
         <v>209</v>
       </c>
       <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44">
+        <v>3.2</v>
+      </c>
+      <c r="H44">
+        <v>2.7</v>
+      </c>
+      <c r="I44">
         <v>2.82</v>
-      </c>
-      <c r="G44">
-        <v>3</v>
-      </c>
-      <c r="H44">
-        <v>2.86</v>
-      </c>
-      <c r="I44">
-        <v>3.1</v>
       </c>
       <c r="J44">
         <v>3.1</v>
@@ -11446,7 +11446,7 @@
         <v>3.15</v>
       </c>
       <c r="O44">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P44">
         <v>1.7</v>
@@ -11461,28 +11461,28 @@
         <v>4.4</v>
       </c>
       <c r="T44">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U44">
         <v>1.97</v>
       </c>
       <c r="V44">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W44">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="X44">
         <v>12</v>
       </c>
       <c r="Y44">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z44">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AA44">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB44">
         <v>10.5</v>
@@ -11491,13 +11491,13 @@
         <v>7</v>
       </c>
       <c r="AD44">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE44">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF44">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AG44">
         <v>14</v>
@@ -11521,7 +11521,7 @@
         <v>580</v>
       </c>
       <c r="AN44">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO44">
         <v>44</v>
@@ -11530,13 +11530,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ44">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR44">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS44">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT44">
         <v>8.4</v>
@@ -11548,7 +11548,7 @@
         <v>11</v>
       </c>
       <c r="AW44">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX44">
         <v>13</v>
@@ -11560,31 +11560,31 @@
         <v>13.5</v>
       </c>
       <c r="BA44">
+        <v>7</v>
+      </c>
+      <c r="BB44">
+        <v>6.8</v>
+      </c>
+      <c r="BC44">
         <v>6.6</v>
       </c>
-      <c r="BB44">
-        <v>6.6</v>
-      </c>
-      <c r="BC44">
-        <v>6.2</v>
-      </c>
       <c r="BD44">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE44">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF44">
         <v>30</v>
       </c>
       <c r="BG44">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH44">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI44">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ44">
         <v>12.5</v>
@@ -11599,13 +11599,13 @@
         <v>4.8</v>
       </c>
       <c r="BN44">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO44">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP44">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BQ44">
         <v>4.2</v>
@@ -11617,22 +11617,22 @@
         <v>4.5</v>
       </c>
       <c r="BT44">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU44">
+        <v>4.2</v>
+      </c>
+      <c r="BV44">
+        <v>27</v>
+      </c>
+      <c r="BW44">
+        <v>4.1</v>
+      </c>
+      <c r="BX44">
+        <v>50</v>
+      </c>
+      <c r="BY44">
         <v>4.4</v>
-      </c>
-      <c r="BV44">
-        <v>30</v>
-      </c>
-      <c r="BW44">
-        <v>4.2</v>
-      </c>
-      <c r="BX44">
-        <v>55</v>
-      </c>
-      <c r="BY44">
-        <v>4.5</v>
       </c>
       <c r="BZ44">
         <v>0</v>
@@ -11667,7 +11667,7 @@
         <v>2.1</v>
       </c>
       <c r="H45">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I45">
         <v>5</v>
@@ -11694,7 +11694,7 @@
         <v>1.61</v>
       </c>
       <c r="Q45">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R45">
         <v>1.23</v>
@@ -11736,7 +11736,7 @@
         <v>21</v>
       </c>
       <c r="AE45">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF45">
         <v>11.5</v>
@@ -11826,7 +11826,7 @@
         <v>3.3</v>
       </c>
       <c r="BI45">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ45">
         <v>13.5</v>
@@ -11841,13 +11841,13 @@
         <v>1.01</v>
       </c>
       <c r="BN45">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BO45">
         <v>3.95</v>
       </c>
       <c r="BP45">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ45">
         <v>1.01</v>
@@ -11871,7 +11871,7 @@
         <v>1.01</v>
       </c>
       <c r="BX45">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BY45">
         <v>1.01</v>
@@ -11906,10 +11906,10 @@
         <v>2.32</v>
       </c>
       <c r="G46">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H46">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I46">
         <v>3.7</v>
@@ -11918,7 +11918,7 @@
         <v>3.2</v>
       </c>
       <c r="K46">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L46">
         <v>1.49</v>
@@ -11942,13 +11942,13 @@
         <v>1.27</v>
       </c>
       <c r="S46">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T46">
         <v>1.9</v>
       </c>
       <c r="U46">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V46">
         <v>1.38</v>
@@ -11960,31 +11960,31 @@
         <v>13</v>
       </c>
       <c r="Y46">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z46">
         <v>48</v>
       </c>
       <c r="AA46">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB46">
         <v>9</v>
       </c>
       <c r="AC46">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD46">
         <v>18.5</v>
       </c>
       <c r="AE46">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AF46">
         <v>15</v>
       </c>
       <c r="AG46">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH46">
         <v>21</v>
@@ -12008,7 +12008,7 @@
         <v>34</v>
       </c>
       <c r="AO46">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AP46">
         <v>8</v>
@@ -12020,106 +12020,106 @@
         <v>17.5</v>
       </c>
       <c r="AS46">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT46">
+        <v>7.4</v>
+      </c>
+      <c r="AU46">
         <v>6.4</v>
-      </c>
-      <c r="AU46">
-        <v>5.6</v>
       </c>
       <c r="AV46">
         <v>11</v>
       </c>
       <c r="AW46">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AX46">
         <v>10.5</v>
       </c>
       <c r="AY46">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ46">
         <v>14.5</v>
       </c>
       <c r="BA46">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB46">
+        <v>5.5</v>
+      </c>
+      <c r="BC46">
+        <v>5.4</v>
+      </c>
+      <c r="BD46">
+        <v>5.8</v>
+      </c>
+      <c r="BE46">
+        <v>6.2</v>
+      </c>
+      <c r="BF46">
+        <v>5.4</v>
+      </c>
+      <c r="BG46">
+        <v>5.9</v>
+      </c>
+      <c r="BH46">
+        <v>3.5</v>
+      </c>
+      <c r="BI46">
+        <v>2.7</v>
+      </c>
+      <c r="BJ46">
+        <v>12.5</v>
+      </c>
+      <c r="BK46">
+        <v>1.01</v>
+      </c>
+      <c r="BL46">
+        <v>190</v>
+      </c>
+      <c r="BM46">
+        <v>1.01</v>
+      </c>
+      <c r="BN46">
+        <v>6</v>
+      </c>
+      <c r="BO46">
+        <v>3.9</v>
+      </c>
+      <c r="BP46">
+        <v>23</v>
+      </c>
+      <c r="BQ46">
+        <v>1.01</v>
+      </c>
+      <c r="BR46">
+        <v>44</v>
+      </c>
+      <c r="BS46">
+        <v>1.01</v>
+      </c>
+      <c r="BT46">
+        <v>7.8</v>
+      </c>
+      <c r="BU46">
         <v>5</v>
       </c>
-      <c r="BC46">
-        <v>21</v>
-      </c>
-      <c r="BD46">
-        <v>5.2</v>
-      </c>
-      <c r="BE46">
-        <v>5.6</v>
-      </c>
-      <c r="BF46">
-        <v>5</v>
-      </c>
-      <c r="BG46">
-        <v>5.4</v>
-      </c>
-      <c r="BH46">
-        <v>1000</v>
-      </c>
-      <c r="BI46">
-        <v>1.01</v>
-      </c>
-      <c r="BJ46">
-        <v>1000</v>
-      </c>
-      <c r="BK46">
-        <v>1.01</v>
-      </c>
-      <c r="BL46">
-        <v>1000</v>
-      </c>
-      <c r="BM46">
-        <v>1.01</v>
-      </c>
-      <c r="BN46">
-        <v>1000</v>
-      </c>
-      <c r="BO46">
-        <v>1.01</v>
-      </c>
-      <c r="BP46">
-        <v>1000</v>
-      </c>
-      <c r="BQ46">
-        <v>1.01</v>
-      </c>
-      <c r="BR46">
-        <v>1000</v>
-      </c>
-      <c r="BS46">
-        <v>1.01</v>
-      </c>
-      <c r="BT46">
-        <v>1000</v>
-      </c>
-      <c r="BU46">
-        <v>1.01</v>
-      </c>
       <c r="BV46">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW46">
         <v>1.01</v>
       </c>
       <c r="BX46">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY46">
         <v>1.01</v>
       </c>
       <c r="BZ46">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA46">
         <v>1.01</v>
@@ -12148,16 +12148,16 @@
         <v>2.38</v>
       </c>
       <c r="G47">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H47">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="I47">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="J47">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="K47">
         <v>3.25</v>
@@ -12172,139 +12172,139 @@
         <v>2.48</v>
       </c>
       <c r="O47">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P47">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Q47">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R47">
         <v>1.16</v>
       </c>
       <c r="S47">
-        <v>2.74</v>
+        <v>5.6</v>
       </c>
       <c r="T47">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U47">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V47">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W47">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X47">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="Y47">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="Z47">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AA47">
         <v>900</v>
       </c>
       <c r="AB47">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="AC47">
-        <v>500</v>
+        <v>7.6</v>
       </c>
       <c r="AD47">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AE47">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AF47">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AG47">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AH47">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AI47">
         <v>500</v>
       </c>
       <c r="AJ47">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK47">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AL47">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AM47">
         <v>580</v>
       </c>
       <c r="AN47">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO47">
         <v>500</v>
       </c>
       <c r="AP47">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AQ47">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR47">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS47">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT47">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU47">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV47">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW47">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX47">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY47">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ47">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA47">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB47">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC47">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD47">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE47">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF47">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BG47">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12387,22 +12387,22 @@
         <v>213</v>
       </c>
       <c r="F48">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G48">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H48">
         <v>3.55</v>
       </c>
       <c r="I48">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J48">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K48">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L48">
         <v>1.49</v>
@@ -12411,82 +12411,82 @@
         <v>1.1</v>
       </c>
       <c r="N48">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O48">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P48">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q48">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R48">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S48">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T48">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="U48">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="V48">
         <v>1.33</v>
       </c>
       <c r="W48">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X48">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="Y48">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="Z48">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AA48">
         <v>900</v>
       </c>
       <c r="AB48">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC48">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD48">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AE48">
         <v>500</v>
       </c>
       <c r="AF48">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AG48">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH48">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AI48">
         <v>500</v>
       </c>
       <c r="AJ48">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AK48">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AL48">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AM48">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN48">
         <v>500</v>
@@ -12495,58 +12495,58 @@
         <v>500</v>
       </c>
       <c r="AP48">
-        <v>1.48</v>
+        <v>8.4</v>
       </c>
       <c r="AQ48">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AR48">
-        <v>1.61</v>
+        <v>16</v>
       </c>
       <c r="AS48">
-        <v>1.55</v>
+        <v>8.6</v>
       </c>
       <c r="AT48">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AU48">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV48">
-        <v>1.6</v>
+        <v>13.5</v>
       </c>
       <c r="AW48">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX48">
+        <v>11.5</v>
+      </c>
+      <c r="AY48">
+        <v>9.6</v>
+      </c>
+      <c r="AZ48">
+        <v>17</v>
+      </c>
+      <c r="BA48">
         <v>8.4</v>
       </c>
-      <c r="AY48">
-        <v>1.49</v>
-      </c>
-      <c r="AZ48">
-        <v>1.6</v>
-      </c>
-      <c r="BA48">
-        <v>1.55</v>
-      </c>
       <c r="BB48">
-        <v>1.62</v>
+        <v>18.5</v>
       </c>
       <c r="BC48">
-        <v>1.6</v>
+        <v>17</v>
       </c>
       <c r="BD48">
-        <v>1.55</v>
+        <v>29</v>
       </c>
       <c r="BE48">
-        <v>1.48</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF48">
-        <v>1.55</v>
+        <v>20</v>
       </c>
       <c r="BG48">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH48">
         <v>1000</v>
@@ -12629,13 +12629,13 @@
         <v>214</v>
       </c>
       <c r="F49">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G49">
         <v>3.4</v>
       </c>
       <c r="H49">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I49">
         <v>2.74</v>
@@ -12647,106 +12647,106 @@
         <v>3.05</v>
       </c>
       <c r="L49">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N49">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="O49">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="P49">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="Q49">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="R49">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S49">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="T49">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="U49">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="V49">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W49">
         <v>1.41</v>
       </c>
       <c r="X49">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="Y49">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z49">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA49">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB49">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AC49">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD49">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE49">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF49">
         <v>21</v>
       </c>
       <c r="AG49">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH49">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI49">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ49">
         <v>65</v>
       </c>
       <c r="AK49">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL49">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM49">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AN49">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO49">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP49">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ49">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR49">
         <v>14</v>
       </c>
       <c r="AS49">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT49">
         <v>8.6</v>
@@ -12755,58 +12755,58 @@
         <v>6.4</v>
       </c>
       <c r="AV49">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW49">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AX49">
         <v>18.5</v>
       </c>
       <c r="AY49">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AZ49">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA49">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB49">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC49">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="BD49">
         <v>28</v>
       </c>
       <c r="BE49">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BF49">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="BG49">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BH49">
         <v>2.92</v>
       </c>
       <c r="BI49">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="BJ49">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK49">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL49">
         <v>1000</v>
       </c>
       <c r="BM49">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN49">
         <v>6.6</v>
@@ -12818,13 +12818,13 @@
         <v>34</v>
       </c>
       <c r="BQ49">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BR49">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS49">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT49">
         <v>5.4</v>
@@ -12833,22 +12833,22 @@
         <v>4.6</v>
       </c>
       <c r="BV49">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW49">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX49">
+        <v>46</v>
+      </c>
+      <c r="BY49">
+        <v>8.4</v>
+      </c>
+      <c r="BZ49">
         <v>48</v>
       </c>
-      <c r="BY49">
-        <v>7.8</v>
-      </c>
-      <c r="BZ49">
-        <v>55</v>
-      </c>
       <c r="CA49">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB49" t="s">
         <v>215</v>
